--- a/00.data/01.incertezas/merged_uncertainty_indices.xlsx
+++ b/00.data/01.incertezas/merged_uncertainty_indices.xlsx
@@ -389,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D792"/>
+  <dimension ref="A1:D793"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -3969,7 +3969,7 @@
         <v>35431</v>
       </c>
       <c r="B448">
-        <v>78.88172911601586</v>
+        <v>78.57118072421564</v>
       </c>
       <c r="D448">
         <v>26.79430816055774</v>
@@ -3980,7 +3980,7 @@
         <v>35462</v>
       </c>
       <c r="B449">
-        <v>75.63586895472635</v>
+        <v>75.66477259555531</v>
       </c>
       <c r="D449">
         <v>35.15929037279584</v>
@@ -3991,7 +3991,7 @@
         <v>35490</v>
       </c>
       <c r="B450">
-        <v>64.61026303941573</v>
+        <v>64.20964132086495</v>
       </c>
       <c r="D450">
         <v>30.29108998670148</v>
@@ -4002,7 +4002,7 @@
         <v>35521</v>
       </c>
       <c r="B451">
-        <v>71.7409153781858</v>
+        <v>71.70127271404529</v>
       </c>
       <c r="D451">
         <v>32.08635956621232</v>
@@ -4013,7 +4013,7 @@
         <v>35551</v>
       </c>
       <c r="B452">
-        <v>82.41257274010701</v>
+        <v>82.29804958233474</v>
       </c>
       <c r="D452">
         <v>33.63899132861557</v>
@@ -4024,7 +4024,7 @@
         <v>35582</v>
       </c>
       <c r="B453">
-        <v>82.85556613851293</v>
+        <v>83.00037358131266</v>
       </c>
       <c r="D453">
         <v>34.3660237997538</v>
@@ -4035,7 +4035,7 @@
         <v>35612</v>
       </c>
       <c r="B454">
-        <v>66.50030625934696</v>
+        <v>66.41480168348022</v>
       </c>
       <c r="D454">
         <v>30.62748373705926</v>
@@ -4046,7 +4046,7 @@
         <v>35643</v>
       </c>
       <c r="B455">
-        <v>58.23589172410215</v>
+        <v>57.95276230874258</v>
       </c>
       <c r="D455">
         <v>27.38005526249686</v>
@@ -4057,7 +4057,7 @@
         <v>35674</v>
       </c>
       <c r="B456">
-        <v>60.9561807658015</v>
+        <v>60.65129317215975</v>
       </c>
       <c r="D456">
         <v>33.76015819045553</v>
@@ -4068,7 +4068,7 @@
         <v>35704</v>
       </c>
       <c r="B457">
-        <v>76.10270761588991</v>
+        <v>75.95065992047836</v>
       </c>
       <c r="D457">
         <v>36.76305761040125</v>
@@ -4079,7 +4079,7 @@
         <v>35735</v>
       </c>
       <c r="B458">
-        <v>84.54287480749029</v>
+        <v>83.95028923871065</v>
       </c>
       <c r="D458">
         <v>47.08053373710609</v>
@@ -4090,7 +4090,7 @@
         <v>35765</v>
       </c>
       <c r="B459">
-        <v>92.99636080270791</v>
+        <v>92.45998052913758</v>
       </c>
       <c r="D459">
         <v>31.96717400639344</v>
@@ -4101,7 +4101,7 @@
         <v>35796</v>
       </c>
       <c r="B460">
-        <v>88.80542842904607</v>
+        <v>88.1445689993093</v>
       </c>
       <c r="D460">
         <v>30.68600263672319</v>
@@ -4112,7 +4112,7 @@
         <v>35827</v>
       </c>
       <c r="B461">
-        <v>76.31219724080658</v>
+        <v>75.63332218241041</v>
       </c>
       <c r="D461">
         <v>25.52968123687727</v>
@@ -4123,7 +4123,7 @@
         <v>35855</v>
       </c>
       <c r="B462">
-        <v>76.49184034039831</v>
+        <v>76.08511831750164</v>
       </c>
       <c r="D462">
         <v>29.84241487397484</v>
@@ -4134,7 +4134,7 @@
         <v>35886</v>
       </c>
       <c r="B463">
-        <v>72.05325594701561</v>
+        <v>71.30368064276563</v>
       </c>
       <c r="D463">
         <v>30.76646679691886</v>
@@ -4145,7 +4145,7 @@
         <v>35916</v>
       </c>
       <c r="B464">
-        <v>78.55399794716824</v>
+        <v>77.8988796701544</v>
       </c>
       <c r="D464">
         <v>25.65856996236743</v>
@@ -4156,7 +4156,7 @@
         <v>35947</v>
       </c>
       <c r="B465">
-        <v>76.69198401296532</v>
+        <v>76.07220014492798</v>
       </c>
       <c r="D465">
         <v>33.53731570809468</v>
@@ -4167,7 +4167,7 @@
         <v>35977</v>
       </c>
       <c r="B466">
-        <v>92.38793384344818</v>
+        <v>91.77059119792412</v>
       </c>
       <c r="D466">
         <v>36.33124721655767</v>
@@ -4178,7 +4178,7 @@
         <v>36008</v>
       </c>
       <c r="B467">
-        <v>103.7408166290898</v>
+        <v>103.0937688080636</v>
       </c>
       <c r="D467">
         <v>32.31396056760174</v>
@@ -4189,7 +4189,7 @@
         <v>36039</v>
       </c>
       <c r="B468">
-        <v>142.2620299025487</v>
+        <v>142.6858139801402</v>
       </c>
       <c r="D468">
         <v>32.45070422535211</v>
@@ -4200,7 +4200,7 @@
         <v>36069</v>
       </c>
       <c r="B469">
-        <v>108.7567106317408</v>
+        <v>108.0688872019831</v>
       </c>
       <c r="D469">
         <v>33.76769557123685</v>
@@ -4211,7 +4211,7 @@
         <v>36100</v>
       </c>
       <c r="B470">
-        <v>90.38910998478227</v>
+        <v>90.07161422708249</v>
       </c>
       <c r="D470">
         <v>30.20467045352087</v>
@@ -4222,7 +4222,7 @@
         <v>36130</v>
       </c>
       <c r="B471">
-        <v>89.17130879864598</v>
+        <v>88.97084294021978</v>
       </c>
       <c r="D471">
         <v>35.70021095579201</v>
@@ -4233,7 +4233,7 @@
         <v>36161</v>
       </c>
       <c r="B472">
-        <v>91.41169161626863</v>
+        <v>91.49401821271482</v>
       </c>
       <c r="D472">
         <v>34.19077996282613</v>
@@ -4244,7 +4244,7 @@
         <v>36192</v>
       </c>
       <c r="B473">
-        <v>74.6885824810598</v>
+        <v>74.69705224764208</v>
       </c>
       <c r="D473">
         <v>34.41053261520048</v>
@@ -4255,7 +4255,7 @@
         <v>36220</v>
       </c>
       <c r="B474">
-        <v>56.53704810554756</v>
+        <v>56.51740925169905</v>
       </c>
       <c r="D474">
         <v>39.11342894393742</v>
@@ -4266,7 +4266,7 @@
         <v>36251</v>
       </c>
       <c r="B475">
-        <v>63.33413610031029</v>
+        <v>63.24217964700514</v>
       </c>
       <c r="D475">
         <v>34.92721618820136</v>
@@ -4277,7 +4277,7 @@
         <v>36281</v>
       </c>
       <c r="B476">
-        <v>67.33185877348713</v>
+        <v>67.15236607824785</v>
       </c>
       <c r="D476">
         <v>30.32059571052749</v>
@@ -4288,7 +4288,7 @@
         <v>36312</v>
       </c>
       <c r="B477">
-        <v>66.93554570991243</v>
+        <v>66.87281863447099</v>
       </c>
       <c r="D477">
         <v>33.0491863062406</v>
@@ -4299,7 +4299,7 @@
         <v>36342</v>
       </c>
       <c r="B478">
-        <v>70.01122291021774</v>
+        <v>70.10820107781508</v>
       </c>
       <c r="D478">
         <v>31.69572107765451</v>
@@ -4310,7 +4310,7 @@
         <v>36373</v>
       </c>
       <c r="B479">
-        <v>67.66068809319977</v>
+        <v>67.84925105187031</v>
       </c>
       <c r="D479">
         <v>32.25347436323104</v>
@@ -4321,7 +4321,7 @@
         <v>36404</v>
       </c>
       <c r="B480">
-        <v>61.61684192890461</v>
+        <v>61.48158530008502</v>
       </c>
       <c r="D480">
         <v>30.38519072550486</v>
@@ -4332,7 +4332,7 @@
         <v>36434</v>
       </c>
       <c r="B481">
-        <v>65.96760368359179</v>
+        <v>66.06217462121386</v>
       </c>
       <c r="D481">
         <v>32.63973888208894</v>
@@ -4343,7 +4343,7 @@
         <v>36465</v>
       </c>
       <c r="B482">
-        <v>65.05732046258142</v>
+        <v>65.04577994267187</v>
       </c>
       <c r="D482">
         <v>48.94195531386688</v>
@@ -4354,7 +4354,7 @@
         <v>36495</v>
       </c>
       <c r="B483">
-        <v>57.92363843517686</v>
+        <v>57.75203300815224</v>
       </c>
       <c r="D483">
         <v>41.58353964858303</v>
@@ -4365,7 +4365,7 @@
         <v>36526</v>
       </c>
       <c r="B484">
-        <v>66.36937686325349</v>
+        <v>66.40531228547813</v>
       </c>
       <c r="D484">
         <v>32.11734816164134</v>
@@ -4376,7 +4376,7 @@
         <v>36557</v>
       </c>
       <c r="B485">
-        <v>55.56712223882615</v>
+        <v>55.57682245758716</v>
       </c>
       <c r="D485">
         <v>28.17585620597523</v>
@@ -4387,7 +4387,7 @@
         <v>36586</v>
       </c>
       <c r="B486">
-        <v>60.53040614362065</v>
+        <v>60.55873213053427</v>
       </c>
       <c r="D486">
         <v>36.83850616548651</v>
@@ -4398,7 +4398,7 @@
         <v>36617</v>
       </c>
       <c r="B487">
-        <v>61.61349384977663</v>
+        <v>61.63069719471124</v>
       </c>
       <c r="D487">
         <v>35.28104006572906</v>
@@ -4409,7 +4409,7 @@
         <v>36647</v>
       </c>
       <c r="B488">
-        <v>81.41720614975051</v>
+        <v>81.43633076281019</v>
       </c>
       <c r="D488">
         <v>49.32756293917819</v>
@@ -4420,7 +4420,7 @@
         <v>36678</v>
       </c>
       <c r="B489">
-        <v>85.19201386611233</v>
+        <v>85.21831071461878</v>
       </c>
       <c r="D489">
         <v>27.36688135513247</v>
@@ -4431,7 +4431,7 @@
         <v>36708</v>
       </c>
       <c r="B490">
-        <v>63.41370315600142</v>
+        <v>63.43967656618085</v>
       </c>
       <c r="D490">
         <v>31.94444444444445</v>
@@ -4442,7 +4442,7 @@
         <v>36739</v>
       </c>
       <c r="B491">
-        <v>52.79341073984149</v>
+        <v>52.81009788652795</v>
       </c>
       <c r="D491">
         <v>29.21261803935777</v>
@@ -4453,7 +4453,7 @@
         <v>36770</v>
       </c>
       <c r="B492">
-        <v>61.66484636111075</v>
+        <v>61.68400811087739</v>
       </c>
       <c r="D492">
         <v>33.43174713442168</v>
@@ -4464,7 +4464,7 @@
         <v>36800</v>
       </c>
       <c r="B493">
-        <v>67.72110406580776</v>
+        <v>67.7468490606027</v>
       </c>
       <c r="D493">
         <v>25.48113774315842</v>
@@ -4475,7 +4475,7 @@
         <v>36831</v>
       </c>
       <c r="B494">
-        <v>93.83541312982821</v>
+        <v>93.8415610874582</v>
       </c>
       <c r="D494">
         <v>26.90486439948343</v>
@@ -4486,7 +4486,7 @@
         <v>36861</v>
       </c>
       <c r="B495">
-        <v>94.66183915404399</v>
+        <v>94.69139998088097</v>
       </c>
       <c r="D495">
         <v>29.81667404318759</v>
@@ -4497,7 +4497,7 @@
         <v>36892</v>
       </c>
       <c r="B496">
-        <v>93.3555846028043</v>
+        <v>93.38940354667724</v>
       </c>
       <c r="D496">
         <v>25.98787232624775</v>
@@ -4508,7 +4508,7 @@
         <v>36923</v>
       </c>
       <c r="B497">
-        <v>93.59337463522466</v>
+        <v>93.61953785443541</v>
       </c>
       <c r="D497">
         <v>20.64627646804629</v>
@@ -4519,7 +4519,7 @@
         <v>36951</v>
       </c>
       <c r="B498">
-        <v>104.0945070837737</v>
+        <v>104.1318899869225</v>
       </c>
       <c r="D498">
         <v>25.07863640227833</v>
@@ -4530,7 +4530,7 @@
         <v>36982</v>
       </c>
       <c r="B499">
-        <v>95.96301122819013</v>
+        <v>95.97975262155236</v>
       </c>
       <c r="D499">
         <v>34.3147347471004</v>
@@ -4541,7 +4541,7 @@
         <v>37012</v>
       </c>
       <c r="B500">
-        <v>76.23125947664855</v>
+        <v>76.24907787234997</v>
       </c>
       <c r="D500">
         <v>27.79333821691731</v>
@@ -4552,7 +4552,7 @@
         <v>37043</v>
       </c>
       <c r="B501">
-        <v>70.38790848777758</v>
+        <v>70.41441125394122</v>
       </c>
       <c r="D501">
         <v>30.15970937007334</v>
@@ -4563,7 +4563,7 @@
         <v>37073</v>
       </c>
       <c r="B502">
-        <v>89.31964965010265</v>
+        <v>89.33913539939647</v>
       </c>
       <c r="D502">
         <v>34.29895712630359</v>
@@ -4574,7 +4574,7 @@
         <v>37104</v>
       </c>
       <c r="B503">
-        <v>78.63095877168659</v>
+        <v>78.65587821853363</v>
       </c>
       <c r="D503">
         <v>28.28561572956192</v>
@@ -4585,7 +4585,7 @@
         <v>37135</v>
       </c>
       <c r="B504">
-        <v>157.8723655824944</v>
+        <v>157.900303492271</v>
       </c>
       <c r="D504">
         <v>24.12961047914512</v>
@@ -4596,7 +4596,7 @@
         <v>37165</v>
       </c>
       <c r="B505">
-        <v>149.6623063911168</v>
+        <v>149.6951438155147</v>
       </c>
       <c r="D505">
         <v>24.04201024948858</v>
@@ -4607,7 +4607,7 @@
         <v>37196</v>
       </c>
       <c r="B506">
-        <v>116.1887525114461</v>
+        <v>116.2229925402432</v>
       </c>
       <c r="D506">
         <v>33.66046643789207</v>
@@ -4618,7 +4618,7 @@
         <v>37226</v>
       </c>
       <c r="B507">
-        <v>100.5869565895578</v>
+        <v>100.6259893484772</v>
       </c>
       <c r="D507">
         <v>34.28891325138206</v>
@@ -4629,7 +4629,7 @@
         <v>37257</v>
       </c>
       <c r="B508">
-        <v>99.52874514680569</v>
+        <v>99.5713084907656</v>
       </c>
       <c r="D508">
         <v>31.63412870571222</v>
@@ -4640,7 +4640,7 @@
         <v>37288</v>
       </c>
       <c r="B509">
-        <v>80.76623809411846</v>
+        <v>80.7941328594266</v>
       </c>
       <c r="D509">
         <v>31.94888178913738</v>
@@ -4651,7 +4651,7 @@
         <v>37316</v>
       </c>
       <c r="B510">
-        <v>74.59895293555981</v>
+        <v>74.63588545244289</v>
       </c>
       <c r="D510">
         <v>53.87744504067855</v>
@@ -4662,7 +4662,7 @@
         <v>37347</v>
       </c>
       <c r="B511">
-        <v>79.13781955667604</v>
+        <v>79.1691146283863</v>
       </c>
       <c r="D511">
         <v>36.55340475424158</v>
@@ -4673,7 +4673,7 @@
         <v>37377</v>
       </c>
       <c r="B512">
-        <v>77.9733241571243</v>
+        <v>78.00537131504606</v>
       </c>
       <c r="D512">
         <v>41.12330393860093</v>
@@ -4684,7 +4684,7 @@
         <v>37408</v>
       </c>
       <c r="B513">
-        <v>88.84457167091276</v>
+        <v>88.86527764028003</v>
       </c>
       <c r="D513">
         <v>39.78324987996433</v>
@@ -4695,7 +4695,7 @@
         <v>37438</v>
       </c>
       <c r="B514">
-        <v>94.06359565894648</v>
+        <v>94.10067606051061</v>
       </c>
       <c r="D514">
         <v>40.61059219798858</v>
@@ -4706,7 +4706,7 @@
         <v>37469</v>
       </c>
       <c r="B515">
-        <v>98.66473333025834</v>
+        <v>98.69483710970307</v>
       </c>
       <c r="D515">
         <v>34.50802429743081</v>
@@ -4717,7 +4717,7 @@
         <v>37500</v>
       </c>
       <c r="B516">
-        <v>113.8383331222476</v>
+        <v>113.8761766624583</v>
       </c>
       <c r="D516">
         <v>27.68700072621641</v>
@@ -4728,7 +4728,7 @@
         <v>37530</v>
       </c>
       <c r="B517">
-        <v>113.1492716886883</v>
+        <v>113.1879198638282</v>
       </c>
       <c r="D517">
         <v>32.54575425842174</v>
@@ -4739,7 +4739,7 @@
         <v>37561</v>
       </c>
       <c r="B518">
-        <v>114.3935444407054</v>
+        <v>114.4343924884649</v>
       </c>
       <c r="D518">
         <v>31.85472511755911</v>
@@ -4750,7 +4750,7 @@
         <v>37591</v>
       </c>
       <c r="B519">
-        <v>115.9276924859186</v>
+        <v>115.9898072298102</v>
       </c>
       <c r="D519">
         <v>24.72299013327939</v>
@@ -4761,7 +4761,7 @@
         <v>37622</v>
       </c>
       <c r="B520">
-        <v>113.244577202114</v>
+        <v>113.2780218049955</v>
       </c>
       <c r="D520">
         <v>25.27453372842949</v>
@@ -4772,7 +4772,7 @@
         <v>37653</v>
       </c>
       <c r="B521">
-        <v>122.6759438035132</v>
+        <v>122.6962068545575</v>
       </c>
       <c r="D521">
         <v>31.57377739317538</v>
@@ -4783,7 +4783,7 @@
         <v>37681</v>
       </c>
       <c r="B522">
-        <v>154.9595546879596</v>
+        <v>155.0111181696256</v>
       </c>
       <c r="D522">
         <v>23.27466179007086</v>
@@ -4794,7 +4794,7 @@
         <v>37712</v>
       </c>
       <c r="B523">
-        <v>130.42518219938</v>
+        <v>130.4987692661987</v>
       </c>
       <c r="D523">
         <v>16.24980785700169</v>
@@ -4805,7 +4805,7 @@
         <v>37742</v>
       </c>
       <c r="B524">
-        <v>101.6855314401487</v>
+        <v>101.7353919231809</v>
       </c>
       <c r="D524">
         <v>28.59866539561487</v>
@@ -4816,7 +4816,7 @@
         <v>37773</v>
       </c>
       <c r="B525">
-        <v>82.52073210287212</v>
+        <v>82.56056338381144</v>
       </c>
       <c r="D525">
         <v>32.85968028419182</v>
@@ -4827,7 +4827,7 @@
         <v>37803</v>
       </c>
       <c r="B526">
-        <v>82.57534944349455</v>
+        <v>82.63717785535752</v>
       </c>
       <c r="D526">
         <v>28.43494085532302</v>
@@ -4838,7 +4838,7 @@
         <v>37834</v>
       </c>
       <c r="B527">
-        <v>71.23392431474886</v>
+        <v>71.27819141588559</v>
       </c>
       <c r="D527">
         <v>24.55159244356544</v>
@@ -4849,7 +4849,7 @@
         <v>37865</v>
       </c>
       <c r="B528">
-        <v>76.21134111173582</v>
+        <v>76.24735842652191</v>
       </c>
       <c r="D528">
         <v>39.80838000134943</v>
@@ -4860,7 +4860,7 @@
         <v>37895</v>
       </c>
       <c r="B529">
-        <v>78.34126034325047</v>
+        <v>78.38680454134509</v>
       </c>
       <c r="D529">
         <v>31.40458547999754</v>
@@ -4871,7 +4871,7 @@
         <v>37926</v>
       </c>
       <c r="B530">
-        <v>75.21309848582165</v>
+        <v>75.24123867757834</v>
       </c>
       <c r="D530">
         <v>50.17905300853265</v>
@@ -4882,7 +4882,7 @@
         <v>37956</v>
       </c>
       <c r="B531">
-        <v>69.90866692378887</v>
+        <v>69.94716143770079</v>
       </c>
       <c r="D531">
         <v>46.6441488017279</v>
@@ -4893,7 +4893,7 @@
         <v>37987</v>
       </c>
       <c r="B532">
-        <v>76.73857317936411</v>
+        <v>76.78115936638162</v>
       </c>
       <c r="D532">
         <v>30.87917420265561</v>
@@ -4904,7 +4904,7 @@
         <v>38018</v>
       </c>
       <c r="B533">
-        <v>79.58371614961932</v>
+        <v>79.62758811936206</v>
       </c>
       <c r="D533">
         <v>35.39903333408972</v>
@@ -4915,7 +4915,7 @@
         <v>38047</v>
       </c>
       <c r="B534">
-        <v>74.99949180902354</v>
+        <v>75.03600589485724</v>
       </c>
       <c r="D534">
         <v>27.12360614801739</v>
@@ -4926,7 +4926,7 @@
         <v>38078</v>
       </c>
       <c r="B535">
-        <v>79.72398823875371</v>
+        <v>79.76890066779714</v>
       </c>
       <c r="D535">
         <v>28.38389214120986</v>
@@ -4937,7 +4937,7 @@
         <v>38108</v>
       </c>
       <c r="B536">
-        <v>94.40995441448936</v>
+        <v>94.43824107098972</v>
       </c>
       <c r="D536">
         <v>30.99539496989018</v>
@@ -4948,7 +4948,7 @@
         <v>38139</v>
       </c>
       <c r="B537">
-        <v>77.95710234432404</v>
+        <v>77.99602794796898</v>
       </c>
       <c r="D537">
         <v>22.94156782674528</v>
@@ -4959,7 +4959,7 @@
         <v>38169</v>
       </c>
       <c r="B538">
-        <v>71.90350899087414</v>
+        <v>71.9396137219379</v>
       </c>
       <c r="D538">
         <v>34.2544484803899</v>
@@ -4970,7 +4970,7 @@
         <v>38200</v>
       </c>
       <c r="B539">
-        <v>67.77622312861554</v>
+        <v>67.81001082550377</v>
       </c>
       <c r="D539">
         <v>28.87239753682358</v>
@@ -4981,7 +4981,7 @@
         <v>38231</v>
       </c>
       <c r="B540">
-        <v>73.99646653768954</v>
+        <v>74.02283791029636</v>
       </c>
       <c r="D540">
         <v>28.53132693679391</v>
@@ -4992,7 +4992,7 @@
         <v>38261</v>
       </c>
       <c r="B541">
-        <v>88.92491967325466</v>
+        <v>88.97210500727789</v>
       </c>
       <c r="D541">
         <v>29.3588205040288</v>
@@ -5003,7 +5003,7 @@
         <v>38292</v>
       </c>
       <c r="B542">
-        <v>80.41834994172602</v>
+        <v>80.4554364077819</v>
       </c>
       <c r="D542">
         <v>31.06233174570304</v>
@@ -5014,7 +5014,7 @@
         <v>38322</v>
       </c>
       <c r="B543">
-        <v>67.83004991528632</v>
+        <v>67.88588088870627</v>
       </c>
       <c r="D543">
         <v>30.10064904524504</v>
@@ -5025,7 +5025,7 @@
         <v>38353</v>
       </c>
       <c r="B544">
-        <v>64.16668912774533</v>
+        <v>64.20632583148812</v>
       </c>
       <c r="D544">
         <v>27.60942760942761</v>
@@ -5036,7 +5036,7 @@
         <v>38384</v>
       </c>
       <c r="B545">
-        <v>58.05649702958101</v>
+        <v>58.0886944085553</v>
       </c>
       <c r="D545">
         <v>19.91745056632751</v>
@@ -5047,7 +5047,7 @@
         <v>38412</v>
       </c>
       <c r="B546">
-        <v>56.27007537004487</v>
+        <v>56.30350050351331</v>
       </c>
       <c r="D546">
         <v>23.08211571543671</v>
@@ -5058,7 +5058,7 @@
         <v>38443</v>
       </c>
       <c r="B547">
-        <v>76.24049403429329</v>
+        <v>76.30503394605381</v>
       </c>
       <c r="D547">
         <v>31.50427234196868</v>
@@ -5069,7 +5069,7 @@
         <v>38473</v>
       </c>
       <c r="B548">
-        <v>63.97245707837673</v>
+        <v>63.99170942475578</v>
       </c>
       <c r="D548">
         <v>33.32582751632515</v>
@@ -5080,7 +5080,7 @@
         <v>38504</v>
       </c>
       <c r="B549">
-        <v>71.54825752460219</v>
+        <v>71.58625175209211</v>
       </c>
       <c r="D549">
         <v>38.64912119260146</v>
@@ -5091,7 +5091,7 @@
         <v>38534</v>
       </c>
       <c r="B550">
-        <v>64.83889133784538</v>
+        <v>64.88890003788114</v>
       </c>
       <c r="D550">
         <v>34.02699011596953</v>
@@ -5102,7 +5102,7 @@
         <v>38565</v>
       </c>
       <c r="B551">
-        <v>63.04799211433685</v>
+        <v>63.09625553976446</v>
       </c>
       <c r="D551">
         <v>22.78778574683969</v>
@@ -5113,7 +5113,7 @@
         <v>38596</v>
       </c>
       <c r="B552">
-        <v>92.16807740522933</v>
+        <v>92.2249000502882</v>
       </c>
       <c r="D552">
         <v>22.9043630566097</v>
@@ -5124,7 +5124,7 @@
         <v>38626</v>
       </c>
       <c r="B553">
-        <v>68.56135815849498</v>
+        <v>68.60398215992502</v>
       </c>
       <c r="D553">
         <v>34.35678872749413</v>
@@ -5135,7 +5135,7 @@
         <v>38657</v>
       </c>
       <c r="B554">
-        <v>64.4249797776489</v>
+        <v>64.45380919082463</v>
       </c>
       <c r="D554">
         <v>28.04210913437227</v>
@@ -5146,7 +5146,7 @@
         <v>38687</v>
       </c>
       <c r="B555">
-        <v>66.70399686008517</v>
+        <v>66.75609064230144</v>
       </c>
       <c r="D555">
         <v>32.10837161338709</v>
@@ -5157,7 +5157,7 @@
         <v>38718</v>
       </c>
       <c r="B556">
-        <v>78.21150002374877</v>
+        <v>78.29673922039393</v>
       </c>
       <c r="D556">
         <v>23.6623859955432</v>
@@ -5168,7 +5168,7 @@
         <v>38749</v>
       </c>
       <c r="B557">
-        <v>61.18742939647976</v>
+        <v>61.24277056138386</v>
       </c>
       <c r="D557">
         <v>24.28658166363085</v>
@@ -5179,7 +5179,7 @@
         <v>38777</v>
       </c>
       <c r="B558">
-        <v>61.39760992370227</v>
+        <v>61.44567902950821</v>
       </c>
       <c r="D558">
         <v>24.32237000679273</v>
@@ -5190,7 +5190,7 @@
         <v>38808</v>
       </c>
       <c r="B559">
-        <v>73.98392708481954</v>
+        <v>74.03565797581602</v>
       </c>
       <c r="D559">
         <v>26.57322923525538</v>
@@ -5201,7 +5201,7 @@
         <v>38838</v>
       </c>
       <c r="B560">
-        <v>62.93668945080138</v>
+        <v>62.96969454928283</v>
       </c>
       <c r="D560">
         <v>27.05389969246422</v>
@@ -5212,7 +5212,7 @@
         <v>38869</v>
       </c>
       <c r="B561">
-        <v>72.61408210837797</v>
+        <v>72.655013660382</v>
       </c>
       <c r="D561">
         <v>26.84156474652227</v>
@@ -5223,7 +5223,7 @@
         <v>38899</v>
       </c>
       <c r="B562">
-        <v>71.11815604211809</v>
+        <v>71.16684342495321</v>
       </c>
       <c r="D562">
         <v>30.90742261071135</v>
@@ -5234,7 +5234,7 @@
         <v>38930</v>
       </c>
       <c r="B563">
-        <v>64.52291523591346</v>
+        <v>64.57872901692006</v>
       </c>
       <c r="D563">
         <v>20.98435711560473</v>
@@ -5245,7 +5245,7 @@
         <v>38961</v>
       </c>
       <c r="B564">
-        <v>57.07307302995512</v>
+        <v>57.09474729295705</v>
       </c>
       <c r="D564">
         <v>26.78760250957539</v>
@@ -5256,7 +5256,7 @@
         <v>38991</v>
       </c>
       <c r="B565">
-        <v>66.82635050830424</v>
+        <v>66.88803231055297</v>
       </c>
       <c r="D565">
         <v>23.69347414026536</v>
@@ -5267,7 +5267,7 @@
         <v>39022</v>
       </c>
       <c r="B566">
-        <v>64.2086085949077</v>
+        <v>64.26007478426405</v>
       </c>
       <c r="D566">
         <v>25.99792936845738</v>
@@ -5278,7 +5278,7 @@
         <v>39052</v>
       </c>
       <c r="B567">
-        <v>61.84574688195142</v>
+        <v>61.90166250226316</v>
       </c>
       <c r="D567">
         <v>26.97579469233012</v>
@@ -5289,7 +5289,7 @@
         <v>39083</v>
       </c>
       <c r="B568">
-        <v>65.10858379689357</v>
+        <v>65.13601102979226</v>
       </c>
       <c r="D568">
         <v>22.50257343260001</v>
@@ -5300,7 +5300,7 @@
         <v>39114</v>
       </c>
       <c r="B569">
-        <v>57.82362139546598</v>
+        <v>57.86122484891435</v>
       </c>
       <c r="D569">
         <v>27.55530375215679</v>
@@ -5311,7 +5311,7 @@
         <v>39142</v>
       </c>
       <c r="B570">
-        <v>67.47420584862533</v>
+        <v>67.53120117179637</v>
       </c>
       <c r="D570">
         <v>26.70623145400593</v>
@@ -5322,7 +5322,7 @@
         <v>39173</v>
       </c>
       <c r="B571">
-        <v>64.48334498032101</v>
+        <v>64.52218515820721</v>
       </c>
       <c r="D571">
         <v>30.43747420553033</v>
@@ -5333,7 +5333,7 @@
         <v>39203</v>
       </c>
       <c r="B572">
-        <v>57.17513541227581</v>
+        <v>57.21014820048162</v>
       </c>
       <c r="D572">
         <v>29.71149307194624</v>
@@ -5344,7 +5344,7 @@
         <v>39234</v>
       </c>
       <c r="B573">
-        <v>57.43122822458017</v>
+        <v>57.4732639487197</v>
       </c>
       <c r="D573">
         <v>34.27456563579319</v>
@@ -5355,7 +5355,7 @@
         <v>39264</v>
       </c>
       <c r="B574">
-        <v>52.31968378419396</v>
+        <v>52.37534909636721</v>
       </c>
       <c r="D574">
         <v>24.37064115527209</v>
@@ -5366,7 +5366,7 @@
         <v>39295</v>
       </c>
       <c r="B575">
-        <v>76.540727512646</v>
+        <v>76.58815533583363</v>
       </c>
       <c r="D575">
         <v>23.17382836575204</v>
@@ -5377,7 +5377,7 @@
         <v>39326</v>
       </c>
       <c r="B576">
-        <v>94.28849035136464</v>
+        <v>94.34433005662176</v>
       </c>
       <c r="D576">
         <v>18.99715042743588</v>
@@ -5388,7 +5388,7 @@
         <v>39356</v>
       </c>
       <c r="B577">
-        <v>79.06568496629717</v>
+        <v>79.11778962957177</v>
       </c>
       <c r="D577">
         <v>25.88229602573716</v>
@@ -5399,7 +5399,7 @@
         <v>39387</v>
       </c>
       <c r="B578">
-        <v>79.25007815061896</v>
+        <v>79.29422593887658</v>
       </c>
       <c r="D578">
         <v>27.3709128569315</v>
@@ -5410,7 +5410,7 @@
         <v>39417</v>
       </c>
       <c r="B579">
-        <v>99.51455601387137</v>
+        <v>99.59407560270064</v>
       </c>
       <c r="D579">
         <v>21.81988206873263</v>
@@ -5421,7 +5421,7 @@
         <v>39448</v>
       </c>
       <c r="B580">
-        <v>132.6866729092949</v>
+        <v>132.7696013132085</v>
       </c>
       <c r="C580">
         <v>17245.12</v>
@@ -5435,7 +5435,7 @@
         <v>39479</v>
       </c>
       <c r="B581">
-        <v>97.70335257087402</v>
+        <v>97.7583196387164</v>
       </c>
       <c r="C581">
         <v>16059.42</v>
@@ -5449,7 +5449,7 @@
         <v>39508</v>
       </c>
       <c r="B582">
-        <v>129.5137423689665</v>
+        <v>129.6511699923242</v>
       </c>
       <c r="C582">
         <v>11944.98</v>
@@ -5463,7 +5463,7 @@
         <v>39539</v>
       </c>
       <c r="B583">
-        <v>98.86075322955161</v>
+        <v>98.95335063460783</v>
       </c>
       <c r="C583">
         <v>14277.65</v>
@@ -5477,7 +5477,7 @@
         <v>39569</v>
       </c>
       <c r="B584">
-        <v>81.66252393700918</v>
+        <v>81.7308539421897</v>
       </c>
       <c r="C584">
         <v>14969.42</v>
@@ -5491,7 +5491,7 @@
         <v>39600</v>
       </c>
       <c r="B585">
-        <v>90.89590009976827</v>
+        <v>90.95951726161954</v>
       </c>
       <c r="C585">
         <v>16455.88</v>
@@ -5505,7 +5505,7 @@
         <v>39630</v>
       </c>
       <c r="B586">
-        <v>108.0645253639221</v>
+        <v>108.1919428369347</v>
       </c>
       <c r="C586">
         <v>9904.023999999999</v>
@@ -5519,7 +5519,7 @@
         <v>39661</v>
       </c>
       <c r="B587">
-        <v>98.97747596837375</v>
+        <v>99.10729394733214</v>
       </c>
       <c r="C587">
         <v>12619.14</v>
@@ -5533,7 +5533,7 @@
         <v>39692</v>
       </c>
       <c r="B588">
-        <v>159.3999812007487</v>
+        <v>159.5050423995914</v>
       </c>
       <c r="C588">
         <v>13118.48</v>
@@ -5547,7 +5547,7 @@
         <v>39722</v>
       </c>
       <c r="B589">
-        <v>209.1339075488069</v>
+        <v>209.2860670338012</v>
       </c>
       <c r="C589">
         <v>15511.13</v>
@@ -5561,7 +5561,7 @@
         <v>39753</v>
       </c>
       <c r="B590">
-        <v>146.3748940593563</v>
+        <v>146.5023403589852</v>
       </c>
       <c r="C590">
         <v>16251.19</v>
@@ -5575,7 +5575,7 @@
         <v>39783</v>
       </c>
       <c r="B591">
-        <v>148.5973638890535</v>
+        <v>148.7238643219771</v>
       </c>
       <c r="C591">
         <v>11388.37</v>
@@ -5589,7 +5589,7 @@
         <v>39814</v>
       </c>
       <c r="B592">
-        <v>146.4705902327778</v>
+        <v>146.6191685590836</v>
       </c>
       <c r="C592">
         <v>11772.56</v>
@@ -5603,7 +5603,7 @@
         <v>39845</v>
       </c>
       <c r="B593">
-        <v>144.3384447416162</v>
+        <v>144.45254603137</v>
       </c>
       <c r="C593">
         <v>15087.54</v>
@@ -5617,7 +5617,7 @@
         <v>39873</v>
       </c>
       <c r="B594">
-        <v>136.4048018819873</v>
+        <v>136.5335274027738</v>
       </c>
       <c r="C594">
         <v>20401.91</v>
@@ -5631,7 +5631,7 @@
         <v>39904</v>
       </c>
       <c r="B595">
-        <v>104.7647747970286</v>
+        <v>104.85473267745</v>
       </c>
       <c r="C595">
         <v>16736.19</v>
@@ -5645,7 +5645,7 @@
         <v>39934</v>
       </c>
       <c r="B596">
-        <v>100.5353298221776</v>
+        <v>100.5988320613798</v>
       </c>
       <c r="C596">
         <v>16066.15</v>
@@ -5659,7 +5659,7 @@
         <v>39965</v>
       </c>
       <c r="B597">
-        <v>130.6222469154595</v>
+        <v>130.8217387336834</v>
       </c>
       <c r="C597">
         <v>17881.58</v>
@@ -5673,7 +5673,7 @@
         <v>39995</v>
       </c>
       <c r="B598">
-        <v>117.8306243183183</v>
+        <v>117.9801342955144</v>
       </c>
       <c r="C598">
         <v>12265.1</v>
@@ -5687,7 +5687,7 @@
         <v>40026</v>
       </c>
       <c r="B599">
-        <v>109.3040517056946</v>
+        <v>109.4393080085026</v>
       </c>
       <c r="C599">
         <v>14420.23</v>
@@ -5701,7 +5701,7 @@
         <v>40057</v>
       </c>
       <c r="B600">
-        <v>119.6230030403589</v>
+        <v>119.8341153649106</v>
       </c>
       <c r="C600">
         <v>13766.26</v>
@@ -5715,7 +5715,7 @@
         <v>40087</v>
       </c>
       <c r="B601">
-        <v>98.08124681223606</v>
+        <v>98.21574209666818</v>
       </c>
       <c r="C601">
         <v>19294.3</v>
@@ -5729,7 +5729,7 @@
         <v>40118</v>
       </c>
       <c r="B602">
-        <v>109.3748415485837</v>
+        <v>109.5113423276896</v>
       </c>
       <c r="C602">
         <v>20780.36</v>
@@ -5743,7 +5743,7 @@
         <v>40148</v>
       </c>
       <c r="B603">
-        <v>105.7067494303369</v>
+        <v>105.8216448535447</v>
       </c>
       <c r="C603">
         <v>19363.22</v>
@@ -5757,7 +5757,7 @@
         <v>40179</v>
       </c>
       <c r="B604">
-        <v>120.6832925792413</v>
+        <v>120.8221375552374</v>
       </c>
       <c r="C604">
         <v>23146.06</v>
@@ -5771,7 +5771,7 @@
         <v>40210</v>
       </c>
       <c r="B605">
-        <v>120.5001794832185</v>
+        <v>120.6237408870844</v>
       </c>
       <c r="C605">
         <v>29661.91</v>
@@ -5785,7 +5785,7 @@
         <v>40238</v>
       </c>
       <c r="B606">
-        <v>121.4842965003669</v>
+        <v>121.6519997005863</v>
       </c>
       <c r="C606">
         <v>19562.9</v>
@@ -5799,7 +5799,7 @@
         <v>40269</v>
       </c>
       <c r="B607">
-        <v>109.3133013264814</v>
+        <v>109.4240408827375</v>
       </c>
       <c r="C607">
         <v>23612.76</v>
@@ -5813,7 +5813,7 @@
         <v>40299</v>
       </c>
       <c r="B608">
-        <v>143.275729035161</v>
+        <v>143.4003044797819</v>
       </c>
       <c r="C608">
         <v>22580.16</v>
@@ -5827,7 +5827,7 @@
         <v>40330</v>
       </c>
       <c r="B609">
-        <v>142.0815533962391</v>
+        <v>142.2429074268007</v>
       </c>
       <c r="C609">
         <v>23196.64</v>
@@ -5841,7 +5841,7 @@
         <v>40360</v>
       </c>
       <c r="B610">
-        <v>146.9209713414436</v>
+        <v>147.0695338777873</v>
       </c>
       <c r="C610">
         <v>20535.61</v>
@@ -5855,7 +5855,7 @@
         <v>40391</v>
       </c>
       <c r="B611">
-        <v>121.9142822258456</v>
+        <v>122.0251591335703</v>
       </c>
       <c r="C611">
         <v>32177.13</v>
@@ -5869,7 +5869,7 @@
         <v>40422</v>
       </c>
       <c r="B612">
-        <v>127.4171863375786</v>
+        <v>127.5128548108033</v>
       </c>
       <c r="C612">
         <v>20655.87</v>
@@ -5883,7 +5883,7 @@
         <v>40452</v>
       </c>
       <c r="B613">
-        <v>123.4111746373698</v>
+        <v>123.5252435365387</v>
       </c>
       <c r="C613">
         <v>27171.7</v>
@@ -5897,7 +5897,7 @@
         <v>40483</v>
       </c>
       <c r="B614">
-        <v>127.7106064877101</v>
+        <v>127.8192903329097</v>
       </c>
       <c r="C614">
         <v>13966.62</v>
@@ -5911,7 +5911,7 @@
         <v>40513</v>
       </c>
       <c r="B615">
-        <v>139.8851147927135</v>
+        <v>140.0316549127836</v>
       </c>
       <c r="C615">
         <v>14303.45</v>
@@ -5925,7 +5925,7 @@
         <v>40544</v>
       </c>
       <c r="B616">
-        <v>124.4622311919417</v>
+        <v>124.6527272398392</v>
       </c>
       <c r="C616">
         <v>15449.49</v>
@@ -5939,7 +5939,7 @@
         <v>40575</v>
       </c>
       <c r="B617">
-        <v>97.60907441428736</v>
+        <v>97.68156942116386</v>
       </c>
       <c r="C617">
         <v>14260.61</v>
@@ -5953,7 +5953,7 @@
         <v>40603</v>
       </c>
       <c r="B618">
-        <v>132.0742589870941</v>
+        <v>132.2226395732113</v>
       </c>
       <c r="C618">
         <v>12549.44</v>
@@ -5967,7 +5967,7 @@
         <v>40634</v>
       </c>
       <c r="B619">
-        <v>124.3235338329732</v>
+        <v>124.4896096711237</v>
       </c>
       <c r="C619">
         <v>10858.82</v>
@@ -5981,7 +5981,7 @@
         <v>40664</v>
       </c>
       <c r="B620">
-        <v>94.72883744682505</v>
+        <v>94.81990221929456</v>
       </c>
       <c r="C620">
         <v>14147.12</v>
@@ -5995,7 +5995,7 @@
         <v>40695</v>
       </c>
       <c r="B621">
-        <v>124.3364118557164</v>
+        <v>124.4625296308099</v>
       </c>
       <c r="C621">
         <v>12621</v>
@@ -6009,7 +6009,7 @@
         <v>40725</v>
       </c>
       <c r="B622">
-        <v>151.2710689534927</v>
+        <v>151.3937268147959</v>
       </c>
       <c r="C622">
         <v>16853.56</v>
@@ -6023,7 +6023,7 @@
         <v>40756</v>
       </c>
       <c r="B623">
-        <v>215.6907848079821</v>
+        <v>215.8631167738925</v>
       </c>
       <c r="C623">
         <v>15732.06</v>
@@ -6037,7 +6037,7 @@
         <v>40787</v>
       </c>
       <c r="B624">
-        <v>194.6959568517232</v>
+        <v>194.8710531523376</v>
       </c>
       <c r="C624">
         <v>18687.09</v>
@@ -6051,7 +6051,7 @@
         <v>40817</v>
       </c>
       <c r="B625">
-        <v>173.3647525582189</v>
+        <v>173.5585385561833</v>
       </c>
       <c r="C625">
         <v>22334.08</v>
@@ -6065,7 +6065,7 @@
         <v>40848</v>
       </c>
       <c r="B626">
-        <v>195.3614609151723</v>
+        <v>195.5603140453931</v>
       </c>
       <c r="C626">
         <v>18310.76</v>
@@ -6079,7 +6079,7 @@
         <v>40878</v>
       </c>
       <c r="B627">
-        <v>186.4077038194364</v>
+        <v>186.603820471264</v>
       </c>
       <c r="C627">
         <v>17926.63</v>
@@ -6093,7 +6093,7 @@
         <v>40909</v>
       </c>
       <c r="B628">
-        <v>158.5157590445268</v>
+        <v>158.6706051409631</v>
       </c>
       <c r="C628">
         <v>18402.08</v>
@@ -6107,7 +6107,7 @@
         <v>40940</v>
       </c>
       <c r="B629">
-        <v>148.374160568207</v>
+        <v>148.5530884531795</v>
       </c>
       <c r="C629">
         <v>18511.58</v>
@@ -6121,7 +6121,7 @@
         <v>40969</v>
       </c>
       <c r="B630">
-        <v>146.903459682541</v>
+        <v>147.0793193613002</v>
       </c>
       <c r="C630">
         <v>18355.28</v>
@@ -6135,7 +6135,7 @@
         <v>41000</v>
       </c>
       <c r="B631">
-        <v>136.5372240879313</v>
+        <v>136.699620704505</v>
       </c>
       <c r="C631">
         <v>15813.25</v>
@@ -6149,7 +6149,7 @@
         <v>41030</v>
       </c>
       <c r="B632">
-        <v>165.6088549374678</v>
+        <v>165.780031041318</v>
       </c>
       <c r="C632">
         <v>14609.73</v>
@@ -6163,7 +6163,7 @@
         <v>41061</v>
       </c>
       <c r="B633">
-        <v>188.3483883078947</v>
+        <v>188.5271270443731</v>
       </c>
       <c r="C633">
         <v>36236.57</v>
@@ -6177,7 +6177,7 @@
         <v>41091</v>
       </c>
       <c r="B634">
-        <v>153.0254723297647</v>
+        <v>153.1802605620028</v>
       </c>
       <c r="C634">
         <v>33079.34</v>
@@ -6191,7 +6191,7 @@
         <v>41122</v>
       </c>
       <c r="B635">
-        <v>118.6556210585757</v>
+        <v>118.7568783502385</v>
       </c>
       <c r="C635">
         <v>35269.25</v>
@@ -6205,7 +6205,7 @@
         <v>41153</v>
       </c>
       <c r="B636">
-        <v>156.1375351831097</v>
+        <v>156.2924182462142</v>
       </c>
       <c r="C636">
         <v>24828.08</v>
@@ -6219,7 +6219,7 @@
         <v>41183</v>
       </c>
       <c r="B637">
-        <v>151.6872857495252</v>
+        <v>151.8327028390947</v>
       </c>
       <c r="C637">
         <v>20310.6</v>
@@ -6233,7 +6233,7 @@
         <v>41214</v>
       </c>
       <c r="B638">
-        <v>161.0703212750844</v>
+        <v>161.2275928187646</v>
       </c>
       <c r="C638">
         <v>30968.85</v>
@@ -6247,7 +6247,7 @@
         <v>41244</v>
       </c>
       <c r="B639">
-        <v>170.0831506396141</v>
+        <v>170.265823998872</v>
       </c>
       <c r="C639">
         <v>39555.1</v>
@@ -6261,7 +6261,7 @@
         <v>41275</v>
       </c>
       <c r="B640">
-        <v>165.9964059980464</v>
+        <v>166.1675638404668</v>
       </c>
       <c r="C640">
         <v>30948.78</v>
@@ -6275,7 +6275,7 @@
         <v>41306</v>
       </c>
       <c r="B641">
-        <v>123.439959189748</v>
+        <v>123.5508051586799</v>
       </c>
       <c r="C641">
         <v>20086.67</v>
@@ -6289,7 +6289,7 @@
         <v>41334</v>
       </c>
       <c r="B642">
-        <v>145.2909752034043</v>
+        <v>145.4100117288481</v>
       </c>
       <c r="C642">
         <v>31259.48</v>
@@ -6303,7 +6303,7 @@
         <v>41365</v>
       </c>
       <c r="B643">
-        <v>139.8455096755501</v>
+        <v>140.0028930308006</v>
       </c>
       <c r="C643">
         <v>20386.52</v>
@@ -6317,7 +6317,7 @@
         <v>41395</v>
       </c>
       <c r="B644">
-        <v>108.4748599345831</v>
+        <v>108.5689123744349</v>
       </c>
       <c r="C644">
         <v>14386.56</v>
@@ -6331,7 +6331,7 @@
         <v>41426</v>
       </c>
       <c r="B645">
-        <v>130.3628576954784</v>
+        <v>130.4979296106069</v>
       </c>
       <c r="C645">
         <v>13789.65</v>
@@ -6345,7 +6345,7 @@
         <v>41456</v>
       </c>
       <c r="B646">
-        <v>108.6329876377047</v>
+        <v>108.733239453248</v>
       </c>
       <c r="C646">
         <v>15417.21</v>
@@ -6359,7 +6359,7 @@
         <v>41487</v>
       </c>
       <c r="B647">
-        <v>127.5315953585069</v>
+        <v>127.6643026763873</v>
       </c>
       <c r="C647">
         <v>14158.71</v>
@@ -6373,7 +6373,7 @@
         <v>41518</v>
       </c>
       <c r="B648">
-        <v>141.5032166762949</v>
+        <v>141.6359499755157</v>
       </c>
       <c r="C648">
         <v>15448.87</v>
@@ -6387,7 +6387,7 @@
         <v>41548</v>
       </c>
       <c r="B649">
-        <v>167.4577111007315</v>
+        <v>167.6591144573588</v>
       </c>
       <c r="C649">
         <v>21717.67</v>
@@ -6401,7 +6401,7 @@
         <v>41579</v>
       </c>
       <c r="B650">
-        <v>108.1519240515667</v>
+        <v>108.3106550828385</v>
       </c>
       <c r="C650">
         <v>12641.28</v>
@@ -6415,7 +6415,7 @@
         <v>41609</v>
       </c>
       <c r="B651">
-        <v>128.310470434717</v>
+        <v>128.4737624764945</v>
       </c>
       <c r="C651">
         <v>17539.43</v>
@@ -6429,7 +6429,7 @@
         <v>41640</v>
       </c>
       <c r="B652">
-        <v>119.7538198882918</v>
+        <v>119.892451683436</v>
       </c>
       <c r="C652">
         <v>21842.74</v>
@@ -6443,7 +6443,7 @@
         <v>41671</v>
       </c>
       <c r="B653">
-        <v>100.9456042423108</v>
+        <v>101.0401489747724</v>
       </c>
       <c r="C653">
         <v>21788.17</v>
@@ -6457,7 +6457,7 @@
         <v>41699</v>
       </c>
       <c r="B654">
-        <v>114.6506400943257</v>
+        <v>114.7845236699494</v>
       </c>
       <c r="C654">
         <v>19225.85</v>
@@ -6471,7 +6471,7 @@
         <v>41730</v>
       </c>
       <c r="B655">
-        <v>118.5220146820977</v>
+        <v>118.6954967387737</v>
       </c>
       <c r="C655">
         <v>13590.26</v>
@@ -6485,7 +6485,7 @@
         <v>41760</v>
       </c>
       <c r="B656">
-        <v>111.0650071172092</v>
+        <v>111.1686931616511</v>
       </c>
       <c r="C656">
         <v>17282.29</v>
@@ -6499,7 +6499,7 @@
         <v>41791</v>
       </c>
       <c r="B657">
-        <v>96.51738334775199</v>
+        <v>96.65906523050651</v>
       </c>
       <c r="C657">
         <v>19739.77</v>
@@ -6513,7 +6513,7 @@
         <v>41821</v>
       </c>
       <c r="B658">
-        <v>99.94650408854484</v>
+        <v>100.073175695144</v>
       </c>
       <c r="C658">
         <v>20342.31</v>
@@ -6527,7 +6527,7 @@
         <v>41852</v>
       </c>
       <c r="B659">
-        <v>105.1431681781496</v>
+        <v>105.2470776390631</v>
       </c>
       <c r="C659">
         <v>13934.56</v>
@@ -6541,7 +6541,7 @@
         <v>41883</v>
       </c>
       <c r="B660">
-        <v>128.6500099226577</v>
+        <v>128.7945163781695</v>
       </c>
       <c r="C660">
         <v>14067.97</v>
@@ -6555,7 +6555,7 @@
         <v>41913</v>
       </c>
       <c r="B661">
-        <v>114.7456557088522</v>
+        <v>114.8793428905325</v>
       </c>
       <c r="C661">
         <v>14332.98</v>
@@ -6569,7 +6569,7 @@
         <v>41944</v>
       </c>
       <c r="B662">
-        <v>128.6080595669804</v>
+        <v>128.7689480297002</v>
       </c>
       <c r="C662">
         <v>25064.32</v>
@@ -6583,7 +6583,7 @@
         <v>41974</v>
       </c>
       <c r="B663">
-        <v>113.9373971650104</v>
+        <v>114.0162687994992</v>
       </c>
       <c r="C663">
         <v>17021.78</v>
@@ -6597,7 +6597,7 @@
         <v>42005</v>
       </c>
       <c r="B664">
-        <v>135.1771603649389</v>
+        <v>135.3098201958523</v>
       </c>
       <c r="C664">
         <v>25443.97</v>
@@ -6611,7 +6611,7 @@
         <v>42036</v>
       </c>
       <c r="B665">
-        <v>122.7378516914768</v>
+        <v>122.8665979679264</v>
       </c>
       <c r="C665">
         <v>29456.69</v>
@@ -6625,7 +6625,7 @@
         <v>42064</v>
       </c>
       <c r="B666">
-        <v>117.9176179813466</v>
+        <v>118.0749727036708</v>
       </c>
       <c r="C666">
         <v>29700.53</v>
@@ -6639,7 +6639,7 @@
         <v>42095</v>
       </c>
       <c r="B667">
-        <v>100.8433658402262</v>
+        <v>100.929883261628</v>
       </c>
       <c r="C667">
         <v>22530.23</v>
@@ -6653,7 +6653,7 @@
         <v>42125</v>
       </c>
       <c r="B668">
-        <v>101.5193429796456</v>
+        <v>101.6116917821393</v>
       </c>
       <c r="C668">
         <v>21803.69</v>
@@ -6667,7 +6667,7 @@
         <v>42156</v>
       </c>
       <c r="B669">
-        <v>118.7530725634764</v>
+        <v>118.8823586677045</v>
       </c>
       <c r="C669">
         <v>25042.18</v>
@@ -6681,7 +6681,7 @@
         <v>42186</v>
       </c>
       <c r="B670">
-        <v>122.9862860317201</v>
+        <v>123.167139606705</v>
       </c>
       <c r="C670">
         <v>26689.86</v>
@@ -6695,7 +6695,7 @@
         <v>42217</v>
       </c>
       <c r="B671">
-        <v>117.2071917885623</v>
+        <v>117.2886513595701</v>
       </c>
       <c r="C671">
         <v>22015.01</v>
@@ -6709,7 +6709,7 @@
         <v>42248</v>
       </c>
       <c r="B672">
-        <v>153.8674762333925</v>
+        <v>153.9980135225141</v>
       </c>
       <c r="C672">
         <v>20895.17</v>
@@ -6723,7 +6723,7 @@
         <v>42278</v>
       </c>
       <c r="B673">
-        <v>115.4236527406059</v>
+        <v>115.5419217619356</v>
       </c>
       <c r="C673">
         <v>25572.94</v>
@@ -6737,7 +6737,7 @@
         <v>42309</v>
       </c>
       <c r="B674">
-        <v>106.0877554600118</v>
+        <v>106.217832773303</v>
       </c>
       <c r="C674">
         <v>21316.99</v>
@@ -6751,7 +6751,7 @@
         <v>42339</v>
       </c>
       <c r="B675">
-        <v>116.9507555175347</v>
+        <v>117.0787378122828</v>
       </c>
       <c r="C675">
         <v>16845.93</v>
@@ -6765,7 +6765,7 @@
         <v>42370</v>
       </c>
       <c r="B676">
-        <v>141.0168003856225</v>
+        <v>141.1904709520688</v>
       </c>
       <c r="C676">
         <v>18498.77</v>
@@ -6779,7 +6779,7 @@
         <v>42401</v>
       </c>
       <c r="B677">
-        <v>145.8078140508598</v>
+        <v>145.9550791088167</v>
       </c>
       <c r="C677">
         <v>20446.37</v>
@@ -6793,7 +6793,7 @@
         <v>42430</v>
       </c>
       <c r="B678">
-        <v>162.3910166409273</v>
+        <v>162.6024656915891</v>
       </c>
       <c r="C678">
         <v>22191.53</v>
@@ -6807,7 +6807,7 @@
         <v>42461</v>
       </c>
       <c r="B679">
-        <v>146.4469297566512</v>
+        <v>146.6718839837212</v>
       </c>
       <c r="C679">
         <v>15032.11</v>
@@ -6821,7 +6821,7 @@
         <v>42491</v>
       </c>
       <c r="B680">
-        <v>123.8090023597251</v>
+        <v>123.9689383522726</v>
       </c>
       <c r="C680">
         <v>21466.45</v>
@@ -6835,7 +6835,7 @@
         <v>42522</v>
       </c>
       <c r="B681">
-        <v>220.9011973956959</v>
+        <v>221.0801629101615</v>
       </c>
       <c r="C681">
         <v>17423.54</v>
@@ -6849,7 +6849,7 @@
         <v>42552</v>
       </c>
       <c r="B682">
-        <v>189.0666232119036</v>
+        <v>189.2196495242323</v>
       </c>
       <c r="C682">
         <v>45973.39</v>
@@ -6863,7 +6863,7 @@
         <v>42583</v>
       </c>
       <c r="B683">
-        <v>136.5567453861132</v>
+        <v>136.7152867039044</v>
       </c>
       <c r="C683">
         <v>44083.75</v>
@@ -6877,7 +6877,7 @@
         <v>42614</v>
       </c>
       <c r="B684">
-        <v>139.2049211818659</v>
+        <v>139.406087995387</v>
       </c>
       <c r="C684">
         <v>28374.06</v>
@@ -6891,7 +6891,7 @@
         <v>42644</v>
       </c>
       <c r="B685">
-        <v>122.4424806979685</v>
+        <v>122.5881593609823</v>
       </c>
       <c r="C685">
         <v>18582.51</v>
@@ -6905,7 +6905,7 @@
         <v>42675</v>
       </c>
       <c r="B686">
-        <v>215.2387763793166</v>
+        <v>215.4203519048661</v>
       </c>
       <c r="C686">
         <v>26743.54</v>
@@ -6919,7 +6919,7 @@
         <v>42705</v>
       </c>
       <c r="B687">
-        <v>186.8106113706972</v>
+        <v>186.9887081276159</v>
       </c>
       <c r="C687">
         <v>30556.11</v>
@@ -6933,7 +6933,7 @@
         <v>42736</v>
       </c>
       <c r="B688">
-        <v>255.5100494285929</v>
+        <v>255.9307409329231</v>
       </c>
       <c r="C688">
         <v>38065.04</v>
@@ -6947,7 +6947,7 @@
         <v>42767</v>
       </c>
       <c r="B689">
-        <v>189.8065487433733</v>
+        <v>190.0485762081897</v>
       </c>
       <c r="C689">
         <v>34721.72</v>
@@ -6961,7 +6961,7 @@
         <v>42795</v>
       </c>
       <c r="B690">
-        <v>250.3446963339073</v>
+        <v>250.8238032924824</v>
       </c>
       <c r="C690">
         <v>28585.07</v>
@@ -6975,7 +6975,7 @@
         <v>42826</v>
       </c>
       <c r="B691">
-        <v>177.9198220675771</v>
+        <v>178.1587166421914</v>
       </c>
       <c r="C691">
         <v>22038.28</v>
@@ -6989,7 +6989,7 @@
         <v>42856</v>
       </c>
       <c r="B692">
-        <v>142.7687887921635</v>
+        <v>142.9479770084823</v>
       </c>
       <c r="C692">
         <v>20300.89</v>
@@ -7003,7 +7003,7 @@
         <v>42887</v>
       </c>
       <c r="B693">
-        <v>175.6724110677694</v>
+        <v>175.9848780563877</v>
       </c>
       <c r="C693">
         <v>15384.21</v>
@@ -7017,7 +7017,7 @@
         <v>42917</v>
       </c>
       <c r="B694">
-        <v>172.4458646142616</v>
+        <v>172.7591751725655</v>
       </c>
       <c r="C694">
         <v>16915.2</v>
@@ -7031,7 +7031,7 @@
         <v>42948</v>
       </c>
       <c r="B695">
-        <v>141.8866804636533</v>
+        <v>142.1128545354746</v>
       </c>
       <c r="C695">
         <v>21567.95</v>
@@ -7045,7 +7045,7 @@
         <v>42979</v>
       </c>
       <c r="B696">
-        <v>163.5985896742135</v>
+        <v>163.8820779579743</v>
       </c>
       <c r="C696">
         <v>15468.96</v>
@@ -7059,7 +7059,7 @@
         <v>43009</v>
       </c>
       <c r="B697">
-        <v>149.9161750754167</v>
+        <v>150.1122744008245</v>
       </c>
       <c r="C697">
         <v>20376.24</v>
@@ -7073,7 +7073,7 @@
         <v>43040</v>
       </c>
       <c r="B698">
-        <v>168.1591772257453</v>
+        <v>168.4426853655091</v>
       </c>
       <c r="C698">
         <v>20821.27</v>
@@ -7087,7 +7087,7 @@
         <v>43070</v>
       </c>
       <c r="B699">
-        <v>155.6681030797795</v>
+        <v>155.8984480690011</v>
       </c>
       <c r="C699">
         <v>27945.3</v>
@@ -7101,7 +7101,7 @@
         <v>43101</v>
       </c>
       <c r="B700">
-        <v>180.2844515066332</v>
+        <v>180.658729538629</v>
       </c>
       <c r="C700">
         <v>21420.12</v>
@@ -7115,7 +7115,7 @@
         <v>43132</v>
       </c>
       <c r="B701">
-        <v>130.8782900577072</v>
+        <v>131.0892099172494</v>
       </c>
       <c r="C701">
         <v>17493.08</v>
@@ -7129,7 +7129,7 @@
         <v>43160</v>
       </c>
       <c r="B702">
-        <v>181.638700854879</v>
+        <v>181.997277959306</v>
       </c>
       <c r="C702">
         <v>12197.86</v>
@@ -7143,7 +7143,7 @@
         <v>43191</v>
       </c>
       <c r="B703">
-        <v>173.6540012662262</v>
+        <v>173.9947432526082</v>
       </c>
       <c r="C703">
         <v>12920.08</v>
@@ -7157,7 +7157,7 @@
         <v>43221</v>
       </c>
       <c r="B704">
-        <v>172.6817242143045</v>
+        <v>172.9787164202766</v>
       </c>
       <c r="C704">
         <v>19883.07</v>
@@ -7171,7 +7171,7 @@
         <v>43252</v>
       </c>
       <c r="B705">
-        <v>163.6462963473224</v>
+        <v>163.9326591117224</v>
       </c>
       <c r="C705">
         <v>25859.36</v>
@@ -7185,7 +7185,7 @@
         <v>43282</v>
       </c>
       <c r="B706">
-        <v>238.739934918368</v>
+        <v>239.2982397851821</v>
       </c>
       <c r="C706">
         <v>22117.7</v>
@@ -7199,7 +7199,7 @@
         <v>43313</v>
       </c>
       <c r="B707">
-        <v>182.3126761231703</v>
+        <v>182.693165848459</v>
       </c>
       <c r="C707">
         <v>30926.84</v>
@@ -7213,7 +7213,7 @@
         <v>43344</v>
       </c>
       <c r="B708">
-        <v>205.9418993446218</v>
+        <v>206.3856120951636</v>
       </c>
       <c r="C708">
         <v>27915.26</v>
@@ -7227,7 +7227,7 @@
         <v>43374</v>
       </c>
       <c r="B709">
-        <v>226.0635595477576</v>
+        <v>226.54948126494</v>
       </c>
       <c r="C709">
         <v>22779.45</v>
@@ -7241,7 +7241,7 @@
         <v>43405</v>
       </c>
       <c r="B710">
-        <v>265.4982650310577</v>
+        <v>266.1191756408321</v>
       </c>
       <c r="C710">
         <v>18793.39</v>
@@ -7255,7 +7255,7 @@
         <v>43435</v>
       </c>
       <c r="B711">
-        <v>218.4257367252193</v>
+        <v>218.7769090018232</v>
       </c>
       <c r="C711">
         <v>26231.1</v>
@@ -7269,7 +7269,7 @@
         <v>43466</v>
       </c>
       <c r="B712">
-        <v>243.8024859897635</v>
+        <v>244.2214635767608</v>
       </c>
       <c r="C712">
         <v>36382.28</v>
@@ -7283,7 +7283,7 @@
         <v>43497</v>
       </c>
       <c r="B713">
-        <v>177.94327321086</v>
+        <v>178.2899325716794</v>
       </c>
       <c r="C713">
         <v>51178.63</v>
@@ -7297,7 +7297,7 @@
         <v>43525</v>
       </c>
       <c r="B714">
-        <v>251.986220996224</v>
+        <v>252.5826209283937</v>
       </c>
       <c r="C714">
         <v>35809.01</v>
@@ -7311,7 +7311,7 @@
         <v>43556</v>
       </c>
       <c r="B715">
-        <v>205.0180191149946</v>
+        <v>205.4807447521729</v>
       </c>
       <c r="C715">
         <v>27627.57</v>
@@ -7325,7 +7325,7 @@
         <v>43586</v>
       </c>
       <c r="B716">
-        <v>238.3807214281135</v>
+        <v>238.9102125903181</v>
       </c>
       <c r="C716">
         <v>57517.98</v>
@@ -7339,7 +7339,7 @@
         <v>43617</v>
       </c>
       <c r="B717">
-        <v>350.2308830017263</v>
+        <v>351.1708384074168</v>
       </c>
       <c r="C717">
         <v>41085.63</v>
@@ -7353,7 +7353,7 @@
         <v>43647</v>
       </c>
       <c r="B718">
-        <v>259.9741197004991</v>
+        <v>260.5201211260178</v>
       </c>
       <c r="C718">
         <v>22822.22</v>
@@ -7367,7 +7367,7 @@
         <v>43678</v>
       </c>
       <c r="B719">
-        <v>293.3206114570096</v>
+        <v>293.8965768618484</v>
       </c>
       <c r="C719">
         <v>33126.3</v>
@@ -7381,7 +7381,7 @@
         <v>43709</v>
       </c>
       <c r="B720">
-        <v>250.6110680347673</v>
+        <v>251.1160926319757</v>
       </c>
       <c r="C720">
         <v>32220.86</v>
@@ -7395,7 +7395,7 @@
         <v>43739</v>
       </c>
       <c r="B721">
-        <v>209.0291485427257</v>
+        <v>209.3719427163467</v>
       </c>
       <c r="C721">
         <v>39475.35</v>
@@ -7409,7 +7409,7 @@
         <v>43770</v>
       </c>
       <c r="B722">
-        <v>259.4912238983889</v>
+        <v>260.0705860041973</v>
       </c>
       <c r="C722">
         <v>39040.36</v>
@@ -7423,7 +7423,7 @@
         <v>43800</v>
       </c>
       <c r="B723">
-        <v>244.7206967161762</v>
+        <v>245.2120936384618</v>
       </c>
       <c r="C723">
         <v>52683.16</v>
@@ -7437,7 +7437,7 @@
         <v>43831</v>
       </c>
       <c r="B724">
-        <v>199.5056678598146</v>
+        <v>199.8889612320059</v>
       </c>
       <c r="C724">
         <v>42258.74</v>
@@ -7451,7 +7451,7 @@
         <v>43862</v>
       </c>
       <c r="B725">
-        <v>198.1615212936142</v>
+        <v>198.4574359810781</v>
       </c>
       <c r="C725">
         <v>39762.47</v>
@@ -7465,7 +7465,7 @@
         <v>43891</v>
       </c>
       <c r="B726">
-        <v>311.6427468254961</v>
+        <v>311.9758385074605</v>
       </c>
       <c r="C726">
         <v>56223.62</v>
@@ -7479,7 +7479,7 @@
         <v>43922</v>
       </c>
       <c r="B727">
-        <v>335.0807987281287</v>
+        <v>335.576589880221</v>
       </c>
       <c r="C727">
         <v>21438.99</v>
@@ -7493,7 +7493,7 @@
         <v>43952</v>
       </c>
       <c r="B728">
-        <v>424.2603487784621</v>
+        <v>425.0232118983376</v>
       </c>
       <c r="C728">
         <v>26490.73</v>
@@ -7507,7 +7507,7 @@
         <v>43983</v>
       </c>
       <c r="B729">
-        <v>325.2644271983714</v>
+        <v>325.9055634815653</v>
       </c>
       <c r="C729">
         <v>28737.92</v>
@@ -7521,7 +7521,7 @@
         <v>44013</v>
       </c>
       <c r="B730">
-        <v>308.8091152478705</v>
+        <v>309.3038143411002</v>
       </c>
       <c r="C730">
         <v>26888.29</v>
@@ -7535,7 +7535,7 @@
         <v>44044</v>
       </c>
       <c r="B731">
-        <v>304.575175254195</v>
+        <v>305.2678130347502</v>
       </c>
       <c r="C731">
         <v>20430.03</v>
@@ -7549,7 +7549,7 @@
         <v>44075</v>
       </c>
       <c r="B732">
-        <v>328.1502705800482</v>
+        <v>328.9058660150179</v>
       </c>
       <c r="C732">
         <v>26409.8</v>
@@ -7563,7 +7563,7 @@
         <v>44105</v>
       </c>
       <c r="B733">
-        <v>313.3327396140153</v>
+        <v>313.9432334315234</v>
       </c>
       <c r="C733">
         <v>28194.52</v>
@@ -7577,7 +7577,7 @@
         <v>44136</v>
       </c>
       <c r="B734">
-        <v>421.8613280215853</v>
+        <v>422.878764847364</v>
       </c>
       <c r="C734">
         <v>25062.17</v>
@@ -7591,7 +7591,7 @@
         <v>44166</v>
       </c>
       <c r="B735">
-        <v>315.2522255663239</v>
+        <v>315.9257692684623</v>
       </c>
       <c r="C735">
         <v>14886.35</v>
@@ -7605,7 +7605,7 @@
         <v>44197</v>
       </c>
       <c r="B736">
-        <v>283.4355501549978</v>
+        <v>284.023490862621</v>
       </c>
       <c r="C736">
         <v>11956.53</v>
@@ -7619,7 +7619,7 @@
         <v>44228</v>
       </c>
       <c r="B737">
-        <v>200.2478114641451</v>
+        <v>200.6125493669494</v>
       </c>
       <c r="C737">
         <v>9050.271000000001</v>
@@ -7633,7 +7633,7 @@
         <v>44256</v>
       </c>
       <c r="B738">
-        <v>221.6317771193362</v>
+        <v>222.0983122796519</v>
       </c>
       <c r="C738">
         <v>13602.12</v>
@@ -7647,7 +7647,7 @@
         <v>44287</v>
       </c>
       <c r="B739">
-        <v>206.5810678094904</v>
+        <v>207.0239541429045</v>
       </c>
       <c r="C739">
         <v>14889.97</v>
@@ -7661,7 +7661,7 @@
         <v>44317</v>
       </c>
       <c r="B740">
-        <v>179.9670211525667</v>
+        <v>180.3003668438903</v>
       </c>
       <c r="C740">
         <v>15392.93</v>
@@ -7675,7 +7675,7 @@
         <v>44348</v>
       </c>
       <c r="B741">
-        <v>181.3020096490278</v>
+        <v>181.639061906586</v>
       </c>
       <c r="C741">
         <v>21543.41</v>
@@ -7689,7 +7689,7 @@
         <v>44378</v>
       </c>
       <c r="B742">
-        <v>190.7335152842316</v>
+        <v>191.0856113273062</v>
       </c>
       <c r="C742">
         <v>19371.39</v>
@@ -7703,7 +7703,7 @@
         <v>44409</v>
       </c>
       <c r="B743">
-        <v>210.3200427154354</v>
+        <v>210.7892699137883</v>
       </c>
       <c r="C743">
         <v>17169.7</v>
@@ -7717,7 +7717,7 @@
         <v>44440</v>
       </c>
       <c r="B744">
-        <v>220.1285189007347</v>
+        <v>220.5535740355701</v>
       </c>
       <c r="C744">
         <v>23904</v>
@@ -7731,7 +7731,7 @@
         <v>44470</v>
       </c>
       <c r="B745">
-        <v>195.6532883440151</v>
+        <v>196.0467364909717</v>
       </c>
       <c r="C745">
         <v>10477.78</v>
@@ -7745,7 +7745,7 @@
         <v>44501</v>
       </c>
       <c r="B746">
-        <v>235.0302014765577</v>
+        <v>235.5484715965082</v>
       </c>
       <c r="C746">
         <v>14556.52</v>
@@ -7759,7 +7759,7 @@
         <v>44531</v>
       </c>
       <c r="B747">
-        <v>267.9229771818789</v>
+        <v>268.4616988956613</v>
       </c>
       <c r="C747">
         <v>28225.75</v>
@@ -7773,7 +7773,7 @@
         <v>44562</v>
       </c>
       <c r="B748">
-        <v>233.9620671705152</v>
+        <v>234.4592535592012</v>
       </c>
       <c r="C748">
         <v>25576.78</v>
@@ -7787,7 +7787,7 @@
         <v>44593</v>
       </c>
       <c r="B749">
-        <v>186.568678768579</v>
+        <v>186.8265155168883</v>
       </c>
       <c r="C749">
         <v>25212.72</v>
@@ -7801,7 +7801,7 @@
         <v>44621</v>
       </c>
       <c r="B750">
-        <v>306.0470879959728</v>
+        <v>306.5956849936787</v>
       </c>
       <c r="C750">
         <v>27256.75</v>
@@ -7815,7 +7815,7 @@
         <v>44652</v>
       </c>
       <c r="B751">
-        <v>288.4587322649264</v>
+        <v>288.9671095776354</v>
       </c>
       <c r="C751">
         <v>41669.1</v>
@@ -7829,7 +7829,7 @@
         <v>44682</v>
       </c>
       <c r="B752">
-        <v>290.9634481101851</v>
+        <v>291.5508821770336</v>
       </c>
       <c r="C752">
         <v>25064.35</v>
@@ -7843,7 +7843,7 @@
         <v>44713</v>
       </c>
       <c r="B753">
-        <v>265.739759703214</v>
+        <v>266.2320802190257</v>
       </c>
       <c r="C753">
         <v>23022.65</v>
@@ -7857,7 +7857,7 @@
         <v>44743</v>
       </c>
       <c r="B754">
-        <v>305.9329306061541</v>
+        <v>306.4909894804255</v>
       </c>
       <c r="C754">
         <v>19588.13</v>
@@ -7871,7 +7871,7 @@
         <v>44774</v>
       </c>
       <c r="B755">
-        <v>242.1303504951733</v>
+        <v>242.563560941931</v>
       </c>
       <c r="C755">
         <v>31577.91</v>
@@ -7885,7 +7885,7 @@
         <v>44805</v>
       </c>
       <c r="B756">
-        <v>254.3714047755861</v>
+        <v>254.7496900239954</v>
       </c>
       <c r="C756">
         <v>22559.72</v>
@@ -7899,7 +7899,7 @@
         <v>44835</v>
       </c>
       <c r="B757">
-        <v>269.5370102297978</v>
+        <v>269.9497378152338</v>
       </c>
       <c r="C757">
         <v>28962.72</v>
@@ -7913,7 +7913,7 @@
         <v>44866</v>
       </c>
       <c r="B758">
-        <v>327.5913978896877</v>
+        <v>328.2976158611773</v>
       </c>
       <c r="C758">
         <v>34628.48</v>
@@ -7927,7 +7927,7 @@
         <v>44896</v>
       </c>
       <c r="B759">
-        <v>256.2219491488248</v>
+        <v>256.7122095015598</v>
       </c>
       <c r="C759">
         <v>17405.95</v>
@@ -7941,7 +7941,7 @@
         <v>44927</v>
       </c>
       <c r="B760">
-        <v>229.5096668725043</v>
+        <v>229.9478413661854</v>
       </c>
       <c r="C760">
         <v>29339.84</v>
@@ -7955,7 +7955,7 @@
         <v>44958</v>
       </c>
       <c r="B761">
-        <v>263.6985779779534</v>
+        <v>264.2695590895259</v>
       </c>
       <c r="C761">
         <v>32027.81</v>
@@ -7969,7 +7969,7 @@
         <v>44986</v>
       </c>
       <c r="B762">
-        <v>340.1524081238038</v>
+        <v>340.9567395938898</v>
       </c>
       <c r="C762">
         <v>17736.47</v>
@@ -7983,7 +7983,7 @@
         <v>45017</v>
       </c>
       <c r="B763">
-        <v>284.6330027390407</v>
+        <v>285.2195103065358</v>
       </c>
       <c r="C763">
         <v>37638.8</v>
@@ -7997,7 +7997,7 @@
         <v>45047</v>
       </c>
       <c r="B764">
-        <v>214.1639835101327</v>
+        <v>214.4999115646287</v>
       </c>
       <c r="C764">
         <v>37309.42</v>
@@ -8011,7 +8011,7 @@
         <v>45078</v>
       </c>
       <c r="B765">
-        <v>238.5786392032969</v>
+        <v>239.0165934222418</v>
       </c>
       <c r="C765">
         <v>17679.01</v>
@@ -8025,7 +8025,7 @@
         <v>45108</v>
       </c>
       <c r="B766">
-        <v>203.3524691491816</v>
+        <v>203.7424290637706</v>
       </c>
       <c r="C766">
         <v>15649.48</v>
@@ -8039,7 +8039,7 @@
         <v>45139</v>
       </c>
       <c r="B767">
-        <v>188.6362229513092</v>
+        <v>189.0482174751642</v>
       </c>
       <c r="C767">
         <v>22258</v>
@@ -8053,7 +8053,7 @@
         <v>45170</v>
       </c>
       <c r="B768">
-        <v>213.466529030591</v>
+        <v>213.8582975090245</v>
       </c>
       <c r="C768">
         <v>16389.48</v>
@@ -8067,7 +8067,7 @@
         <v>45200</v>
       </c>
       <c r="B769">
-        <v>199.5842079104344</v>
+        <v>199.8491867911129</v>
       </c>
       <c r="C769">
         <v>15354.48</v>
@@ -8081,7 +8081,7 @@
         <v>45231</v>
       </c>
       <c r="B770">
-        <v>221.3427213251015</v>
+        <v>221.7164301914602</v>
       </c>
       <c r="C770">
         <v>17278.77</v>
@@ -8095,7 +8095,7 @@
         <v>45261</v>
       </c>
       <c r="B771">
-        <v>250.1822697256955</v>
+        <v>250.6849982388583</v>
       </c>
       <c r="C771">
         <v>17108.95</v>
@@ -8109,7 +8109,7 @@
         <v>45292</v>
       </c>
       <c r="B772">
-        <v>263.3542934176646</v>
+        <v>263.9307657199365</v>
       </c>
       <c r="C772">
         <v>17865.73</v>
@@ -8123,7 +8123,7 @@
         <v>45323</v>
       </c>
       <c r="B773">
-        <v>182.0628533443758</v>
+        <v>182.3339728773556</v>
       </c>
       <c r="C773">
         <v>16358.07</v>
@@ -8137,7 +8137,7 @@
         <v>45352</v>
       </c>
       <c r="B774">
-        <v>189.9759238771742</v>
+        <v>190.3504001283818</v>
       </c>
       <c r="C774">
         <v>17273.86</v>
@@ -8151,7 +8151,7 @@
         <v>45383</v>
       </c>
       <c r="B775">
-        <v>178.2169959090607</v>
+        <v>178.4600678900442</v>
       </c>
       <c r="C775">
         <v>16746.02</v>
@@ -8165,7 +8165,7 @@
         <v>45413</v>
       </c>
       <c r="B776">
-        <v>191.4851152481054</v>
+        <v>191.7909143576972</v>
       </c>
       <c r="C776">
         <v>15083.26</v>
@@ -8179,7 +8179,7 @@
         <v>45444</v>
       </c>
       <c r="B777">
-        <v>175.6365379379351</v>
+        <v>175.8151151947228</v>
       </c>
       <c r="C777">
         <v>14606.01</v>
@@ -8193,7 +8193,7 @@
         <v>45474</v>
       </c>
       <c r="B778">
-        <v>244.960343996371</v>
+        <v>245.4202814297943</v>
       </c>
       <c r="C778">
         <v>15929.92</v>
@@ -8207,7 +8207,7 @@
         <v>45505</v>
       </c>
       <c r="B779">
-        <v>202.1807387189281</v>
+        <v>202.5762713818185</v>
       </c>
       <c r="C779">
         <v>21425.35</v>
@@ -8221,7 +8221,7 @@
         <v>45536</v>
       </c>
       <c r="B780">
-        <v>211.6742003799142</v>
+        <v>212.0140658625617</v>
       </c>
       <c r="C780">
         <v>20372.42</v>
@@ -8235,7 +8235,7 @@
         <v>45566</v>
       </c>
       <c r="B781">
-        <v>215.4550666195515</v>
+        <v>215.8275729789033</v>
       </c>
       <c r="C781">
         <v>21669.22</v>
@@ -8249,7 +8249,7 @@
         <v>45597</v>
       </c>
       <c r="B782">
-        <v>282.1164052475826</v>
+        <v>282.5131666539344</v>
       </c>
       <c r="C782">
         <v>24333.03</v>
@@ -8263,7 +8263,7 @@
         <v>45627</v>
       </c>
       <c r="B783">
-        <v>336.8410505757261</v>
+        <v>337.5859169100238</v>
       </c>
       <c r="C783">
         <v>30375.61</v>
@@ -8277,7 +8277,7 @@
         <v>45658</v>
       </c>
       <c r="B784">
-        <v>309.8253883999113</v>
+        <v>310.5167715595696</v>
       </c>
       <c r="C784">
         <v>41383.23</v>
@@ -8291,7 +8291,7 @@
         <v>45689</v>
       </c>
       <c r="B785">
-        <v>319.9406981561854</v>
+        <v>320.8345110480037</v>
       </c>
       <c r="C785">
         <v>48816.02</v>
@@ -8305,7 +8305,7 @@
         <v>45717</v>
       </c>
       <c r="B786">
-        <v>458.7697145880418</v>
+        <v>460.0060886216664</v>
       </c>
       <c r="C786">
         <v>53189.5</v>
@@ -8319,7 +8319,7 @@
         <v>45748</v>
       </c>
       <c r="B787">
-        <v>585.0689625613861</v>
+        <v>586.1978822275637</v>
       </c>
       <c r="C787">
         <v>72733.48</v>
@@ -8333,7 +8333,7 @@
         <v>45778</v>
       </c>
       <c r="B788">
-        <v>487.7082325800611</v>
+        <v>486.333461737259</v>
       </c>
       <c r="C788">
         <v>77997.67999999999</v>
@@ -8347,7 +8347,7 @@
         <v>45809</v>
       </c>
       <c r="B789">
-        <v>357.87896040807</v>
+        <v>359.4442257999357</v>
       </c>
       <c r="C789">
         <v>84305.33</v>
@@ -8361,7 +8361,7 @@
         <v>45839</v>
       </c>
       <c r="B790">
-        <v>395.0715850419593</v>
+        <v>396.0146503954984</v>
       </c>
       <c r="C790">
         <v>95509.25999999999</v>
@@ -8375,7 +8375,7 @@
         <v>45870</v>
       </c>
       <c r="B791">
-        <v>312.8893413839743</v>
+        <v>326.8352886643954</v>
       </c>
       <c r="C791">
         <v>105558.3</v>
@@ -8388,8 +8388,25 @@
       <c r="A792" s="2">
         <v>45901</v>
       </c>
+      <c r="B792">
+        <v>291.0521904773695</v>
+      </c>
+      <c r="C792">
+        <v>122422.5</v>
+      </c>
       <c r="D792">
         <v>465.310904678215</v>
+      </c>
+    </row>
+    <row r="793" spans="1:4">
+      <c r="A793" s="2">
+        <v>45931</v>
+      </c>
+      <c r="C793">
+        <v>110331.9</v>
+      </c>
+      <c r="D793">
+        <v>426.213747796827</v>
       </c>
     </row>
   </sheetData>

--- a/00.data/01.incertezas/merged_uncertainty_indices.xlsx
+++ b/00.data/01.incertezas/merged_uncertainty_indices.xlsx
@@ -389,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D793"/>
+  <dimension ref="A1:D795"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -3969,7 +3969,7 @@
         <v>35431</v>
       </c>
       <c r="B448">
-        <v>78.57118072421564</v>
+        <v>78.95696233854623</v>
       </c>
       <c r="D448">
         <v>26.79430816055774</v>
@@ -3980,7 +3980,7 @@
         <v>35462</v>
       </c>
       <c r="B449">
-        <v>75.66477259555531</v>
+        <v>75.59514446381327</v>
       </c>
       <c r="D449">
         <v>35.15929037279584</v>
@@ -3991,7 +3991,7 @@
         <v>35490</v>
       </c>
       <c r="B450">
-        <v>64.20964132086495</v>
+        <v>64.57199544827893</v>
       </c>
       <c r="D450">
         <v>30.29108998670148</v>
@@ -4002,7 +4002,7 @@
         <v>35521</v>
       </c>
       <c r="B451">
-        <v>71.70127271404529</v>
+        <v>71.66583073570435</v>
       </c>
       <c r="D451">
         <v>32.08635956621232</v>
@@ -4013,7 +4013,7 @@
         <v>35551</v>
       </c>
       <c r="B452">
-        <v>82.29804958233474</v>
+        <v>82.64486561406692</v>
       </c>
       <c r="D452">
         <v>33.63899132861557</v>
@@ -4024,7 +4024,7 @@
         <v>35582</v>
       </c>
       <c r="B453">
-        <v>83.00037358131266</v>
+        <v>82.92313197264333</v>
       </c>
       <c r="D453">
         <v>34.3660237997538</v>
@@ -4035,7 +4035,7 @@
         <v>35612</v>
       </c>
       <c r="B454">
-        <v>66.41480168348022</v>
+        <v>66.46854043161487</v>
       </c>
       <c r="D454">
         <v>30.62748373705926</v>
@@ -4046,7 +4046,7 @@
         <v>35643</v>
       </c>
       <c r="B455">
-        <v>57.95276230874258</v>
+        <v>58.19720045036387</v>
       </c>
       <c r="D455">
         <v>27.38005526249686</v>
@@ -4057,7 +4057,7 @@
         <v>35674</v>
       </c>
       <c r="B456">
-        <v>60.65129317215975</v>
+        <v>61.05889296115504</v>
       </c>
       <c r="D456">
         <v>33.76015819045553</v>
@@ -4068,7 +4068,7 @@
         <v>35704</v>
       </c>
       <c r="B457">
-        <v>75.95065992047836</v>
+        <v>76.07947878990885</v>
       </c>
       <c r="D457">
         <v>36.76305761040125</v>
@@ -4079,7 +4079,7 @@
         <v>35735</v>
       </c>
       <c r="B458">
-        <v>83.95028923871065</v>
+        <v>84.84888851015464</v>
       </c>
       <c r="D458">
         <v>47.08053373710609</v>
@@ -4090,7 +4090,7 @@
         <v>35765</v>
       </c>
       <c r="B459">
-        <v>92.45998052913758</v>
+        <v>93.28884178580232</v>
       </c>
       <c r="D459">
         <v>31.96717400639344</v>
@@ -4101,7 +4101,7 @@
         <v>35796</v>
       </c>
       <c r="B460">
-        <v>88.1445689993093</v>
+        <v>89.09108904679188</v>
       </c>
       <c r="D460">
         <v>30.68600263672319</v>
@@ -4112,7 +4112,7 @@
         <v>35827</v>
       </c>
       <c r="B461">
-        <v>75.63332218241041</v>
+        <v>76.39437937826045</v>
       </c>
       <c r="D461">
         <v>25.52968123687727</v>
@@ -4123,7 +4123,7 @@
         <v>35855</v>
       </c>
       <c r="B462">
-        <v>76.08511831750164</v>
+        <v>76.67862922640539</v>
       </c>
       <c r="D462">
         <v>29.84241487397484</v>
@@ -4134,7 +4134,7 @@
         <v>35886</v>
       </c>
       <c r="B463">
-        <v>71.30368064276563</v>
+        <v>72.31512024128168</v>
       </c>
       <c r="D463">
         <v>30.76646679691886</v>
@@ -4145,7 +4145,7 @@
         <v>35916</v>
       </c>
       <c r="B464">
-        <v>77.8988796701544</v>
+        <v>78.74670606033294</v>
       </c>
       <c r="D464">
         <v>25.65856996236743</v>
@@ -4156,7 +4156,7 @@
         <v>35947</v>
       </c>
       <c r="B465">
-        <v>76.07220014492798</v>
+        <v>76.91365501129597</v>
       </c>
       <c r="D465">
         <v>33.53731570809468</v>
@@ -4167,7 +4167,7 @@
         <v>35977</v>
       </c>
       <c r="B466">
-        <v>91.77059119792412</v>
+        <v>92.63473093776973</v>
       </c>
       <c r="D466">
         <v>36.33124721655767</v>
@@ -4178,7 +4178,7 @@
         <v>36008</v>
       </c>
       <c r="B467">
-        <v>103.0937688080636</v>
+        <v>104.0340521745058</v>
       </c>
       <c r="D467">
         <v>32.31396056760174</v>
@@ -4189,7 +4189,7 @@
         <v>36039</v>
       </c>
       <c r="B468">
-        <v>142.6858139801402</v>
+        <v>142.4562141616617</v>
       </c>
       <c r="D468">
         <v>32.45070422535211</v>
@@ -4200,7 +4200,7 @@
         <v>36069</v>
       </c>
       <c r="B469">
-        <v>108.0688872019831</v>
+        <v>108.8959631388216</v>
       </c>
       <c r="D469">
         <v>33.76769557123685</v>
@@ -4211,7 +4211,7 @@
         <v>36100</v>
       </c>
       <c r="B470">
-        <v>90.07161422708249</v>
+        <v>90.27099885748649</v>
       </c>
       <c r="D470">
         <v>30.20467045352087</v>
@@ -4222,7 +4222,7 @@
         <v>36130</v>
       </c>
       <c r="B471">
-        <v>88.97084294021978</v>
+        <v>89.14261472301666</v>
       </c>
       <c r="D471">
         <v>35.70021095579201</v>
@@ -4233,7 +4233,7 @@
         <v>36161</v>
       </c>
       <c r="B472">
-        <v>91.49401821271482</v>
+        <v>91.2927053674953</v>
       </c>
       <c r="D472">
         <v>34.19077996282613</v>
@@ -4244,7 +4244,7 @@
         <v>36192</v>
       </c>
       <c r="B473">
-        <v>74.69705224764208</v>
+        <v>74.58134882571804</v>
       </c>
       <c r="D473">
         <v>34.41053261520048</v>
@@ -4255,7 +4255,7 @@
         <v>36220</v>
       </c>
       <c r="B474">
-        <v>56.51740925169905</v>
+        <v>56.43764902904483</v>
       </c>
       <c r="D474">
         <v>39.11342894393742</v>
@@ -4266,7 +4266,7 @@
         <v>36251</v>
       </c>
       <c r="B475">
-        <v>63.24217964700514</v>
+        <v>63.26337290084778</v>
       </c>
       <c r="D475">
         <v>34.92721618820136</v>
@@ -4277,7 +4277,7 @@
         <v>36281</v>
       </c>
       <c r="B476">
-        <v>67.15236607824785</v>
+        <v>67.44230137886983</v>
       </c>
       <c r="D476">
         <v>30.32059571052749</v>
@@ -4288,7 +4288,7 @@
         <v>36312</v>
       </c>
       <c r="B477">
-        <v>66.87281863447099</v>
+        <v>66.82881734789933</v>
       </c>
       <c r="D477">
         <v>33.0491863062406</v>
@@ -4299,7 +4299,7 @@
         <v>36342</v>
       </c>
       <c r="B478">
-        <v>70.10820107781508</v>
+        <v>69.91170662410919</v>
       </c>
       <c r="D478">
         <v>31.69572107765451</v>
@@ -4310,7 +4310,7 @@
         <v>36373</v>
       </c>
       <c r="B479">
-        <v>67.84925105187031</v>
+        <v>67.58128577468824</v>
       </c>
       <c r="D479">
         <v>32.25347436323104</v>
@@ -4321,7 +4321,7 @@
         <v>36404</v>
       </c>
       <c r="B480">
-        <v>61.48158530008502</v>
+        <v>61.43656059243794</v>
       </c>
       <c r="D480">
         <v>30.38519072550486</v>
@@ -4332,7 +4332,7 @@
         <v>36434</v>
       </c>
       <c r="B481">
-        <v>66.06217462121386</v>
+        <v>65.96162063096185</v>
       </c>
       <c r="D481">
         <v>32.63973888208894</v>
@@ -4343,7 +4343,7 @@
         <v>36465</v>
       </c>
       <c r="B482">
-        <v>65.04577994267187</v>
+        <v>64.88000296033906</v>
       </c>
       <c r="D482">
         <v>48.94195531386688</v>
@@ -4354,7 +4354,7 @@
         <v>36495</v>
       </c>
       <c r="B483">
-        <v>57.75203300815224</v>
+        <v>57.84974874346484</v>
       </c>
       <c r="D483">
         <v>41.58353964858303</v>
@@ -4365,7 +4365,7 @@
         <v>36526</v>
       </c>
       <c r="B484">
-        <v>66.40531228547813</v>
+        <v>66.36177028012447</v>
       </c>
       <c r="D484">
         <v>32.11734816164134</v>
@@ -4376,7 +4376,7 @@
         <v>36557</v>
       </c>
       <c r="B485">
-        <v>55.57682245758716</v>
+        <v>55.56510488772031</v>
       </c>
       <c r="D485">
         <v>28.17585620597523</v>
@@ -4387,7 +4387,7 @@
         <v>36586</v>
       </c>
       <c r="B486">
-        <v>60.55873213053427</v>
+        <v>60.52443734103579</v>
       </c>
       <c r="D486">
         <v>36.83850616548651</v>
@@ -4398,7 +4398,7 @@
         <v>36617</v>
       </c>
       <c r="B487">
-        <v>61.63069719471124</v>
+        <v>61.60965122757217</v>
       </c>
       <c r="D487">
         <v>35.28104006572906</v>
@@ -4409,7 +4409,7 @@
         <v>36647</v>
       </c>
       <c r="B488">
-        <v>81.43633076281019</v>
+        <v>81.41318862003649</v>
       </c>
       <c r="D488">
         <v>49.32756293917819</v>
@@ -4420,7 +4420,7 @@
         <v>36678</v>
       </c>
       <c r="B489">
-        <v>85.21831071461878</v>
+        <v>85.18713308769051</v>
       </c>
       <c r="D489">
         <v>27.36688135513247</v>
@@ -4431,7 +4431,7 @@
         <v>36708</v>
       </c>
       <c r="B490">
-        <v>63.43967656618085</v>
+        <v>63.40839146880375</v>
       </c>
       <c r="D490">
         <v>31.94444444444445</v>
@@ -4442,7 +4442,7 @@
         <v>36739</v>
       </c>
       <c r="B491">
-        <v>52.81009788652795</v>
+        <v>52.78984019296506</v>
       </c>
       <c r="D491">
         <v>29.21261803935777</v>
@@ -4453,7 +4453,7 @@
         <v>36770</v>
       </c>
       <c r="B492">
-        <v>61.68400811087739</v>
+        <v>61.66076453839437</v>
       </c>
       <c r="D492">
         <v>33.43174713442168</v>
@@ -4464,7 +4464,7 @@
         <v>36800</v>
       </c>
       <c r="B493">
-        <v>67.7468490606027</v>
+        <v>67.71565168032539</v>
       </c>
       <c r="D493">
         <v>25.48113774315842</v>
@@ -4475,7 +4475,7 @@
         <v>36831</v>
       </c>
       <c r="B494">
-        <v>93.8415610874582</v>
+        <v>93.83410154139268</v>
       </c>
       <c r="D494">
         <v>26.90486439948343</v>
@@ -4486,7 +4486,7 @@
         <v>36861</v>
       </c>
       <c r="B495">
-        <v>94.69139998088097</v>
+        <v>94.65584094881976</v>
       </c>
       <c r="D495">
         <v>29.81667404318759</v>
@@ -4497,7 +4497,7 @@
         <v>36892</v>
       </c>
       <c r="B496">
-        <v>93.38940354667724</v>
+        <v>93.34856320021318</v>
       </c>
       <c r="D496">
         <v>25.98787232624775</v>
@@ -4508,7 +4508,7 @@
         <v>36923</v>
       </c>
       <c r="B497">
-        <v>93.61953785443541</v>
+        <v>93.5879803245857</v>
       </c>
       <c r="D497">
         <v>20.64627646804629</v>
@@ -4519,7 +4519,7 @@
         <v>36951</v>
       </c>
       <c r="B498">
-        <v>104.1318899869225</v>
+        <v>104.0867042354465</v>
       </c>
       <c r="D498">
         <v>25.07863640227833</v>
@@ -4530,7 +4530,7 @@
         <v>36982</v>
       </c>
       <c r="B499">
-        <v>95.97975262155236</v>
+        <v>95.95988126881788</v>
       </c>
       <c r="D499">
         <v>34.3147347471004</v>
@@ -4541,7 +4541,7 @@
         <v>37012</v>
       </c>
       <c r="B500">
-        <v>76.24907787234997</v>
+        <v>76.22725393721501</v>
       </c>
       <c r="D500">
         <v>27.79333821691731</v>
@@ -4552,7 +4552,7 @@
         <v>37043</v>
       </c>
       <c r="B501">
-        <v>70.41441125394122</v>
+        <v>70.38255144570097</v>
       </c>
       <c r="D501">
         <v>30.15970937007334</v>
@@ -4563,7 +4563,7 @@
         <v>37073</v>
       </c>
       <c r="B502">
-        <v>89.33913539939647</v>
+        <v>89.31537722768631</v>
       </c>
       <c r="D502">
         <v>34.29895712630359</v>
@@ -4574,7 +4574,7 @@
         <v>37104</v>
       </c>
       <c r="B503">
-        <v>78.65587821853363</v>
+        <v>78.62556900255626</v>
       </c>
       <c r="D503">
         <v>28.28561572956192</v>
@@ -4585,7 +4585,7 @@
         <v>37135</v>
       </c>
       <c r="B504">
-        <v>157.900303492271</v>
+        <v>157.8663235188563</v>
       </c>
       <c r="D504">
         <v>24.12961047914512</v>
@@ -4596,7 +4596,7 @@
         <v>37165</v>
       </c>
       <c r="B505">
-        <v>149.6951438155147</v>
+        <v>149.6552580182867</v>
       </c>
       <c r="D505">
         <v>24.04201024948858</v>
@@ -4607,7 +4607,7 @@
         <v>37196</v>
       </c>
       <c r="B506">
-        <v>116.2229925402432</v>
+        <v>116.1812653346947</v>
       </c>
       <c r="D506">
         <v>33.66046643789207</v>
@@ -4618,7 +4618,7 @@
         <v>37226</v>
       </c>
       <c r="B507">
-        <v>100.6259893484772</v>
+        <v>100.5784433640315</v>
       </c>
       <c r="D507">
         <v>34.28891325138206</v>
@@ -4629,7 +4629,7 @@
         <v>37257</v>
       </c>
       <c r="B508">
-        <v>99.5713084907656</v>
+        <v>99.51953709586206</v>
       </c>
       <c r="D508">
         <v>31.63412870571222</v>
@@ -4640,7 +4640,7 @@
         <v>37288</v>
       </c>
       <c r="B509">
-        <v>80.7941328594266</v>
+        <v>80.76035068362273</v>
       </c>
       <c r="D509">
         <v>31.94888178913738</v>
@@ -4651,7 +4651,7 @@
         <v>37316</v>
       </c>
       <c r="B510">
-        <v>74.63588545244289</v>
+        <v>74.59110008680135</v>
       </c>
       <c r="D510">
         <v>53.87744504067855</v>
@@ -4662,7 +4662,7 @@
         <v>37347</v>
       </c>
       <c r="B511">
-        <v>79.1691146283863</v>
+        <v>79.13124498937587</v>
       </c>
       <c r="D511">
         <v>36.55340475424158</v>
@@ -4673,7 +4673,7 @@
         <v>37377</v>
       </c>
       <c r="B512">
-        <v>78.00537131504606</v>
+        <v>77.96673128864585</v>
       </c>
       <c r="D512">
         <v>41.12330393860093</v>
@@ -4684,7 +4684,7 @@
         <v>37408</v>
       </c>
       <c r="B513">
-        <v>88.86527764028003</v>
+        <v>88.84046706569988</v>
       </c>
       <c r="D513">
         <v>39.78324987996433</v>
@@ -4695,7 +4695,7 @@
         <v>37438</v>
       </c>
       <c r="B514">
-        <v>94.10067606051061</v>
+        <v>94.05573162843365</v>
       </c>
       <c r="D514">
         <v>40.61059219798858</v>
@@ -4706,7 +4706,7 @@
         <v>37469</v>
       </c>
       <c r="B515">
-        <v>98.69483710970307</v>
+        <v>98.65856547395823</v>
       </c>
       <c r="D515">
         <v>34.50802429743081</v>
@@ -4717,7 +4717,7 @@
         <v>37500</v>
       </c>
       <c r="B516">
-        <v>113.8761766624583</v>
+        <v>113.8302108290269</v>
       </c>
       <c r="D516">
         <v>27.68700072621641</v>
@@ -4728,7 +4728,7 @@
         <v>37530</v>
       </c>
       <c r="B517">
-        <v>113.1879198638282</v>
+        <v>113.1411263794254</v>
       </c>
       <c r="D517">
         <v>32.54575425842174</v>
@@ -4739,7 +4739,7 @@
         <v>37561</v>
       </c>
       <c r="B518">
-        <v>114.4343924884649</v>
+        <v>114.3848004180443</v>
       </c>
       <c r="D518">
         <v>31.85472511755911</v>
@@ -4750,7 +4750,7 @@
         <v>37591</v>
       </c>
       <c r="B519">
-        <v>115.9898072298102</v>
+        <v>115.9145009018859</v>
       </c>
       <c r="D519">
         <v>24.72299013327939</v>
@@ -4761,7 +4761,7 @@
         <v>37622</v>
       </c>
       <c r="B520">
-        <v>113.2780218049955</v>
+        <v>113.237606493776</v>
       </c>
       <c r="D520">
         <v>25.27453372842949</v>
@@ -4772,7 +4772,7 @@
         <v>37653</v>
       </c>
       <c r="B521">
-        <v>122.6962068545575</v>
+        <v>122.6716517540427</v>
       </c>
       <c r="D521">
         <v>31.57377739317538</v>
@@ -4783,7 +4783,7 @@
         <v>37681</v>
       </c>
       <c r="B522">
-        <v>155.0111181696256</v>
+        <v>154.9488312459112</v>
       </c>
       <c r="D522">
         <v>23.27466179007086</v>
@@ -4794,7 +4794,7 @@
         <v>37712</v>
       </c>
       <c r="B523">
-        <v>130.4987692661987</v>
+        <v>130.4096381371546</v>
       </c>
       <c r="D523">
         <v>16.24980785700169</v>
@@ -4805,7 +4805,7 @@
         <v>37742</v>
       </c>
       <c r="B524">
-        <v>101.7353919231809</v>
+        <v>101.6752723648004</v>
       </c>
       <c r="D524">
         <v>28.59866539561487</v>
@@ -4816,7 +4816,7 @@
         <v>37773</v>
       </c>
       <c r="B525">
-        <v>82.56056338381144</v>
+        <v>82.51226157747517</v>
       </c>
       <c r="D525">
         <v>32.85968028419182</v>
@@ -4827,7 +4827,7 @@
         <v>37803</v>
       </c>
       <c r="B526">
-        <v>82.63717785535752</v>
+        <v>82.56268589989422</v>
       </c>
       <c r="D526">
         <v>28.43494085532302</v>
@@ -4838,7 +4838,7 @@
         <v>37834</v>
       </c>
       <c r="B527">
-        <v>71.27819141588559</v>
+        <v>71.2245104450609</v>
       </c>
       <c r="D527">
         <v>24.55159244356544</v>
@@ -4849,7 +4849,7 @@
         <v>37865</v>
       </c>
       <c r="B528">
-        <v>76.24735842652191</v>
+        <v>76.20423551358773</v>
       </c>
       <c r="D528">
         <v>39.80838000134943</v>
@@ -4860,7 +4860,7 @@
         <v>37895</v>
       </c>
       <c r="B529">
-        <v>78.38680454134509</v>
+        <v>78.33202890196377</v>
       </c>
       <c r="D529">
         <v>31.40458547999754</v>
@@ -4871,7 +4871,7 @@
         <v>37926</v>
       </c>
       <c r="B530">
-        <v>75.24123867757834</v>
+        <v>75.20743852650411</v>
       </c>
       <c r="D530">
         <v>50.17905300853265</v>
@@ -4882,7 +4882,7 @@
         <v>37956</v>
       </c>
       <c r="B531">
-        <v>69.94716143770079</v>
+        <v>69.90059521921975</v>
       </c>
       <c r="D531">
         <v>46.6441488017279</v>
@@ -4893,7 +4893,7 @@
         <v>37987</v>
       </c>
       <c r="B532">
-        <v>76.78115936638162</v>
+        <v>76.72960464501551</v>
       </c>
       <c r="D532">
         <v>30.87917420265561</v>
@@ -4904,7 +4904,7 @@
         <v>38018</v>
       </c>
       <c r="B533">
-        <v>79.62758811936206</v>
+        <v>79.57467835557406</v>
       </c>
       <c r="D533">
         <v>35.39903333408972</v>
@@ -4915,7 +4915,7 @@
         <v>38047</v>
       </c>
       <c r="B534">
-        <v>75.03600589485724</v>
+        <v>74.99179717874699</v>
       </c>
       <c r="D534">
         <v>27.12360614801739</v>
@@ -4926,7 +4926,7 @@
         <v>38078</v>
       </c>
       <c r="B535">
-        <v>79.76890066779714</v>
+        <v>79.71451570607465</v>
       </c>
       <c r="D535">
         <v>28.38389214120986</v>
@@ -4937,7 +4937,7 @@
         <v>38108</v>
       </c>
       <c r="B536">
-        <v>94.43824107098972</v>
+        <v>94.40407034797813</v>
       </c>
       <c r="D536">
         <v>30.99539496989018</v>
@@ -4948,7 +4948,7 @@
         <v>38139</v>
       </c>
       <c r="B537">
-        <v>77.99602794796898</v>
+        <v>77.94931354769014</v>
       </c>
       <c r="D537">
         <v>22.94156782674528</v>
@@ -4959,7 +4959,7 @@
         <v>38169</v>
       </c>
       <c r="B538">
-        <v>71.9396137219379</v>
+        <v>71.8959741913867</v>
       </c>
       <c r="D538">
         <v>34.2544484803899</v>
@@ -4970,7 +4970,7 @@
         <v>38200</v>
       </c>
       <c r="B539">
-        <v>67.81001082550377</v>
+        <v>67.7691088923453</v>
       </c>
       <c r="D539">
         <v>28.87239753682358</v>
@@ -4981,7 +4981,7 @@
         <v>38231</v>
       </c>
       <c r="B540">
-        <v>74.02283791029636</v>
+        <v>73.99104320879279</v>
       </c>
       <c r="D540">
         <v>28.53132693679391</v>
@@ -4992,7 +4992,7 @@
         <v>38261</v>
       </c>
       <c r="B541">
-        <v>88.97210500727789</v>
+        <v>88.91488754351363</v>
       </c>
       <c r="D541">
         <v>29.3588205040288</v>
@@ -5003,7 +5003,7 @@
         <v>38292</v>
       </c>
       <c r="B542">
-        <v>80.4554364077819</v>
+        <v>80.41051972417775</v>
       </c>
       <c r="D542">
         <v>31.06233174570304</v>
@@ -5014,7 +5014,7 @@
         <v>38322</v>
       </c>
       <c r="B543">
-        <v>67.88588088870627</v>
+        <v>67.81839077567228</v>
       </c>
       <c r="D543">
         <v>30.10064904524504</v>
@@ -5025,7 +5025,7 @@
         <v>38353</v>
       </c>
       <c r="B544">
-        <v>64.20632583148812</v>
+        <v>64.1582961416923</v>
       </c>
       <c r="D544">
         <v>27.60942760942761</v>
@@ -5036,7 +5036,7 @@
         <v>38384</v>
       </c>
       <c r="B545">
-        <v>58.0886944085553</v>
+        <v>58.04976357155461</v>
       </c>
       <c r="D545">
         <v>19.91745056632751</v>
@@ -5047,7 +5047,7 @@
         <v>38412</v>
       </c>
       <c r="B546">
-        <v>56.30350050351331</v>
+        <v>56.26288623722446</v>
       </c>
       <c r="D546">
         <v>23.08211571543671</v>
@@ -5058,7 +5058,7 @@
         <v>38443</v>
       </c>
       <c r="B547">
-        <v>76.30503394605381</v>
+        <v>76.2271369552514</v>
       </c>
       <c r="D547">
         <v>31.50427234196868</v>
@@ -5069,7 +5069,7 @@
         <v>38473</v>
       </c>
       <c r="B548">
-        <v>63.99170942475578</v>
+        <v>63.96850365805867</v>
       </c>
       <c r="D548">
         <v>33.32582751632515</v>
@@ -5080,7 +5080,7 @@
         <v>38504</v>
       </c>
       <c r="B549">
-        <v>71.58625175209211</v>
+        <v>71.54013827333908</v>
       </c>
       <c r="D549">
         <v>38.64912119260146</v>
@@ -5091,7 +5091,7 @@
         <v>38534</v>
       </c>
       <c r="B550">
-        <v>64.88890003788114</v>
+        <v>64.82827143272166</v>
       </c>
       <c r="D550">
         <v>34.02699011596953</v>
@@ -5102,7 +5102,7 @@
         <v>38565</v>
       </c>
       <c r="B551">
-        <v>63.09625553976446</v>
+        <v>63.03783943454246</v>
       </c>
       <c r="D551">
         <v>22.78778574683969</v>
@@ -5113,7 +5113,7 @@
         <v>38596</v>
       </c>
       <c r="B552">
-        <v>92.2249000502882</v>
+        <v>92.15603106356983</v>
       </c>
       <c r="D552">
         <v>22.9043630566097</v>
@@ -5124,7 +5124,7 @@
         <v>38626</v>
       </c>
       <c r="B553">
-        <v>68.60398215992502</v>
+        <v>68.55257363673689</v>
       </c>
       <c r="D553">
         <v>34.35678872749413</v>
@@ -5135,7 +5135,7 @@
         <v>38657</v>
       </c>
       <c r="B554">
-        <v>64.45380919082463</v>
+        <v>64.41922156653618</v>
       </c>
       <c r="D554">
         <v>28.04210913437227</v>
@@ -5146,7 +5146,7 @@
         <v>38687</v>
       </c>
       <c r="B555">
-        <v>66.75609064230144</v>
+        <v>66.69313648398919</v>
       </c>
       <c r="D555">
         <v>32.10837161338709</v>
@@ -5157,7 +5157,7 @@
         <v>38718</v>
       </c>
       <c r="B556">
-        <v>78.29673922039393</v>
+        <v>78.19382276074207</v>
       </c>
       <c r="D556">
         <v>23.6623859955432</v>
@@ -5168,7 +5168,7 @@
         <v>38749</v>
       </c>
       <c r="B557">
-        <v>61.24277056138386</v>
+        <v>61.17564676235506</v>
       </c>
       <c r="D557">
         <v>24.28658166363085</v>
@@ -5179,7 +5179,7 @@
         <v>38777</v>
       </c>
       <c r="B558">
-        <v>61.44567902950821</v>
+        <v>61.38759010513453</v>
       </c>
       <c r="D558">
         <v>24.32237000679273</v>
@@ -5190,7 +5190,7 @@
         <v>38808</v>
       </c>
       <c r="B559">
-        <v>74.03565797581602</v>
+        <v>73.97299807720053</v>
       </c>
       <c r="D559">
         <v>26.57322923525538</v>
@@ -5201,7 +5201,7 @@
         <v>38838</v>
       </c>
       <c r="B560">
-        <v>62.96969454928283</v>
+        <v>62.92969155524965</v>
       </c>
       <c r="D560">
         <v>27.05389969246422</v>
@@ -5212,7 +5212,7 @@
         <v>38869</v>
       </c>
       <c r="B561">
-        <v>72.655013660382</v>
+        <v>72.60546119208983</v>
       </c>
       <c r="D561">
         <v>26.84156474652227</v>
@@ -5223,7 +5223,7 @@
         <v>38899</v>
       </c>
       <c r="B562">
-        <v>71.16684342495321</v>
+        <v>71.10783515444068</v>
       </c>
       <c r="D562">
         <v>30.90742261071135</v>
@@ -5234,7 +5234,7 @@
         <v>38930</v>
       </c>
       <c r="B563">
-        <v>64.57872901692006</v>
+        <v>64.52191529076737</v>
       </c>
       <c r="D563">
         <v>20.98435711560473</v>
@@ -5245,7 +5245,7 @@
         <v>38961</v>
       </c>
       <c r="B564">
-        <v>57.09474729295705</v>
+        <v>57.06872100114555</v>
       </c>
       <c r="D564">
         <v>26.78760250957539</v>
@@ -5256,7 +5256,7 @@
         <v>38991</v>
       </c>
       <c r="B565">
-        <v>66.88803231055297</v>
+        <v>66.8131346661192</v>
       </c>
       <c r="D565">
         <v>23.69347414026536</v>
@@ -5267,7 +5267,7 @@
         <v>39022</v>
       </c>
       <c r="B566">
-        <v>64.26007478426405</v>
+        <v>64.197817726038</v>
       </c>
       <c r="D566">
         <v>25.99792936845738</v>
@@ -5278,7 +5278,7 @@
         <v>39052</v>
       </c>
       <c r="B567">
-        <v>61.90166250226316</v>
+        <v>61.83402713158144</v>
       </c>
       <c r="D567">
         <v>26.97579469233012</v>
@@ -5289,7 +5289,7 @@
         <v>39083</v>
       </c>
       <c r="B568">
-        <v>65.13601102979226</v>
+        <v>65.10275476479541</v>
       </c>
       <c r="D568">
         <v>22.50257343260001</v>
@@ -5300,7 +5300,7 @@
         <v>39114</v>
       </c>
       <c r="B569">
-        <v>57.86122484891435</v>
+        <v>57.81582193264634</v>
       </c>
       <c r="D569">
         <v>27.55530375215679</v>
@@ -5311,7 +5311,7 @@
         <v>39142</v>
       </c>
       <c r="B570">
-        <v>67.53120117179637</v>
+        <v>67.46203687893771</v>
       </c>
       <c r="D570">
         <v>26.70623145400593</v>
@@ -5322,7 +5322,7 @@
         <v>39173</v>
       </c>
       <c r="B571">
-        <v>64.52218515820721</v>
+        <v>64.47515535128146</v>
       </c>
       <c r="D571">
         <v>30.43747420553033</v>
@@ -5333,7 +5333,7 @@
         <v>39203</v>
       </c>
       <c r="B572">
-        <v>57.21014820048162</v>
+        <v>57.16788180955429</v>
       </c>
       <c r="D572">
         <v>29.71149307194624</v>
@@ -5344,7 +5344,7 @@
         <v>39234</v>
       </c>
       <c r="B573">
-        <v>57.4732639487197</v>
+        <v>57.4221529384896</v>
       </c>
       <c r="D573">
         <v>34.27456563579319</v>
@@ -5355,7 +5355,7 @@
         <v>39264</v>
       </c>
       <c r="B574">
-        <v>52.37534909636721</v>
+        <v>52.30781027290943</v>
       </c>
       <c r="D574">
         <v>24.37064115527209</v>
@@ -5366,7 +5366,7 @@
         <v>39295</v>
       </c>
       <c r="B575">
-        <v>76.58815533583363</v>
+        <v>76.53048711892964</v>
       </c>
       <c r="D575">
         <v>23.17382836575204</v>
@@ -5377,7 +5377,7 @@
         <v>39326</v>
       </c>
       <c r="B576">
-        <v>94.34433005662176</v>
+        <v>94.27644296339074</v>
       </c>
       <c r="D576">
         <v>18.99715042743588</v>
@@ -5388,7 +5388,7 @@
         <v>39356</v>
       </c>
       <c r="B577">
-        <v>79.11778962957177</v>
+        <v>79.05457964207991</v>
       </c>
       <c r="D577">
         <v>25.88229602573716</v>
@@ -5399,7 +5399,7 @@
         <v>39387</v>
       </c>
       <c r="B578">
-        <v>79.29422593887658</v>
+        <v>79.24056570315167</v>
       </c>
       <c r="D578">
         <v>27.3709128569315</v>
@@ -5410,7 +5410,7 @@
         <v>39417</v>
       </c>
       <c r="B579">
-        <v>99.59407560270064</v>
+        <v>99.49764624699213</v>
       </c>
       <c r="D579">
         <v>21.81988206873263</v>
@@ -5421,7 +5421,7 @@
         <v>39448</v>
       </c>
       <c r="B580">
-        <v>132.7696013132085</v>
+        <v>132.6689860616669</v>
       </c>
       <c r="C580">
         <v>17245.12</v>
@@ -5435,7 +5435,7 @@
         <v>39479</v>
       </c>
       <c r="B581">
-        <v>97.7583196387164</v>
+        <v>97.69132053650709</v>
       </c>
       <c r="C581">
         <v>16059.42</v>
@@ -5449,7 +5449,7 @@
         <v>39508</v>
       </c>
       <c r="B582">
-        <v>129.6511699923242</v>
+        <v>129.4850567162087</v>
       </c>
       <c r="C582">
         <v>11944.98</v>
@@ -5463,7 +5463,7 @@
         <v>39539</v>
       </c>
       <c r="B583">
-        <v>98.95335063460783</v>
+        <v>98.84104878749949</v>
       </c>
       <c r="C583">
         <v>14277.65</v>
@@ -5477,7 +5477,7 @@
         <v>39569</v>
       </c>
       <c r="B584">
-        <v>81.7308539421897</v>
+        <v>81.64794905308241</v>
       </c>
       <c r="C584">
         <v>14969.42</v>
@@ -5491,7 +5491,7 @@
         <v>39600</v>
       </c>
       <c r="B585">
-        <v>90.95951726161954</v>
+        <v>90.88232603910964</v>
       </c>
       <c r="C585">
         <v>16455.88</v>
@@ -5505,7 +5505,7 @@
         <v>39630</v>
       </c>
       <c r="B586">
-        <v>108.1919428369347</v>
+        <v>108.0376549221824</v>
       </c>
       <c r="C586">
         <v>9904.023999999999</v>
@@ -5519,7 +5519,7 @@
         <v>39661</v>
       </c>
       <c r="B587">
-        <v>99.10729394733214</v>
+        <v>98.95006665152795</v>
       </c>
       <c r="C587">
         <v>12619.14</v>
@@ -5533,7 +5533,7 @@
         <v>39692</v>
       </c>
       <c r="B588">
-        <v>159.5050423995914</v>
+        <v>159.3776837881561</v>
       </c>
       <c r="C588">
         <v>13118.48</v>
@@ -5547,7 +5547,7 @@
         <v>39722</v>
       </c>
       <c r="B589">
-        <v>209.2860670338012</v>
+        <v>209.1017223622512</v>
       </c>
       <c r="C589">
         <v>15511.13</v>
@@ -5561,7 +5561,7 @@
         <v>39753</v>
       </c>
       <c r="B590">
-        <v>146.5023403589852</v>
+        <v>146.347897498356</v>
       </c>
       <c r="C590">
         <v>16251.19</v>
@@ -5575,7 +5575,7 @@
         <v>39783</v>
       </c>
       <c r="B591">
-        <v>148.7238643219771</v>
+        <v>148.5708057750015</v>
       </c>
       <c r="C591">
         <v>11388.37</v>
@@ -5589,7 +5589,7 @@
         <v>39814</v>
       </c>
       <c r="B592">
-        <v>146.6191685590836</v>
+        <v>146.4392207254933</v>
       </c>
       <c r="C592">
         <v>11772.56</v>
@@ -5603,7 +5603,7 @@
         <v>39845</v>
       </c>
       <c r="B593">
-        <v>144.45254603137</v>
+        <v>144.3146908439211</v>
       </c>
       <c r="C593">
         <v>15087.54</v>
@@ -5617,7 +5617,7 @@
         <v>39873</v>
       </c>
       <c r="B594">
-        <v>136.5335274027738</v>
+        <v>136.3779948874119</v>
       </c>
       <c r="C594">
         <v>20401.91</v>
@@ -5631,7 +5631,7 @@
         <v>39904</v>
       </c>
       <c r="B595">
-        <v>104.85473267745</v>
+        <v>104.745746029674</v>
       </c>
       <c r="C595">
         <v>16736.19</v>
@@ -5645,7 +5645,7 @@
         <v>39934</v>
       </c>
       <c r="B596">
-        <v>100.5988320613798</v>
+        <v>100.5218985281527</v>
       </c>
       <c r="C596">
         <v>16066.15</v>
@@ -5659,7 +5659,7 @@
         <v>39965</v>
       </c>
       <c r="B597">
-        <v>130.8217387336834</v>
+        <v>130.580307638156</v>
       </c>
       <c r="C597">
         <v>17881.58</v>
@@ -5673,7 +5673,7 @@
         <v>39995</v>
       </c>
       <c r="B598">
-        <v>117.9801342955144</v>
+        <v>117.7992038866299</v>
       </c>
       <c r="C598">
         <v>12265.1</v>
@@ -5687,7 +5687,7 @@
         <v>40026</v>
       </c>
       <c r="B599">
-        <v>109.4393080085026</v>
+        <v>109.2755924845191</v>
       </c>
       <c r="C599">
         <v>14420.23</v>
@@ -5701,7 +5701,7 @@
         <v>40057</v>
       </c>
       <c r="B600">
-        <v>119.8341153649106</v>
+        <v>119.5786353129479</v>
       </c>
       <c r="C600">
         <v>13766.26</v>
@@ -5715,7 +5715,7 @@
         <v>40087</v>
       </c>
       <c r="B601">
-        <v>98.21574209666818</v>
+        <v>98.05284284168079</v>
       </c>
       <c r="C601">
         <v>19294.3</v>
@@ -5729,7 +5729,7 @@
         <v>40118</v>
       </c>
       <c r="B602">
-        <v>109.5113423276896</v>
+        <v>109.3460052265073</v>
       </c>
       <c r="C602">
         <v>20780.36</v>
@@ -5743,7 +5743,7 @@
         <v>40148</v>
       </c>
       <c r="B603">
-        <v>105.8216448535447</v>
+        <v>105.6822037323678</v>
       </c>
       <c r="C603">
         <v>19363.22</v>
@@ -5757,7 +5757,7 @@
         <v>40179</v>
       </c>
       <c r="B604">
-        <v>120.8221375552374</v>
+        <v>120.6541925646326</v>
       </c>
       <c r="C604">
         <v>23146.06</v>
@@ -5771,7 +5771,7 @@
         <v>40210</v>
       </c>
       <c r="B605">
-        <v>120.6237408870844</v>
+        <v>120.4738756830882</v>
       </c>
       <c r="C605">
         <v>29661.91</v>
@@ -5785,7 +5785,7 @@
         <v>40238</v>
       </c>
       <c r="B606">
-        <v>121.6519997005863</v>
+        <v>121.4486499167599</v>
       </c>
       <c r="C606">
         <v>19562.9</v>
@@ -5799,7 +5799,7 @@
         <v>40269</v>
       </c>
       <c r="B607">
-        <v>109.4240408827375</v>
+        <v>109.2899844711115</v>
       </c>
       <c r="C607">
         <v>23612.76</v>
@@ -5813,7 +5813,7 @@
         <v>40299</v>
       </c>
       <c r="B608">
-        <v>143.4003044797819</v>
+        <v>143.2495778135694</v>
       </c>
       <c r="C608">
         <v>22580.16</v>
@@ -5827,7 +5827,7 @@
         <v>40330</v>
       </c>
       <c r="B609">
-        <v>142.2429074268007</v>
+        <v>142.0473363347887</v>
       </c>
       <c r="C609">
         <v>23196.64</v>
@@ -5841,7 +5841,7 @@
         <v>40360</v>
       </c>
       <c r="B610">
-        <v>147.0695338777873</v>
+        <v>146.8894558961345</v>
       </c>
       <c r="C610">
         <v>20535.61</v>
@@ -5855,7 +5855,7 @@
         <v>40391</v>
       </c>
       <c r="B611">
-        <v>122.0251591335703</v>
+        <v>121.8905923644854</v>
       </c>
       <c r="C611">
         <v>32177.13</v>
@@ -5869,7 +5869,7 @@
         <v>40422</v>
       </c>
       <c r="B612">
-        <v>127.5128548108033</v>
+        <v>127.3968295946675</v>
       </c>
       <c r="C612">
         <v>20655.87</v>
@@ -5883,7 +5883,7 @@
         <v>40452</v>
       </c>
       <c r="B613">
-        <v>123.5252435365387</v>
+        <v>123.387131219425</v>
       </c>
       <c r="C613">
         <v>27171.7</v>
@@ -5897,7 +5897,7 @@
         <v>40483</v>
       </c>
       <c r="B614">
-        <v>127.8192903329097</v>
+        <v>127.6874940383572</v>
       </c>
       <c r="C614">
         <v>13966.62</v>
@@ -5911,7 +5911,7 @@
         <v>40513</v>
       </c>
       <c r="B615">
-        <v>140.0316549127836</v>
+        <v>139.8541643252609</v>
       </c>
       <c r="C615">
         <v>14303.45</v>
@@ -5925,7 +5925,7 @@
         <v>40544</v>
       </c>
       <c r="B616">
-        <v>124.6527272398392</v>
+        <v>124.4218623012391</v>
       </c>
       <c r="C616">
         <v>15449.49</v>
@@ -5939,7 +5939,7 @@
         <v>40575</v>
       </c>
       <c r="B617">
-        <v>97.68156942116386</v>
+        <v>97.59380192664925</v>
       </c>
       <c r="C617">
         <v>14260.61</v>
@@ -5953,7 +5953,7 @@
         <v>40603</v>
       </c>
       <c r="B618">
-        <v>132.2226395732113</v>
+        <v>132.0426524142706</v>
       </c>
       <c r="C618">
         <v>12549.44</v>
@@ -5967,7 +5967,7 @@
         <v>40634</v>
       </c>
       <c r="B619">
-        <v>124.4896096711237</v>
+        <v>124.2883772537001</v>
       </c>
       <c r="C619">
         <v>10858.82</v>
@@ -5981,7 +5981,7 @@
         <v>40664</v>
       </c>
       <c r="B620">
-        <v>94.81990221929456</v>
+        <v>94.70958434682804</v>
       </c>
       <c r="C620">
         <v>14147.12</v>
@@ -5995,7 +5995,7 @@
         <v>40695</v>
       </c>
       <c r="B621">
-        <v>124.4625296308099</v>
+        <v>124.3094285103497</v>
       </c>
       <c r="C621">
         <v>12621</v>
@@ -6009,7 +6009,7 @@
         <v>40725</v>
       </c>
       <c r="B622">
-        <v>151.3937268147959</v>
+        <v>151.2452272338302</v>
       </c>
       <c r="C622">
         <v>16853.56</v>
@@ -6023,7 +6023,7 @@
         <v>40756</v>
       </c>
       <c r="B623">
-        <v>215.8631167738925</v>
+        <v>215.6544495486055</v>
       </c>
       <c r="C623">
         <v>15732.06</v>
@@ -6037,7 +6037,7 @@
         <v>40787</v>
       </c>
       <c r="B624">
-        <v>194.8710531523376</v>
+        <v>194.6587815391837</v>
       </c>
       <c r="C624">
         <v>18687.09</v>
@@ -6051,7 +6051,7 @@
         <v>40817</v>
       </c>
       <c r="B625">
-        <v>173.5585385561833</v>
+        <v>173.323636431364</v>
       </c>
       <c r="C625">
         <v>22334.08</v>
@@ -6065,7 +6065,7 @@
         <v>40848</v>
       </c>
       <c r="B626">
-        <v>195.5603140453931</v>
+        <v>195.3191983945288</v>
       </c>
       <c r="C626">
         <v>18310.76</v>
@@ -6079,7 +6079,7 @@
         <v>40878</v>
       </c>
       <c r="B627">
-        <v>186.603820471264</v>
+        <v>186.3661586629061</v>
       </c>
       <c r="C627">
         <v>17926.63</v>
@@ -6093,7 +6093,7 @@
         <v>40909</v>
       </c>
       <c r="B628">
-        <v>158.6706051409631</v>
+        <v>158.4827450981174</v>
       </c>
       <c r="C628">
         <v>18402.08</v>
@@ -6107,7 +6107,7 @@
         <v>40940</v>
       </c>
       <c r="B629">
-        <v>148.5530884531795</v>
+        <v>148.336169817166</v>
       </c>
       <c r="C629">
         <v>18511.58</v>
@@ -6121,7 +6121,7 @@
         <v>40969</v>
       </c>
       <c r="B630">
-        <v>147.0793193613002</v>
+        <v>146.8662941329987</v>
       </c>
       <c r="C630">
         <v>18355.28</v>
@@ -6135,7 +6135,7 @@
         <v>41000</v>
       </c>
       <c r="B631">
-        <v>136.699620704505</v>
+        <v>136.5026773660001</v>
       </c>
       <c r="C631">
         <v>15813.25</v>
@@ -6149,7 +6149,7 @@
         <v>41030</v>
       </c>
       <c r="B632">
-        <v>165.780031041318</v>
+        <v>165.5725107898236</v>
       </c>
       <c r="C632">
         <v>14609.73</v>
@@ -6163,7 +6163,7 @@
         <v>41061</v>
       </c>
       <c r="B633">
-        <v>188.5271270443731</v>
+        <v>188.3104954970489</v>
       </c>
       <c r="C633">
         <v>36236.57</v>
@@ -6177,7 +6177,7 @@
         <v>41091</v>
       </c>
       <c r="B634">
-        <v>153.1802605620028</v>
+        <v>152.9925643094402</v>
       </c>
       <c r="C634">
         <v>33079.34</v>
@@ -6191,7 +6191,7 @@
         <v>41122</v>
       </c>
       <c r="B635">
-        <v>118.7568783502385</v>
+        <v>118.6340184514001</v>
       </c>
       <c r="C635">
         <v>35269.25</v>
@@ -6205,7 +6205,7 @@
         <v>41153</v>
       </c>
       <c r="B636">
-        <v>156.2924182462142</v>
+        <v>156.1049057969113</v>
       </c>
       <c r="C636">
         <v>24828.08</v>
@@ -6219,7 +6219,7 @@
         <v>41183</v>
       </c>
       <c r="B637">
-        <v>151.8327028390947</v>
+        <v>151.6563442957393</v>
       </c>
       <c r="C637">
         <v>20310.6</v>
@@ -6233,7 +6233,7 @@
         <v>41214</v>
       </c>
       <c r="B638">
-        <v>161.2275928187646</v>
+        <v>161.037000110006</v>
       </c>
       <c r="C638">
         <v>30968.85</v>
@@ -6247,7 +6247,7 @@
         <v>41244</v>
       </c>
       <c r="B639">
-        <v>170.265823998872</v>
+        <v>170.0445051229279</v>
       </c>
       <c r="C639">
         <v>39555.1</v>
@@ -6261,7 +6261,7 @@
         <v>41275</v>
       </c>
       <c r="B640">
-        <v>166.1675638404668</v>
+        <v>165.9602131185743</v>
       </c>
       <c r="C640">
         <v>30948.78</v>
@@ -6275,7 +6275,7 @@
         <v>41306</v>
       </c>
       <c r="B641">
-        <v>123.5508051586799</v>
+        <v>123.416359685074</v>
       </c>
       <c r="C641">
         <v>20086.67</v>
@@ -6289,7 +6289,7 @@
         <v>41334</v>
       </c>
       <c r="B642">
-        <v>145.4100117288481</v>
+        <v>145.2660393616929</v>
       </c>
       <c r="C642">
         <v>31259.48</v>
@@ -6303,7 +6303,7 @@
         <v>41365</v>
       </c>
       <c r="B643">
-        <v>140.0028930308006</v>
+        <v>139.8121878879431</v>
       </c>
       <c r="C643">
         <v>20386.52</v>
@@ -6317,7 +6317,7 @@
         <v>41395</v>
       </c>
       <c r="B644">
-        <v>108.5689123744349</v>
+        <v>108.4549273193699</v>
       </c>
       <c r="C644">
         <v>14386.56</v>
@@ -6331,7 +6331,7 @@
         <v>41426</v>
       </c>
       <c r="B645">
-        <v>130.4979296106069</v>
+        <v>130.3340246119637</v>
       </c>
       <c r="C645">
         <v>13789.65</v>
@@ -6345,7 +6345,7 @@
         <v>41456</v>
       </c>
       <c r="B646">
-        <v>108.733239453248</v>
+        <v>108.6116566460297</v>
       </c>
       <c r="C646">
         <v>15417.21</v>
@@ -6359,7 +6359,7 @@
         <v>41487</v>
       </c>
       <c r="B647">
-        <v>127.6643026763873</v>
+        <v>127.5034977499067</v>
       </c>
       <c r="C647">
         <v>14158.71</v>
@@ -6373,7 +6373,7 @@
         <v>41518</v>
       </c>
       <c r="B648">
-        <v>141.6359499755157</v>
+        <v>141.4751687497372</v>
       </c>
       <c r="C648">
         <v>15448.87</v>
@@ -6387,7 +6387,7 @@
         <v>41548</v>
       </c>
       <c r="B649">
-        <v>167.6591144573588</v>
+        <v>167.4150691586816</v>
       </c>
       <c r="C649">
         <v>21717.67</v>
@@ -6401,7 +6401,7 @@
         <v>41579</v>
       </c>
       <c r="B650">
-        <v>108.3106550828385</v>
+        <v>108.1183175636579</v>
       </c>
       <c r="C650">
         <v>12641.28</v>
@@ -6415,7 +6415,7 @@
         <v>41609</v>
       </c>
       <c r="B651">
-        <v>128.4737624764945</v>
+        <v>128.2759877710655</v>
       </c>
       <c r="C651">
         <v>17539.43</v>
@@ -6429,7 +6429,7 @@
         <v>41640</v>
       </c>
       <c r="B652">
-        <v>119.892451683436</v>
+        <v>119.7245269233516</v>
       </c>
       <c r="C652">
         <v>21842.74</v>
@@ -6443,7 +6443,7 @@
         <v>41671</v>
       </c>
       <c r="B653">
-        <v>101.0401489747724</v>
+        <v>100.9257881140897</v>
       </c>
       <c r="C653">
         <v>21788.17</v>
@@ -6457,7 +6457,7 @@
         <v>41699</v>
       </c>
       <c r="B654">
-        <v>114.7845236699494</v>
+        <v>114.6227417235872</v>
       </c>
       <c r="C654">
         <v>19225.85</v>
@@ -6471,7 +6471,7 @@
         <v>41730</v>
       </c>
       <c r="B655">
-        <v>118.6954967387737</v>
+        <v>118.4856502358804</v>
       </c>
       <c r="C655">
         <v>13590.26</v>
@@ -6485,7 +6485,7 @@
         <v>41760</v>
       </c>
       <c r="B656">
-        <v>111.1686931616511</v>
+        <v>111.0433455756112</v>
       </c>
       <c r="C656">
         <v>17282.29</v>
@@ -6499,7 +6499,7 @@
         <v>41791</v>
       </c>
       <c r="B657">
-        <v>96.65906523050651</v>
+        <v>96.48710743626016</v>
       </c>
       <c r="C657">
         <v>19739.77</v>
@@ -6513,7 +6513,7 @@
         <v>41821</v>
       </c>
       <c r="B658">
-        <v>100.073175695144</v>
+        <v>99.91989950272327</v>
       </c>
       <c r="C658">
         <v>20342.31</v>
@@ -6527,7 +6527,7 @@
         <v>41852</v>
       </c>
       <c r="B659">
-        <v>105.2470776390631</v>
+        <v>105.1212350096452</v>
       </c>
       <c r="C659">
         <v>13934.56</v>
@@ -6541,7 +6541,7 @@
         <v>41883</v>
       </c>
       <c r="B660">
-        <v>128.7945163781695</v>
+        <v>128.619448259001</v>
       </c>
       <c r="C660">
         <v>14067.97</v>
@@ -6555,7 +6555,7 @@
         <v>41913</v>
       </c>
       <c r="B661">
-        <v>114.8793428905325</v>
+        <v>114.7173344999121</v>
       </c>
       <c r="C661">
         <v>14332.98</v>
@@ -6569,7 +6569,7 @@
         <v>41944</v>
       </c>
       <c r="B662">
-        <v>128.7689480297002</v>
+        <v>128.5742069786289</v>
       </c>
       <c r="C662">
         <v>25064.32</v>
@@ -6583,7 +6583,7 @@
         <v>41974</v>
       </c>
       <c r="B663">
-        <v>114.0162687994992</v>
+        <v>113.9207567224148</v>
       </c>
       <c r="C663">
         <v>17021.78</v>
@@ -6597,7 +6597,7 @@
         <v>42005</v>
       </c>
       <c r="B664">
-        <v>135.3098201958523</v>
+        <v>135.149157854376</v>
       </c>
       <c r="C664">
         <v>25443.97</v>
@@ -6611,7 +6611,7 @@
         <v>42036</v>
       </c>
       <c r="B665">
-        <v>122.8665979679264</v>
+        <v>122.7105160759219</v>
       </c>
       <c r="C665">
         <v>29456.69</v>
@@ -6625,7 +6625,7 @@
         <v>42064</v>
       </c>
       <c r="B666">
-        <v>118.0749727036708</v>
+        <v>117.8843039202131</v>
       </c>
       <c r="C666">
         <v>29700.53</v>
@@ -6639,7 +6639,7 @@
         <v>42095</v>
       </c>
       <c r="B667">
-        <v>100.929883261628</v>
+        <v>100.8251195492363</v>
       </c>
       <c r="C667">
         <v>22530.23</v>
@@ -6653,7 +6653,7 @@
         <v>42125</v>
       </c>
       <c r="B668">
-        <v>101.6116917821393</v>
+        <v>101.5000153384344</v>
       </c>
       <c r="C668">
         <v>21803.69</v>
@@ -6667,7 +6667,7 @@
         <v>42156</v>
       </c>
       <c r="B669">
-        <v>118.8823586677045</v>
+        <v>118.7254655937451</v>
       </c>
       <c r="C669">
         <v>25042.18</v>
@@ -6681,7 +6681,7 @@
         <v>42186</v>
       </c>
       <c r="B670">
-        <v>123.167139606705</v>
+        <v>122.9482155335303</v>
       </c>
       <c r="C670">
         <v>26689.86</v>
@@ -6695,7 +6695,7 @@
         <v>42217</v>
       </c>
       <c r="B671">
-        <v>117.2886513595701</v>
+        <v>117.1897306919892</v>
       </c>
       <c r="C671">
         <v>22015.01</v>
@@ -6709,7 +6709,7 @@
         <v>42248</v>
       </c>
       <c r="B672">
-        <v>153.9980135225141</v>
+        <v>153.8398599199942</v>
       </c>
       <c r="C672">
         <v>20895.17</v>
@@ -6723,7 +6723,7 @@
         <v>42278</v>
       </c>
       <c r="B673">
-        <v>115.5419217619356</v>
+        <v>115.3986716072227</v>
       </c>
       <c r="C673">
         <v>25572.94</v>
@@ -6737,7 +6737,7 @@
         <v>42309</v>
       </c>
       <c r="B674">
-        <v>106.217832773303</v>
+        <v>106.0600801796203</v>
       </c>
       <c r="C674">
         <v>21316.99</v>
@@ -6751,7 +6751,7 @@
         <v>42339</v>
       </c>
       <c r="B675">
-        <v>117.0787378122828</v>
+        <v>116.9237490628539</v>
       </c>
       <c r="C675">
         <v>16845.93</v>
@@ -6765,7 +6765,7 @@
         <v>42370</v>
       </c>
       <c r="B676">
-        <v>141.1904709520688</v>
+        <v>140.9802811438042</v>
       </c>
       <c r="C676">
         <v>18498.77</v>
@@ -6779,7 +6779,7 @@
         <v>42401</v>
       </c>
       <c r="B677">
-        <v>145.9550791088167</v>
+        <v>145.7767468580293</v>
       </c>
       <c r="C677">
         <v>20446.37</v>
@@ -6793,7 +6793,7 @@
         <v>42430</v>
       </c>
       <c r="B678">
-        <v>162.6024656915891</v>
+        <v>162.3461336415121</v>
       </c>
       <c r="C678">
         <v>22191.53</v>
@@ -6807,7 +6807,7 @@
         <v>42461</v>
       </c>
       <c r="B679">
-        <v>146.6718839837212</v>
+        <v>146.3993800613457</v>
       </c>
       <c r="C679">
         <v>15032.11</v>
@@ -6821,7 +6821,7 @@
         <v>42491</v>
       </c>
       <c r="B680">
-        <v>123.9689383522726</v>
+        <v>123.777640218217</v>
       </c>
       <c r="C680">
         <v>21466.45</v>
@@ -6835,7 +6835,7 @@
         <v>42522</v>
       </c>
       <c r="B681">
-        <v>221.0801629101615</v>
+        <v>220.8623331558001</v>
       </c>
       <c r="C681">
         <v>17423.54</v>
@@ -6849,7 +6849,7 @@
         <v>42552</v>
       </c>
       <c r="B682">
-        <v>189.2196495242323</v>
+        <v>189.0333227967832</v>
       </c>
       <c r="C682">
         <v>45973.39</v>
@@ -6863,7 +6863,7 @@
         <v>42583</v>
       </c>
       <c r="B683">
-        <v>136.7152867039044</v>
+        <v>136.5229370638752</v>
       </c>
       <c r="C683">
         <v>44083.75</v>
@@ -6877,7 +6877,7 @@
         <v>42614</v>
       </c>
       <c r="B684">
-        <v>139.406087995387</v>
+        <v>139.162318128015</v>
       </c>
       <c r="C684">
         <v>28374.06</v>
@@ -6891,7 +6891,7 @@
         <v>42644</v>
       </c>
       <c r="B685">
-        <v>122.5881593609823</v>
+        <v>122.411453039911</v>
       </c>
       <c r="C685">
         <v>18582.51</v>
@@ -6905,7 +6905,7 @@
         <v>42675</v>
       </c>
       <c r="B686">
-        <v>215.4203519048661</v>
+        <v>215.2003134715575</v>
       </c>
       <c r="C686">
         <v>26743.54</v>
@@ -6919,7 +6919,7 @@
         <v>42705</v>
       </c>
       <c r="B687">
-        <v>186.9887081276159</v>
+        <v>186.7729169531476</v>
       </c>
       <c r="C687">
         <v>30556.11</v>
@@ -6933,7 +6933,7 @@
         <v>42736</v>
       </c>
       <c r="B688">
-        <v>255.9307409329231</v>
+        <v>255.4222639433124</v>
       </c>
       <c r="C688">
         <v>38065.04</v>
@@ -6947,7 +6947,7 @@
         <v>42767</v>
       </c>
       <c r="B689">
-        <v>190.0485762081897</v>
+        <v>189.7555808488887</v>
       </c>
       <c r="C689">
         <v>34721.72</v>
@@ -6961,7 +6961,7 @@
         <v>42795</v>
       </c>
       <c r="B690">
-        <v>250.8238032924824</v>
+        <v>250.2431285926663</v>
       </c>
       <c r="C690">
         <v>28585.07</v>
@@ -6975,7 +6975,7 @@
         <v>42826</v>
       </c>
       <c r="B691">
-        <v>178.1587166421914</v>
+        <v>177.869298691183</v>
       </c>
       <c r="C691">
         <v>22038.28</v>
@@ -6989,7 +6989,7 @@
         <v>42856</v>
       </c>
       <c r="B692">
-        <v>142.9479770084823</v>
+        <v>142.7336804079073</v>
       </c>
       <c r="C692">
         <v>20300.89</v>
@@ -7003,7 +7003,7 @@
         <v>42887</v>
       </c>
       <c r="B693">
-        <v>175.9848780563877</v>
+        <v>175.6060180706379</v>
       </c>
       <c r="C693">
         <v>15384.21</v>
@@ -7017,7 +7017,7 @@
         <v>42917</v>
       </c>
       <c r="B694">
-        <v>172.7591751725655</v>
+        <v>172.379027228027</v>
       </c>
       <c r="C694">
         <v>16915.2</v>
@@ -7031,7 +7031,7 @@
         <v>42948</v>
       </c>
       <c r="B695">
-        <v>142.1128545354746</v>
+        <v>141.8386167108098</v>
       </c>
       <c r="C695">
         <v>21567.95</v>
@@ -7045,7 +7045,7 @@
         <v>42979</v>
       </c>
       <c r="B696">
-        <v>163.8820779579743</v>
+        <v>163.5386274069365</v>
       </c>
       <c r="C696">
         <v>15468.96</v>
@@ -7059,7 +7059,7 @@
         <v>43009</v>
       </c>
       <c r="B697">
-        <v>150.1122744008245</v>
+        <v>149.8742658588074</v>
       </c>
       <c r="C697">
         <v>20376.24</v>
@@ -7073,7 +7073,7 @@
         <v>43040</v>
       </c>
       <c r="B698">
-        <v>168.4426853655091</v>
+        <v>168.1000626230824</v>
       </c>
       <c r="C698">
         <v>20821.27</v>
@@ -7087,7 +7087,7 @@
         <v>43070</v>
       </c>
       <c r="B699">
-        <v>155.8984480690011</v>
+        <v>155.6193982051384</v>
       </c>
       <c r="C699">
         <v>27945.3</v>
@@ -7101,7 +7101,7 @@
         <v>43101</v>
       </c>
       <c r="B700">
-        <v>180.658729538629</v>
+        <v>180.2059169545451</v>
       </c>
       <c r="C700">
         <v>21420.12</v>
@@ -7115,7 +7115,7 @@
         <v>43132</v>
       </c>
       <c r="B701">
-        <v>131.0892099172494</v>
+        <v>130.8336031571206</v>
       </c>
       <c r="C701">
         <v>17493.08</v>
@@ -7129,7 +7129,7 @@
         <v>43160</v>
       </c>
       <c r="B702">
-        <v>181.997277959306</v>
+        <v>181.5623216587443</v>
       </c>
       <c r="C702">
         <v>12197.86</v>
@@ -7143,7 +7143,7 @@
         <v>43191</v>
       </c>
       <c r="B703">
-        <v>173.9947432526082</v>
+        <v>173.5819054444155</v>
       </c>
       <c r="C703">
         <v>12920.08</v>
@@ -7157,7 +7157,7 @@
         <v>43221</v>
       </c>
       <c r="B704">
-        <v>172.9787164202766</v>
+        <v>172.6211881258129</v>
       </c>
       <c r="C704">
         <v>19883.07</v>
@@ -7171,7 +7171,7 @@
         <v>43252</v>
       </c>
       <c r="B705">
-        <v>163.9326591117224</v>
+        <v>163.585354280652</v>
       </c>
       <c r="C705">
         <v>25859.36</v>
@@ -7185,7 +7185,7 @@
         <v>43282</v>
       </c>
       <c r="B706">
-        <v>239.2982397851821</v>
+        <v>238.6202618329807</v>
       </c>
       <c r="C706">
         <v>22117.7</v>
@@ -7199,7 +7199,7 @@
         <v>43313</v>
       </c>
       <c r="B707">
-        <v>182.693165848459</v>
+        <v>182.2319292355351</v>
       </c>
       <c r="C707">
         <v>30926.84</v>
@@ -7213,7 +7213,7 @@
         <v>43344</v>
       </c>
       <c r="B708">
-        <v>206.3856120951636</v>
+        <v>205.8479735884054</v>
       </c>
       <c r="C708">
         <v>27915.26</v>
@@ -7227,7 +7227,7 @@
         <v>43374</v>
       </c>
       <c r="B709">
-        <v>226.54948126494</v>
+        <v>225.9593538889647</v>
       </c>
       <c r="C709">
         <v>22779.45</v>
@@ -7241,7 +7241,7 @@
         <v>43405</v>
       </c>
       <c r="B710">
-        <v>266.1191756408321</v>
+        <v>265.3688590079915</v>
       </c>
       <c r="C710">
         <v>18793.39</v>
@@ -7255,7 +7255,7 @@
         <v>43435</v>
       </c>
       <c r="B711">
-        <v>218.7769090018232</v>
+        <v>218.3552899090525</v>
       </c>
       <c r="C711">
         <v>26231.1</v>
@@ -7269,7 +7269,7 @@
         <v>43466</v>
       </c>
       <c r="B712">
-        <v>244.2214635767608</v>
+        <v>243.7158717420112</v>
       </c>
       <c r="C712">
         <v>36382.28</v>
@@ -7283,7 +7283,7 @@
         <v>43497</v>
       </c>
       <c r="B713">
-        <v>178.2899325716794</v>
+        <v>177.8681478999297</v>
       </c>
       <c r="C713">
         <v>51178.63</v>
@@ -7297,7 +7297,7 @@
         <v>43525</v>
       </c>
       <c r="B714">
-        <v>252.5826209283937</v>
+        <v>251.8588298763838</v>
       </c>
       <c r="C714">
         <v>35809.01</v>
@@ -7311,7 +7311,7 @@
         <v>43556</v>
       </c>
       <c r="B715">
-        <v>205.4807447521729</v>
+        <v>204.9201688447855</v>
       </c>
       <c r="C715">
         <v>27627.57</v>
@@ -7325,7 +7325,7 @@
         <v>43586</v>
       </c>
       <c r="B716">
-        <v>238.9102125903181</v>
+        <v>238.2745103394634</v>
       </c>
       <c r="C716">
         <v>57517.98</v>
@@ -7339,7 +7339,7 @@
         <v>43617</v>
       </c>
       <c r="B717">
-        <v>351.1708384074168</v>
+        <v>350.0304589158609</v>
       </c>
       <c r="C717">
         <v>41085.63</v>
@@ -7353,7 +7353,7 @@
         <v>43647</v>
       </c>
       <c r="B718">
-        <v>260.5201211260178</v>
+        <v>259.8561942074757</v>
       </c>
       <c r="C718">
         <v>22822.22</v>
@@ -7367,7 +7367,7 @@
         <v>43678</v>
       </c>
       <c r="B719">
-        <v>293.8965768618484</v>
+        <v>293.1981802654853</v>
       </c>
       <c r="C719">
         <v>33126.3</v>
@@ -7381,7 +7381,7 @@
         <v>43709</v>
       </c>
       <c r="B720">
-        <v>251.1160926319757</v>
+        <v>250.5044558967545</v>
       </c>
       <c r="C720">
         <v>32220.86</v>
@@ -7395,7 +7395,7 @@
         <v>43739</v>
       </c>
       <c r="B721">
-        <v>209.3719427163467</v>
+        <v>208.9544648685717</v>
       </c>
       <c r="C721">
         <v>39475.35</v>
@@ -7409,7 +7409,7 @@
         <v>43770</v>
       </c>
       <c r="B722">
-        <v>260.0705860041973</v>
+        <v>259.36974506763</v>
       </c>
       <c r="C722">
         <v>39040.36</v>
@@ -7423,7 +7423,7 @@
         <v>43800</v>
       </c>
       <c r="B723">
-        <v>245.2120936384618</v>
+        <v>244.621386533282</v>
       </c>
       <c r="C723">
         <v>52683.16</v>
@@ -7437,7 +7437,7 @@
         <v>43831</v>
       </c>
       <c r="B724">
-        <v>199.8889612320059</v>
+        <v>199.4266364361742</v>
       </c>
       <c r="C724">
         <v>42258.74</v>
@@ -7451,7 +7451,7 @@
         <v>43862</v>
       </c>
       <c r="B725">
-        <v>198.4574359810781</v>
+        <v>198.0965730411711</v>
       </c>
       <c r="C725">
         <v>39762.47</v>
@@ -7465,7 +7465,7 @@
         <v>43891</v>
       </c>
       <c r="B726">
-        <v>311.9758385074605</v>
+        <v>311.567901301411</v>
       </c>
       <c r="C726">
         <v>56223.62</v>
@@ -7479,7 +7479,7 @@
         <v>43922</v>
       </c>
       <c r="B727">
-        <v>335.576589880221</v>
+        <v>334.9766594393689</v>
       </c>
       <c r="C727">
         <v>21438.99</v>
@@ -7493,7 +7493,7 @@
         <v>43952</v>
       </c>
       <c r="B728">
-        <v>425.0232118983376</v>
+        <v>424.1125449663939</v>
       </c>
       <c r="C728">
         <v>26490.73</v>
@@ -7507,7 +7507,7 @@
         <v>43983</v>
       </c>
       <c r="B729">
-        <v>325.9055634815653</v>
+        <v>325.133513407121</v>
       </c>
       <c r="C729">
         <v>28737.92</v>
@@ -7521,7 +7521,7 @@
         <v>44013</v>
       </c>
       <c r="B730">
-        <v>309.3038143411002</v>
+        <v>308.7049646398453</v>
       </c>
       <c r="C730">
         <v>26888.29</v>
@@ -7535,7 +7535,7 @@
         <v>44044</v>
       </c>
       <c r="B731">
-        <v>305.2678130347502</v>
+        <v>304.4329421174711</v>
       </c>
       <c r="C731">
         <v>20430.03</v>
@@ -7549,7 +7549,7 @@
         <v>44075</v>
       </c>
       <c r="B732">
-        <v>328.9058660150179</v>
+        <v>328.0033306297782</v>
       </c>
       <c r="C732">
         <v>26409.8</v>
@@ -7563,7 +7563,7 @@
         <v>44105</v>
       </c>
       <c r="B733">
-        <v>313.9432334315234</v>
+        <v>313.184656510125</v>
       </c>
       <c r="C733">
         <v>28194.52</v>
@@ -7577,7 +7577,7 @@
         <v>44136</v>
       </c>
       <c r="B734">
-        <v>422.878764847364</v>
+        <v>421.6440340990687</v>
       </c>
       <c r="C734">
         <v>25062.17</v>
@@ -7591,7 +7591,7 @@
         <v>44166</v>
       </c>
       <c r="B735">
-        <v>315.9257692684623</v>
+        <v>315.1138397972732</v>
       </c>
       <c r="C735">
         <v>14886.35</v>
@@ -7605,7 +7605,7 @@
         <v>44197</v>
       </c>
       <c r="B736">
-        <v>284.023490862621</v>
+        <v>283.3187814552742</v>
       </c>
       <c r="C736">
         <v>11956.53</v>
@@ -7619,7 +7619,7 @@
         <v>44228</v>
       </c>
       <c r="B737">
-        <v>200.6125493669494</v>
+        <v>200.1679891856918</v>
       </c>
       <c r="C737">
         <v>9050.271000000001</v>
@@ -7633,7 +7633,7 @@
         <v>44256</v>
       </c>
       <c r="B738">
-        <v>222.0983122796519</v>
+        <v>221.5326150185953</v>
       </c>
       <c r="C738">
         <v>13602.12</v>
@@ -7647,7 +7647,7 @@
         <v>44287</v>
       </c>
       <c r="B739">
-        <v>207.0239541429045</v>
+        <v>206.4836958067224</v>
       </c>
       <c r="C739">
         <v>14889.97</v>
@@ -7661,7 +7661,7 @@
         <v>44317</v>
       </c>
       <c r="B740">
-        <v>180.3003668438903</v>
+        <v>179.8988429019772</v>
       </c>
       <c r="C740">
         <v>15392.93</v>
@@ -7675,7 +7675,7 @@
         <v>44348</v>
       </c>
       <c r="B741">
-        <v>181.639061906586</v>
+        <v>181.2342842132373</v>
       </c>
       <c r="C741">
         <v>21543.41</v>
@@ -7689,7 +7689,7 @@
         <v>44378</v>
       </c>
       <c r="B742">
-        <v>191.0856113273062</v>
+        <v>190.6583625160694</v>
       </c>
       <c r="C742">
         <v>19371.39</v>
@@ -7703,7 +7703,7 @@
         <v>44409</v>
       </c>
       <c r="B743">
-        <v>210.7892699137883</v>
+        <v>210.2341172280997</v>
       </c>
       <c r="C743">
         <v>17169.7</v>
@@ -7717,7 +7717,7 @@
         <v>44440</v>
       </c>
       <c r="B744">
-        <v>220.5535740355701</v>
+        <v>220.0526691068803</v>
       </c>
       <c r="C744">
         <v>23904</v>
@@ -7731,7 +7731,7 @@
         <v>44470</v>
       </c>
       <c r="B745">
-        <v>196.0467364909717</v>
+        <v>195.5307381228812</v>
       </c>
       <c r="C745">
         <v>10477.78</v>
@@ -7745,7 +7745,7 @@
         <v>44501</v>
       </c>
       <c r="B746">
-        <v>235.5484715965082</v>
+        <v>234.9165445577295</v>
       </c>
       <c r="C746">
         <v>14556.52</v>
@@ -7759,7 +7759,7 @@
         <v>44531</v>
       </c>
       <c r="B747">
-        <v>268.4616988956613</v>
+        <v>267.8143930604346</v>
       </c>
       <c r="C747">
         <v>28225.75</v>
@@ -7773,7 +7773,7 @@
         <v>44562</v>
       </c>
       <c r="B748">
-        <v>234.4592535592012</v>
+        <v>233.8661103275871</v>
       </c>
       <c r="C748">
         <v>25576.78</v>
@@ -7787,7 +7787,7 @@
         <v>44593</v>
       </c>
       <c r="B749">
-        <v>186.8265155168883</v>
+        <v>186.5148530451768</v>
       </c>
       <c r="C749">
         <v>25212.72</v>
@@ -7801,7 +7801,7 @@
         <v>44621</v>
       </c>
       <c r="B750">
-        <v>306.5956849936787</v>
+        <v>305.9287663785963</v>
       </c>
       <c r="C750">
         <v>27256.75</v>
@@ -7815,7 +7815,7 @@
         <v>44652</v>
       </c>
       <c r="B751">
-        <v>288.9671095776354</v>
+        <v>288.3391639672753</v>
       </c>
       <c r="C751">
         <v>41669.1</v>
@@ -7829,7 +7829,7 @@
         <v>44682</v>
       </c>
       <c r="B752">
-        <v>291.5508821770336</v>
+        <v>290.8332859373045</v>
       </c>
       <c r="C752">
         <v>25064.35</v>
@@ -7843,7 +7843,7 @@
         <v>44713</v>
       </c>
       <c r="B753">
-        <v>266.2320802190257</v>
+        <v>265.6497128228669</v>
       </c>
       <c r="C753">
         <v>23022.65</v>
@@ -7857,7 +7857,7 @@
         <v>44743</v>
       </c>
       <c r="B754">
-        <v>306.4909894804255</v>
+        <v>305.8102585798032</v>
       </c>
       <c r="C754">
         <v>19588.13</v>
@@ -7871,7 +7871,7 @@
         <v>44774</v>
       </c>
       <c r="B755">
-        <v>242.563560941931</v>
+        <v>242.0802472826197</v>
       </c>
       <c r="C755">
         <v>31577.91</v>
@@ -7885,7 +7885,7 @@
         <v>44805</v>
       </c>
       <c r="B756">
-        <v>254.7496900239954</v>
+        <v>254.3224621816378</v>
       </c>
       <c r="C756">
         <v>22559.72</v>
@@ -7899,7 +7899,7 @@
         <v>44835</v>
       </c>
       <c r="B757">
-        <v>269.9497378152338</v>
+        <v>269.3816730800331</v>
       </c>
       <c r="C757">
         <v>28962.72</v>
@@ -7913,7 +7913,7 @@
         <v>44866</v>
       </c>
       <c r="B758">
-        <v>328.2976158611773</v>
+        <v>327.4263194628471</v>
       </c>
       <c r="C758">
         <v>34628.48</v>
@@ -7927,7 +7927,7 @@
         <v>44896</v>
       </c>
       <c r="B759">
-        <v>256.7122095015598</v>
+        <v>256.1258688829618</v>
       </c>
       <c r="C759">
         <v>17405.95</v>
@@ -7941,7 +7941,7 @@
         <v>44927</v>
       </c>
       <c r="B760">
-        <v>229.9478413661854</v>
+        <v>229.4347090707321</v>
       </c>
       <c r="C760">
         <v>29339.84</v>
@@ -7955,7 +7955,7 @@
         <v>44958</v>
       </c>
       <c r="B761">
-        <v>264.2695590895259</v>
+        <v>263.5794920922101</v>
       </c>
       <c r="C761">
         <v>32027.81</v>
@@ -7969,7 +7969,7 @@
         <v>44986</v>
       </c>
       <c r="B762">
-        <v>340.9567395938898</v>
+        <v>339.9825171873146</v>
       </c>
       <c r="C762">
         <v>17736.47</v>
@@ -7983,7 +7983,7 @@
         <v>45017</v>
       </c>
       <c r="B763">
-        <v>285.2195103065358</v>
+        <v>284.4818161033235</v>
       </c>
       <c r="C763">
         <v>37638.8</v>
@@ -7997,7 +7997,7 @@
         <v>45047</v>
       </c>
       <c r="B764">
-        <v>214.4999115646287</v>
+        <v>214.0624366053083</v>
       </c>
       <c r="C764">
         <v>37309.42</v>
@@ -8011,7 +8011,7 @@
         <v>45078</v>
       </c>
       <c r="B765">
-        <v>239.0165934222418</v>
+        <v>238.4918358182614</v>
       </c>
       <c r="C765">
         <v>17679.01</v>
@@ -8025,7 +8025,7 @@
         <v>45108</v>
       </c>
       <c r="B766">
-        <v>203.7424290637706</v>
+        <v>203.2750010433726</v>
       </c>
       <c r="C766">
         <v>15649.48</v>
@@ -8039,7 +8039,7 @@
         <v>45139</v>
       </c>
       <c r="B767">
-        <v>189.0482174751642</v>
+        <v>188.6206020614568</v>
       </c>
       <c r="C767">
         <v>22258</v>
@@ -8053,7 +8053,7 @@
         <v>45170</v>
       </c>
       <c r="B768">
-        <v>213.8582975090245</v>
+        <v>213.4214422189196</v>
       </c>
       <c r="C768">
         <v>16389.48</v>
@@ -8067,7 +8067,7 @@
         <v>45200</v>
       </c>
       <c r="B769">
-        <v>199.8491867911129</v>
+        <v>199.4589966404571</v>
       </c>
       <c r="C769">
         <v>15354.48</v>
@@ -8081,7 +8081,7 @@
         <v>45231</v>
       </c>
       <c r="B770">
-        <v>221.7164301914602</v>
+        <v>221.2394737275754</v>
       </c>
       <c r="C770">
         <v>17278.77</v>
@@ -8095,7 +8095,7 @@
         <v>45261</v>
       </c>
       <c r="B771">
-        <v>250.6849982388583</v>
+        <v>250.0928694319573</v>
       </c>
       <c r="C771">
         <v>17108.95</v>
@@ -8109,7 +8109,7 @@
         <v>45292</v>
       </c>
       <c r="B772">
-        <v>263.9307657199365</v>
+        <v>263.2454120216013</v>
       </c>
       <c r="C772">
         <v>17865.73</v>
@@ -8123,7 +8123,7 @@
         <v>45323</v>
       </c>
       <c r="B773">
-        <v>182.3339728773556</v>
+        <v>182.0078607190419</v>
       </c>
       <c r="C773">
         <v>16358.07</v>
@@ -8137,7 +8137,7 @@
         <v>45352</v>
       </c>
       <c r="B774">
-        <v>190.3504001283818</v>
+        <v>189.8975372153553</v>
       </c>
       <c r="C774">
         <v>17273.86</v>
@@ -8151,7 +8151,7 @@
         <v>45383</v>
       </c>
       <c r="B775">
-        <v>178.4600678900442</v>
+        <v>178.1456803307008</v>
       </c>
       <c r="C775">
         <v>16746.02</v>
@@ -8165,7 +8165,7 @@
         <v>45413</v>
       </c>
       <c r="B776">
-        <v>191.7909143576972</v>
+        <v>191.4040114292682</v>
       </c>
       <c r="C776">
         <v>15083.26</v>
@@ -8179,7 +8179,7 @@
         <v>45444</v>
       </c>
       <c r="B777">
-        <v>175.8151151947228</v>
+        <v>175.6118807949544</v>
       </c>
       <c r="C777">
         <v>14606.01</v>
@@ -8193,7 +8193,7 @@
         <v>45474</v>
       </c>
       <c r="B778">
-        <v>245.4202814297943</v>
+        <v>244.8646092924179</v>
       </c>
       <c r="C778">
         <v>15929.92</v>
@@ -8207,7 +8207,7 @@
         <v>45505</v>
       </c>
       <c r="B779">
-        <v>202.5762713818185</v>
+        <v>202.1984665853855</v>
       </c>
       <c r="C779">
         <v>21425.35</v>
@@ -8221,7 +8221,7 @@
         <v>45536</v>
       </c>
       <c r="B780">
-        <v>212.0140658625617</v>
+        <v>211.6260664172923</v>
       </c>
       <c r="C780">
         <v>20372.42</v>
@@ -8235,7 +8235,7 @@
         <v>45566</v>
       </c>
       <c r="B781">
-        <v>215.8275729789033</v>
+        <v>215.3047781947442</v>
       </c>
       <c r="C781">
         <v>21669.22</v>
@@ -8249,7 +8249,7 @@
         <v>45597</v>
       </c>
       <c r="B782">
-        <v>282.5131666539344</v>
+        <v>281.9809491690933</v>
       </c>
       <c r="C782">
         <v>24333.03</v>
@@ -8263,7 +8263,7 @@
         <v>45627</v>
       </c>
       <c r="B783">
-        <v>337.5859169100238</v>
+        <v>336.7250888039603</v>
       </c>
       <c r="C783">
         <v>30375.61</v>
@@ -8277,7 +8277,7 @@
         <v>45658</v>
       </c>
       <c r="B784">
-        <v>310.5167715595696</v>
+        <v>309.6800077582786</v>
       </c>
       <c r="C784">
         <v>41383.23</v>
@@ -8291,7 +8291,7 @@
         <v>45689</v>
       </c>
       <c r="B785">
-        <v>320.8345110480037</v>
+        <v>319.9595703778059</v>
       </c>
       <c r="C785">
         <v>48816.02</v>
@@ -8305,7 +8305,7 @@
         <v>45717</v>
       </c>
       <c r="B786">
-        <v>460.0060886216664</v>
+        <v>459.3789618456659</v>
       </c>
       <c r="C786">
         <v>53189.5</v>
@@ -8319,7 +8319,7 @@
         <v>45748</v>
       </c>
       <c r="B787">
-        <v>586.1978822275637</v>
+        <v>584.6521275425574</v>
       </c>
       <c r="C787">
         <v>72733.48</v>
@@ -8333,7 +8333,7 @@
         <v>45778</v>
       </c>
       <c r="B788">
-        <v>486.333461737259</v>
+        <v>484.7157843271671</v>
       </c>
       <c r="C788">
         <v>77997.67999999999</v>
@@ -8347,7 +8347,7 @@
         <v>45809</v>
       </c>
       <c r="B789">
-        <v>359.4442257999357</v>
+        <v>358.5588823693955</v>
       </c>
       <c r="C789">
         <v>84305.33</v>
@@ -8361,7 +8361,7 @@
         <v>45839</v>
       </c>
       <c r="B790">
-        <v>396.0146503954984</v>
+        <v>395.3445338948545</v>
       </c>
       <c r="C790">
         <v>95509.25999999999</v>
@@ -8375,7 +8375,7 @@
         <v>45870</v>
       </c>
       <c r="B791">
-        <v>326.8352886643954</v>
+        <v>332.0747970501799</v>
       </c>
       <c r="C791">
         <v>105558.3</v>
@@ -8389,7 +8389,7 @@
         <v>45901</v>
       </c>
       <c r="B792">
-        <v>291.0521904773695</v>
+        <v>297.6189053615164</v>
       </c>
       <c r="C792">
         <v>122422.5</v>
@@ -8402,11 +8402,36 @@
       <c r="A793" s="2">
         <v>45931</v>
       </c>
+      <c r="B793">
+        <v>404.5629347054088</v>
+      </c>
       <c r="C793">
         <v>110331.9</v>
       </c>
       <c r="D793">
         <v>426.213747796827</v>
+      </c>
+    </row>
+    <row r="794" spans="1:4">
+      <c r="A794" s="2">
+        <v>45962</v>
+      </c>
+      <c r="C794">
+        <v>91874.55</v>
+      </c>
+      <c r="D794">
+        <v>342.788766101217</v>
+      </c>
+    </row>
+    <row r="795" spans="1:4">
+      <c r="A795" s="2">
+        <v>45992</v>
+      </c>
+      <c r="C795">
+        <v>90758.05</v>
+      </c>
+      <c r="D795">
+        <v>308.280990542199</v>
       </c>
     </row>
   </sheetData>

--- a/00.data/01.incertezas/merged_uncertainty_indices.xlsx
+++ b/00.data/01.incertezas/merged_uncertainty_indices.xlsx
@@ -389,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D795"/>
+  <dimension ref="A1:D797"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -3969,7 +3969,7 @@
         <v>35431</v>
       </c>
       <c r="B448">
-        <v>78.95696233854623</v>
+        <v>79.85677211659535</v>
       </c>
       <c r="D448">
         <v>26.79430816055774</v>
@@ -3980,7 +3980,7 @@
         <v>35462</v>
       </c>
       <c r="B449">
-        <v>75.59514446381327</v>
+        <v>75.8282195848044</v>
       </c>
       <c r="D449">
         <v>35.15929037279584</v>
@@ -3991,7 +3991,7 @@
         <v>35490</v>
       </c>
       <c r="B450">
-        <v>64.57199544827893</v>
+        <v>64.85054712899961</v>
       </c>
       <c r="D450">
         <v>30.29108998670148</v>
@@ -4002,7 +4002,7 @@
         <v>35521</v>
       </c>
       <c r="B451">
-        <v>71.66583073570435</v>
+        <v>71.85586285247311</v>
       </c>
       <c r="D451">
         <v>32.08635956621232</v>
@@ -4013,7 +4013,7 @@
         <v>35551</v>
       </c>
       <c r="B452">
-        <v>82.64486561406692</v>
+        <v>82.0583649904861</v>
       </c>
       <c r="D452">
         <v>33.63899132861557</v>
@@ -4024,7 +4024,7 @@
         <v>35582</v>
       </c>
       <c r="B453">
-        <v>82.92313197264333</v>
+        <v>82.50080065782926</v>
       </c>
       <c r="D453">
         <v>34.3660237997538</v>
@@ -4035,7 +4035,7 @@
         <v>35612</v>
       </c>
       <c r="B454">
-        <v>66.46854043161487</v>
+        <v>66.69537705451214</v>
       </c>
       <c r="D454">
         <v>30.62748373705926</v>
@@ -4046,7 +4046,7 @@
         <v>35643</v>
       </c>
       <c r="B455">
-        <v>58.19720045036387</v>
+        <v>59.47591748941928</v>
       </c>
       <c r="D455">
         <v>27.38005526249686</v>
@@ -4057,7 +4057,7 @@
         <v>35674</v>
       </c>
       <c r="B456">
-        <v>61.05889296115504</v>
+        <v>63.03829718934998</v>
       </c>
       <c r="D456">
         <v>33.76015819045553</v>
@@ -4068,7 +4068,7 @@
         <v>35704</v>
       </c>
       <c r="B457">
-        <v>76.07947878990885</v>
+        <v>77.7616262046798</v>
       </c>
       <c r="D457">
         <v>36.76305761040125</v>
@@ -4079,7 +4079,7 @@
         <v>35735</v>
       </c>
       <c r="B458">
-        <v>84.84888851015464</v>
+        <v>90.14153883760599</v>
       </c>
       <c r="D458">
         <v>47.08053373710609</v>
@@ -4090,7 +4090,7 @@
         <v>35765</v>
       </c>
       <c r="B459">
-        <v>93.28884178580232</v>
+        <v>98.93286306015311</v>
       </c>
       <c r="D459">
         <v>31.96717400639344</v>
@@ -4101,7 +4101,7 @@
         <v>35796</v>
       </c>
       <c r="B460">
-        <v>89.09108904679188</v>
+        <v>94.04651555295209</v>
       </c>
       <c r="D460">
         <v>30.68600263672319</v>
@@ -4112,7 +4112,7 @@
         <v>35827</v>
       </c>
       <c r="B461">
-        <v>76.39437937826045</v>
+        <v>79.58862093038459</v>
       </c>
       <c r="D461">
         <v>25.52968123687727</v>
@@ -4123,7 +4123,7 @@
         <v>35855</v>
       </c>
       <c r="B462">
-        <v>76.67862922640539</v>
+        <v>80.68981247219646</v>
       </c>
       <c r="D462">
         <v>29.84241487397484</v>
@@ -4134,7 +4134,7 @@
         <v>35886</v>
       </c>
       <c r="B463">
-        <v>72.31512024128168</v>
+        <v>76.42355610934864</v>
       </c>
       <c r="D463">
         <v>30.76646679691886</v>
@@ -4145,7 +4145,7 @@
         <v>35916</v>
       </c>
       <c r="B464">
-        <v>78.74670606033294</v>
+        <v>82.74596253097332</v>
       </c>
       <c r="D464">
         <v>25.65856996236743</v>
@@ -4156,7 +4156,7 @@
         <v>35947</v>
       </c>
       <c r="B465">
-        <v>76.91365501129597</v>
+        <v>80.89332648684088</v>
       </c>
       <c r="D465">
         <v>33.53731570809468</v>
@@ -4167,7 +4167,7 @@
         <v>35977</v>
       </c>
       <c r="B466">
-        <v>92.63473093776973</v>
+        <v>97.95443459725901</v>
       </c>
       <c r="D466">
         <v>36.33124721655767</v>
@@ -4178,7 +4178,7 @@
         <v>36008</v>
       </c>
       <c r="B467">
-        <v>104.0340521745058</v>
+        <v>109.4752598676489</v>
       </c>
       <c r="D467">
         <v>32.31396056760174</v>
@@ -4189,7 +4189,7 @@
         <v>36039</v>
       </c>
       <c r="B468">
-        <v>142.4562141616617</v>
+        <v>145.1570251725634</v>
       </c>
       <c r="D468">
         <v>32.45070422535211</v>
@@ -4200,7 +4200,7 @@
         <v>36069</v>
       </c>
       <c r="B469">
-        <v>108.8959631388216</v>
+        <v>113.2163537518497</v>
       </c>
       <c r="D469">
         <v>33.76769557123685</v>
@@ -4211,7 +4211,7 @@
         <v>36100</v>
       </c>
       <c r="B470">
-        <v>90.27099885748649</v>
+        <v>91.80712719398637</v>
       </c>
       <c r="D470">
         <v>30.20467045352087</v>
@@ -4222,7 +4222,7 @@
         <v>36130</v>
       </c>
       <c r="B471">
-        <v>89.14261472301666</v>
+        <v>90.79967786071832</v>
       </c>
       <c r="D471">
         <v>35.70021095579201</v>
@@ -4233,7 +4233,7 @@
         <v>36161</v>
       </c>
       <c r="B472">
-        <v>91.2927053674953</v>
+        <v>92.33123506882249</v>
       </c>
       <c r="D472">
         <v>34.19077996282613</v>
@@ -4244,7 +4244,7 @@
         <v>36192</v>
       </c>
       <c r="B473">
-        <v>74.58134882571804</v>
+        <v>75.77428859910488</v>
       </c>
       <c r="D473">
         <v>34.41053261520048</v>
@@ -4255,7 +4255,7 @@
         <v>36220</v>
       </c>
       <c r="B474">
-        <v>56.43764902904483</v>
+        <v>57.54867602139358</v>
       </c>
       <c r="D474">
         <v>39.11342894393742</v>
@@ -4266,7 +4266,7 @@
         <v>36251</v>
       </c>
       <c r="B475">
-        <v>63.26337290084778</v>
+        <v>64.03573239636394</v>
       </c>
       <c r="D475">
         <v>34.92721618820136</v>
@@ -4277,7 +4277,7 @@
         <v>36281</v>
       </c>
       <c r="B476">
-        <v>67.44230137886983</v>
+        <v>69.4133589636459</v>
       </c>
       <c r="D476">
         <v>30.32059571052749</v>
@@ -4288,7 +4288,7 @@
         <v>36312</v>
       </c>
       <c r="B477">
-        <v>66.82881734789933</v>
+        <v>67.60325367294196</v>
       </c>
       <c r="D477">
         <v>33.0491863062406</v>
@@ -4299,7 +4299,7 @@
         <v>36342</v>
       </c>
       <c r="B478">
-        <v>69.91170662410919</v>
+        <v>70.33657621800415</v>
       </c>
       <c r="D478">
         <v>31.69572107765451</v>
@@ -4310,7 +4310,7 @@
         <v>36373</v>
       </c>
       <c r="B479">
-        <v>67.58128577468824</v>
+        <v>67.9520900200344</v>
       </c>
       <c r="D479">
         <v>32.25347436323104</v>
@@ -4321,7 +4321,7 @@
         <v>36404</v>
       </c>
       <c r="B480">
-        <v>61.43656059243794</v>
+        <v>62.11164401500725</v>
       </c>
       <c r="D480">
         <v>30.38519072550486</v>
@@ -4332,7 +4332,7 @@
         <v>36434</v>
       </c>
       <c r="B481">
-        <v>65.96162063096185</v>
+        <v>66.51659657286466</v>
       </c>
       <c r="D481">
         <v>32.63973888208894</v>
@@ -4343,7 +4343,7 @@
         <v>36465</v>
       </c>
       <c r="B482">
-        <v>64.88000296033906</v>
+        <v>64.9132137532964</v>
       </c>
       <c r="D482">
         <v>48.94195531386688</v>
@@ -4354,7 +4354,7 @@
         <v>36495</v>
       </c>
       <c r="B483">
-        <v>57.84974874346484</v>
+        <v>57.96883747083193</v>
       </c>
       <c r="D483">
         <v>41.58353964858303</v>
@@ -4365,7 +4365,7 @@
         <v>36526</v>
       </c>
       <c r="B484">
-        <v>66.36177028012447</v>
+        <v>65.99470916016021</v>
       </c>
       <c r="D484">
         <v>32.11734816164134</v>
@@ -4376,7 +4376,7 @@
         <v>36557</v>
       </c>
       <c r="B485">
-        <v>55.56510488772031</v>
+        <v>55.47122545909148</v>
       </c>
       <c r="D485">
         <v>28.17585620597523</v>
@@ -4387,7 +4387,7 @@
         <v>36586</v>
       </c>
       <c r="B486">
-        <v>60.52443734103579</v>
+        <v>60.1701933550543</v>
       </c>
       <c r="D486">
         <v>36.83850616548651</v>
@@ -4398,7 +4398,7 @@
         <v>36617</v>
       </c>
       <c r="B487">
-        <v>61.60965122757217</v>
+        <v>61.53670800173642</v>
       </c>
       <c r="D487">
         <v>35.28104006572906</v>
@@ -4409,7 +4409,7 @@
         <v>36647</v>
       </c>
       <c r="B488">
-        <v>81.41318862003649</v>
+        <v>81.25756982879226</v>
       </c>
       <c r="D488">
         <v>49.32756293917819</v>
@@ -4420,7 +4420,7 @@
         <v>36678</v>
       </c>
       <c r="B489">
-        <v>85.18713308769051</v>
+        <v>84.96854919459837</v>
       </c>
       <c r="D489">
         <v>27.36688135513247</v>
@@ -4431,7 +4431,7 @@
         <v>36708</v>
       </c>
       <c r="B490">
-        <v>63.40839146880375</v>
+        <v>63.18466140574696</v>
       </c>
       <c r="D490">
         <v>31.94444444444445</v>
@@ -4442,7 +4442,7 @@
         <v>36739</v>
       </c>
       <c r="B491">
-        <v>52.78984019296506</v>
+        <v>52.64268308123221</v>
       </c>
       <c r="D491">
         <v>29.21261803935777</v>
@@ -4453,7 +4453,7 @@
         <v>36770</v>
       </c>
       <c r="B492">
-        <v>61.66076453839437</v>
+        <v>61.48888995243826</v>
       </c>
       <c r="D492">
         <v>33.43174713442168</v>
@@ -4464,7 +4464,7 @@
         <v>36800</v>
       </c>
       <c r="B493">
-        <v>67.71565168032539</v>
+        <v>67.55242452535198</v>
       </c>
       <c r="D493">
         <v>25.48113774315842</v>
@@ -4475,7 +4475,7 @@
         <v>36831</v>
       </c>
       <c r="B494">
-        <v>93.83410154139268</v>
+        <v>93.90535281026389</v>
       </c>
       <c r="D494">
         <v>26.90486439948343</v>
@@ -4486,7 +4486,7 @@
         <v>36861</v>
       </c>
       <c r="B495">
-        <v>94.65584094881976</v>
+        <v>94.42008441707864</v>
       </c>
       <c r="D495">
         <v>29.81667404318759</v>
@@ -4497,7 +4497,7 @@
         <v>36892</v>
       </c>
       <c r="B496">
-        <v>93.34856320021318</v>
+        <v>93.15764527087241</v>
       </c>
       <c r="D496">
         <v>25.98787232624775</v>
@@ -4508,7 +4508,7 @@
         <v>36923</v>
       </c>
       <c r="B497">
-        <v>93.5879803245857</v>
+        <v>93.42270621124335</v>
       </c>
       <c r="D497">
         <v>20.64627646804629</v>
@@ -4519,7 +4519,7 @@
         <v>36951</v>
       </c>
       <c r="B498">
-        <v>104.0867042354465</v>
+        <v>103.9950236587611</v>
       </c>
       <c r="D498">
         <v>25.07863640227833</v>
@@ -4530,7 +4530,7 @@
         <v>36982</v>
       </c>
       <c r="B499">
-        <v>95.95988126881788</v>
+        <v>96.11079074393061</v>
       </c>
       <c r="D499">
         <v>34.3147347471004</v>
@@ -4541,7 +4541,7 @@
         <v>37012</v>
       </c>
       <c r="B500">
-        <v>76.22725393721501</v>
+        <v>76.15390185845823</v>
       </c>
       <c r="D500">
         <v>27.79333821691731</v>
@@ -4552,7 +4552,7 @@
         <v>37043</v>
       </c>
       <c r="B501">
-        <v>70.38255144570097</v>
+        <v>70.29722252117553</v>
       </c>
       <c r="D501">
         <v>30.15970937007334</v>
@@ -4563,7 +4563,7 @@
         <v>37073</v>
       </c>
       <c r="B502">
-        <v>89.31537722768631</v>
+        <v>89.23964460290219</v>
       </c>
       <c r="D502">
         <v>34.29895712630359</v>
@@ -4574,7 +4574,7 @@
         <v>37104</v>
       </c>
       <c r="B503">
-        <v>78.62556900255626</v>
+        <v>78.61485728821751</v>
       </c>
       <c r="D503">
         <v>28.28561572956192</v>
@@ -4585,7 +4585,7 @@
         <v>37135</v>
       </c>
       <c r="B504">
-        <v>157.8663235188563</v>
+        <v>158.047834133464</v>
       </c>
       <c r="D504">
         <v>24.12961047914512</v>
@@ -4596,7 +4596,7 @@
         <v>37165</v>
       </c>
       <c r="B505">
-        <v>149.6552580182867</v>
+        <v>149.9112684144884</v>
       </c>
       <c r="D505">
         <v>24.04201024948858</v>
@@ -4607,7 +4607,7 @@
         <v>37196</v>
       </c>
       <c r="B506">
-        <v>116.1812653346947</v>
+        <v>116.2000121782874</v>
       </c>
       <c r="D506">
         <v>33.66046643789207</v>
@@ -4618,7 +4618,7 @@
         <v>37226</v>
       </c>
       <c r="B507">
-        <v>100.5784433640315</v>
+        <v>100.2618215617448</v>
       </c>
       <c r="D507">
         <v>34.28891325138206</v>
@@ -4629,7 +4629,7 @@
         <v>37257</v>
       </c>
       <c r="B508">
-        <v>99.51953709586206</v>
+        <v>98.9840580540841</v>
       </c>
       <c r="D508">
         <v>31.63412870571222</v>
@@ -4640,7 +4640,7 @@
         <v>37288</v>
       </c>
       <c r="B509">
-        <v>80.76035068362273</v>
+        <v>80.57971421332604</v>
       </c>
       <c r="D509">
         <v>31.94888178913738</v>
@@ -4651,7 +4651,7 @@
         <v>37316</v>
       </c>
       <c r="B510">
-        <v>74.59110008680135</v>
+        <v>74.35185711429997</v>
       </c>
       <c r="D510">
         <v>53.87744504067855</v>
@@ -4662,7 +4662,7 @@
         <v>37347</v>
       </c>
       <c r="B511">
-        <v>79.13124498937587</v>
+        <v>78.95332169794007</v>
       </c>
       <c r="D511">
         <v>36.55340475424158</v>
@@ -4673,7 +4673,7 @@
         <v>37377</v>
       </c>
       <c r="B512">
-        <v>77.96673128864585</v>
+        <v>77.57839390975076</v>
       </c>
       <c r="D512">
         <v>41.12330393860093</v>
@@ -4684,7 +4684,7 @@
         <v>37408</v>
       </c>
       <c r="B513">
-        <v>88.84046706569988</v>
+        <v>88.61970614649796</v>
       </c>
       <c r="D513">
         <v>39.78324987996433</v>
@@ -4695,7 +4695,7 @@
         <v>37438</v>
       </c>
       <c r="B514">
-        <v>94.05573162843365</v>
+        <v>93.91492422318586</v>
       </c>
       <c r="D514">
         <v>40.61059219798858</v>
@@ -4706,7 +4706,7 @@
         <v>37469</v>
       </c>
       <c r="B515">
-        <v>98.65856547395823</v>
+        <v>98.41331902671972</v>
       </c>
       <c r="D515">
         <v>34.50802429743081</v>
@@ -4717,7 +4717,7 @@
         <v>37500</v>
       </c>
       <c r="B516">
-        <v>113.8302108290269</v>
+        <v>113.8264807576451</v>
       </c>
       <c r="D516">
         <v>27.68700072621641</v>
@@ -4728,7 +4728,7 @@
         <v>37530</v>
       </c>
       <c r="B517">
-        <v>113.1411263794254</v>
+        <v>112.8039729028996</v>
       </c>
       <c r="D517">
         <v>32.54575425842174</v>
@@ -4739,7 +4739,7 @@
         <v>37561</v>
       </c>
       <c r="B518">
-        <v>114.3848004180443</v>
+        <v>114.2761269161338</v>
       </c>
       <c r="D518">
         <v>31.85472511755911</v>
@@ -4750,7 +4750,7 @@
         <v>37591</v>
       </c>
       <c r="B519">
-        <v>115.9145009018859</v>
+        <v>115.794311403409</v>
       </c>
       <c r="D519">
         <v>24.72299013327939</v>
@@ -4761,7 +4761,7 @@
         <v>37622</v>
       </c>
       <c r="B520">
-        <v>113.237606493776</v>
+        <v>113.0059590867023</v>
       </c>
       <c r="D520">
         <v>25.27453372842949</v>
@@ -4772,7 +4772,7 @@
         <v>37653</v>
       </c>
       <c r="B521">
-        <v>122.6716517540427</v>
+        <v>122.6054305162209</v>
       </c>
       <c r="D521">
         <v>31.57377739317538</v>
@@ -4783,7 +4783,7 @@
         <v>37681</v>
       </c>
       <c r="B522">
-        <v>154.9488312459112</v>
+        <v>154.9376072669874</v>
       </c>
       <c r="D522">
         <v>23.27466179007086</v>
@@ -4794,7 +4794,7 @@
         <v>37712</v>
       </c>
       <c r="B523">
-        <v>130.4096381371546</v>
+        <v>129.9284818446636</v>
       </c>
       <c r="D523">
         <v>16.24980785700169</v>
@@ -4805,7 +4805,7 @@
         <v>37742</v>
       </c>
       <c r="B524">
-        <v>101.6752723648004</v>
+        <v>101.3484222539913</v>
       </c>
       <c r="D524">
         <v>28.59866539561487</v>
@@ -4816,7 +4816,7 @@
         <v>37773</v>
       </c>
       <c r="B525">
-        <v>82.51226157747517</v>
+        <v>82.16275463023577</v>
       </c>
       <c r="D525">
         <v>32.85968028419182</v>
@@ -4827,7 +4827,7 @@
         <v>37803</v>
       </c>
       <c r="B526">
-        <v>82.56268589989422</v>
+        <v>82.04665516517915</v>
       </c>
       <c r="D526">
         <v>28.43494085532302</v>
@@ -4838,7 +4838,7 @@
         <v>37834</v>
       </c>
       <c r="B527">
-        <v>71.2245104450609</v>
+        <v>70.88787812527407</v>
       </c>
       <c r="D527">
         <v>24.55159244356544</v>
@@ -4849,7 +4849,7 @@
         <v>37865</v>
       </c>
       <c r="B528">
-        <v>76.20423551358773</v>
+        <v>75.88366416883068</v>
       </c>
       <c r="D528">
         <v>39.80838000134943</v>
@@ -4860,7 +4860,7 @@
         <v>37895</v>
       </c>
       <c r="B529">
-        <v>78.33202890196377</v>
+        <v>77.94070234192718</v>
       </c>
       <c r="D529">
         <v>31.40458547999754</v>
@@ -4871,7 +4871,7 @@
         <v>37926</v>
       </c>
       <c r="B530">
-        <v>75.20743852650411</v>
+        <v>74.87345948038501</v>
       </c>
       <c r="D530">
         <v>50.17905300853265</v>
@@ -4882,7 +4882,7 @@
         <v>37956</v>
       </c>
       <c r="B531">
-        <v>69.90059521921975</v>
+        <v>69.48689752268125</v>
       </c>
       <c r="D531">
         <v>46.6441488017279</v>
@@ -4893,7 +4893,7 @@
         <v>37987</v>
       </c>
       <c r="B532">
-        <v>76.72960464501551</v>
+        <v>76.3971676645036</v>
       </c>
       <c r="D532">
         <v>30.87917420265561</v>
@@ -4904,7 +4904,7 @@
         <v>38018</v>
       </c>
       <c r="B533">
-        <v>79.57467835557406</v>
+        <v>79.14747434293268</v>
       </c>
       <c r="D533">
         <v>35.39903333408972</v>
@@ -4915,7 +4915,7 @@
         <v>38047</v>
       </c>
       <c r="B534">
-        <v>74.99179717874699</v>
+        <v>74.67333893165596</v>
       </c>
       <c r="D534">
         <v>27.12360614801739</v>
@@ -4926,7 +4926,7 @@
         <v>38078</v>
       </c>
       <c r="B535">
-        <v>79.71451570607465</v>
+        <v>79.30857604012633</v>
       </c>
       <c r="D535">
         <v>28.38389214120986</v>
@@ -4937,7 +4937,7 @@
         <v>38108</v>
       </c>
       <c r="B536">
-        <v>94.40407034797813</v>
+        <v>94.25520456780551</v>
       </c>
       <c r="D536">
         <v>30.99539496989018</v>
@@ -4948,7 +4948,7 @@
         <v>38139</v>
       </c>
       <c r="B537">
-        <v>77.94931354769014</v>
+        <v>77.66189782927344</v>
       </c>
       <c r="D537">
         <v>22.94156782674528</v>
@@ -4959,7 +4959,7 @@
         <v>38169</v>
       </c>
       <c r="B538">
-        <v>71.8959741913867</v>
+        <v>71.39786784222038</v>
       </c>
       <c r="D538">
         <v>34.2544484803899</v>
@@ -4970,7 +4970,7 @@
         <v>38200</v>
       </c>
       <c r="B539">
-        <v>67.7691088923453</v>
+        <v>67.38990285223147</v>
       </c>
       <c r="D539">
         <v>28.87239753682358</v>
@@ -4981,7 +4981,7 @@
         <v>38231</v>
       </c>
       <c r="B540">
-        <v>73.99104320879279</v>
+        <v>73.89654888140556</v>
       </c>
       <c r="D540">
         <v>28.53132693679391</v>
@@ -4992,7 +4992,7 @@
         <v>38261</v>
       </c>
       <c r="B541">
-        <v>88.91488754351363</v>
+        <v>88.39725717312595</v>
       </c>
       <c r="D541">
         <v>29.3588205040288</v>
@@ -5003,7 +5003,7 @@
         <v>38292</v>
       </c>
       <c r="B542">
-        <v>80.41051972417775</v>
+        <v>79.98830338150351</v>
       </c>
       <c r="D542">
         <v>31.06233174570304</v>
@@ -5014,7 +5014,7 @@
         <v>38322</v>
       </c>
       <c r="B543">
-        <v>67.81839077567228</v>
+        <v>67.44393250983487</v>
       </c>
       <c r="D543">
         <v>30.10064904524504</v>
@@ -5025,7 +5025,7 @@
         <v>38353</v>
       </c>
       <c r="B544">
-        <v>64.1582961416923</v>
+        <v>63.87596101848698</v>
       </c>
       <c r="D544">
         <v>27.60942760942761</v>
@@ -5036,7 +5036,7 @@
         <v>38384</v>
       </c>
       <c r="B545">
-        <v>58.04976357155461</v>
+        <v>57.52738431418949</v>
       </c>
       <c r="D545">
         <v>19.91745056632751</v>
@@ -5047,7 +5047,7 @@
         <v>38412</v>
       </c>
       <c r="B546">
-        <v>56.26288623722446</v>
+        <v>56.01542760682149</v>
       </c>
       <c r="D546">
         <v>23.08211571543671</v>
@@ -5058,7 +5058,7 @@
         <v>38443</v>
       </c>
       <c r="B547">
-        <v>76.2271369552514</v>
+        <v>75.56248491872012</v>
       </c>
       <c r="D547">
         <v>31.50427234196868</v>
@@ -5069,7 +5069,7 @@
         <v>38473</v>
       </c>
       <c r="B548">
-        <v>63.96850365805867</v>
+        <v>63.77107034822789</v>
       </c>
       <c r="D548">
         <v>33.32582751632515</v>
@@ -5080,7 +5080,7 @@
         <v>38504</v>
       </c>
       <c r="B549">
-        <v>71.54013827333908</v>
+        <v>71.27016638081672</v>
       </c>
       <c r="D549">
         <v>38.64912119260146</v>
@@ -5091,7 +5091,7 @@
         <v>38534</v>
       </c>
       <c r="B550">
-        <v>64.82827143272166</v>
+        <v>64.38306901159986</v>
       </c>
       <c r="D550">
         <v>34.02699011596953</v>
@@ -5102,7 +5102,7 @@
         <v>38565</v>
       </c>
       <c r="B551">
-        <v>63.03783943454246</v>
+        <v>62.62064993622975</v>
       </c>
       <c r="D551">
         <v>22.78778574683969</v>
@@ -5113,7 +5113,7 @@
         <v>38596</v>
       </c>
       <c r="B552">
-        <v>92.15603106356983</v>
+        <v>91.58950895700282</v>
       </c>
       <c r="D552">
         <v>22.9043630566097</v>
@@ -5124,7 +5124,7 @@
         <v>38626</v>
       </c>
       <c r="B553">
-        <v>68.55257363673689</v>
+        <v>68.2708391931517</v>
       </c>
       <c r="D553">
         <v>34.35678872749413</v>
@@ -5135,7 +5135,7 @@
         <v>38657</v>
       </c>
       <c r="B554">
-        <v>64.41922156653618</v>
+        <v>63.99226536830357</v>
       </c>
       <c r="D554">
         <v>28.04210913437227</v>
@@ -5146,7 +5146,7 @@
         <v>38687</v>
       </c>
       <c r="B555">
-        <v>66.69313648398919</v>
+        <v>66.17083235985987</v>
       </c>
       <c r="D555">
         <v>32.10837161338709</v>
@@ -5157,7 +5157,7 @@
         <v>38718</v>
       </c>
       <c r="B556">
-        <v>78.19382276074207</v>
+        <v>77.37329681901413</v>
       </c>
       <c r="D556">
         <v>23.6623859955432</v>
@@ -5168,7 +5168,7 @@
         <v>38749</v>
       </c>
       <c r="B557">
-        <v>61.17564676235506</v>
+        <v>60.56384627761986</v>
       </c>
       <c r="D557">
         <v>24.28658166363085</v>
@@ -5179,7 +5179,7 @@
         <v>38777</v>
       </c>
       <c r="B558">
-        <v>61.38759010513453</v>
+        <v>60.92603361862709</v>
       </c>
       <c r="D558">
         <v>24.32237000679273</v>
@@ -5190,7 +5190,7 @@
         <v>38808</v>
       </c>
       <c r="B559">
-        <v>73.97299807720053</v>
+        <v>73.36178681543196</v>
       </c>
       <c r="D559">
         <v>26.57322923525538</v>
@@ -5201,7 +5201,7 @@
         <v>38838</v>
       </c>
       <c r="B560">
-        <v>62.92969155524965</v>
+        <v>62.77032433910549</v>
       </c>
       <c r="D560">
         <v>27.05389969246422</v>
@@ -5212,7 +5212,7 @@
         <v>38869</v>
       </c>
       <c r="B561">
-        <v>72.60546119208983</v>
+        <v>72.22139479277482</v>
       </c>
       <c r="D561">
         <v>26.84156474652227</v>
@@ -5223,7 +5223,7 @@
         <v>38899</v>
       </c>
       <c r="B562">
-        <v>71.10783515444068</v>
+        <v>70.71779023238923</v>
       </c>
       <c r="D562">
         <v>30.90742261071135</v>
@@ -5234,7 +5234,7 @@
         <v>38930</v>
       </c>
       <c r="B563">
-        <v>64.52191529076737</v>
+        <v>63.92850029743883</v>
       </c>
       <c r="D563">
         <v>20.98435711560473</v>
@@ -5245,7 +5245,7 @@
         <v>38961</v>
       </c>
       <c r="B564">
-        <v>57.06872100114555</v>
+        <v>56.84383495235468</v>
       </c>
       <c r="D564">
         <v>26.78760250957539</v>
@@ -5256,7 +5256,7 @@
         <v>38991</v>
       </c>
       <c r="B565">
-        <v>66.8131346661192</v>
+        <v>66.30464181559337</v>
       </c>
       <c r="D565">
         <v>23.69347414026536</v>
@@ -5267,7 +5267,7 @@
         <v>39022</v>
       </c>
       <c r="B566">
-        <v>64.197817726038</v>
+        <v>63.54811678931706</v>
       </c>
       <c r="D566">
         <v>25.99792936845738</v>
@@ -5278,7 +5278,7 @@
         <v>39052</v>
       </c>
       <c r="B567">
-        <v>61.83402713158144</v>
+        <v>61.12727039817307</v>
       </c>
       <c r="D567">
         <v>26.97579469233012</v>
@@ -5289,7 +5289,7 @@
         <v>39083</v>
       </c>
       <c r="B568">
-        <v>65.10275476479541</v>
+        <v>64.98475120935325</v>
       </c>
       <c r="D568">
         <v>22.50257343260001</v>
@@ -5300,7 +5300,7 @@
         <v>39114</v>
       </c>
       <c r="B569">
-        <v>57.81582193264634</v>
+        <v>57.652385488052</v>
       </c>
       <c r="D569">
         <v>27.55530375215679</v>
@@ -5311,7 +5311,7 @@
         <v>39142</v>
       </c>
       <c r="B570">
-        <v>67.46203687893771</v>
+        <v>66.96383236397095</v>
       </c>
       <c r="D570">
         <v>26.70623145400593</v>
@@ -5322,7 +5322,7 @@
         <v>39173</v>
       </c>
       <c r="B571">
-        <v>64.47515535128146</v>
+        <v>64.2964206237835</v>
       </c>
       <c r="D571">
         <v>30.43747420553033</v>
@@ -5333,7 +5333,7 @@
         <v>39203</v>
       </c>
       <c r="B572">
-        <v>57.16788180955429</v>
+        <v>56.96349815187086</v>
       </c>
       <c r="D572">
         <v>29.71149307194624</v>
@@ -5344,7 +5344,7 @@
         <v>39234</v>
       </c>
       <c r="B573">
-        <v>57.4221529384896</v>
+        <v>56.91811278046757</v>
       </c>
       <c r="D573">
         <v>34.27456563579319</v>
@@ -5355,7 +5355,7 @@
         <v>39264</v>
       </c>
       <c r="B574">
-        <v>52.30781027290943</v>
+        <v>51.82665390514378</v>
       </c>
       <c r="D574">
         <v>24.37064115527209</v>
@@ -5366,7 +5366,7 @@
         <v>39295</v>
       </c>
       <c r="B575">
-        <v>76.53048711892964</v>
+        <v>76.21038672503769</v>
       </c>
       <c r="D575">
         <v>23.17382836575204</v>
@@ -5377,7 +5377,7 @@
         <v>39326</v>
       </c>
       <c r="B576">
-        <v>94.27644296339074</v>
+        <v>93.75060409849098</v>
       </c>
       <c r="D576">
         <v>18.99715042743588</v>
@@ -5388,7 +5388,7 @@
         <v>39356</v>
       </c>
       <c r="B577">
-        <v>79.05457964207991</v>
+        <v>78.44035572909212</v>
       </c>
       <c r="D577">
         <v>25.88229602573716</v>
@@ -5399,7 +5399,7 @@
         <v>39387</v>
       </c>
       <c r="B578">
-        <v>79.24056570315167</v>
+        <v>78.61400850279466</v>
       </c>
       <c r="D578">
         <v>27.3709128569315</v>
@@ -5410,7 +5410,7 @@
         <v>39417</v>
       </c>
       <c r="B579">
-        <v>99.49764624699213</v>
+        <v>98.86014303939292</v>
       </c>
       <c r="D579">
         <v>21.81988206873263</v>
@@ -5421,7 +5421,7 @@
         <v>39448</v>
       </c>
       <c r="B580">
-        <v>132.6689860616669</v>
+        <v>132.1454851045315</v>
       </c>
       <c r="C580">
         <v>17245.12</v>
@@ -5435,7 +5435,7 @@
         <v>39479</v>
       </c>
       <c r="B581">
-        <v>97.69132053650709</v>
+        <v>97.44637425242199</v>
       </c>
       <c r="C581">
         <v>16059.42</v>
@@ -5449,7 +5449,7 @@
         <v>39508</v>
       </c>
       <c r="B582">
-        <v>129.4850567162087</v>
+        <v>128.3289080950304</v>
       </c>
       <c r="C582">
         <v>11944.98</v>
@@ -5463,7 +5463,7 @@
         <v>39539</v>
       </c>
       <c r="B583">
-        <v>98.84104878749949</v>
+        <v>97.97794116747787</v>
       </c>
       <c r="C583">
         <v>14277.65</v>
@@ -5477,7 +5477,7 @@
         <v>39569</v>
       </c>
       <c r="B584">
-        <v>81.64794905308241</v>
+        <v>80.94298813616471</v>
       </c>
       <c r="C584">
         <v>14969.42</v>
@@ -5491,7 +5491,7 @@
         <v>39600</v>
       </c>
       <c r="B585">
-        <v>90.88232603910964</v>
+        <v>90.93975132124542</v>
       </c>
       <c r="C585">
         <v>16455.88</v>
@@ -5505,7 +5505,7 @@
         <v>39630</v>
       </c>
       <c r="B586">
-        <v>108.0376549221824</v>
+        <v>107.0538156066983</v>
       </c>
       <c r="C586">
         <v>9904.023999999999</v>
@@ -5519,7 +5519,7 @@
         <v>39661</v>
       </c>
       <c r="B587">
-        <v>98.95006665152795</v>
+        <v>98.09956721048162</v>
       </c>
       <c r="C587">
         <v>12619.14</v>
@@ -5533,7 +5533,7 @@
         <v>39692</v>
       </c>
       <c r="B588">
-        <v>159.3776837881561</v>
+        <v>158.8178041126574</v>
       </c>
       <c r="C588">
         <v>13118.48</v>
@@ -5547,7 +5547,7 @@
         <v>39722</v>
       </c>
       <c r="B589">
-        <v>209.1017223622512</v>
+        <v>208.3850376018547</v>
       </c>
       <c r="C589">
         <v>15511.13</v>
@@ -5561,7 +5561,7 @@
         <v>39753</v>
       </c>
       <c r="B590">
-        <v>146.347897498356</v>
+        <v>145.4011680580948</v>
       </c>
       <c r="C590">
         <v>16251.19</v>
@@ -5575,7 +5575,7 @@
         <v>39783</v>
       </c>
       <c r="B591">
-        <v>148.5708057750015</v>
+        <v>147.8193753421716</v>
       </c>
       <c r="C591">
         <v>11388.37</v>
@@ -5589,7 +5589,7 @@
         <v>39814</v>
       </c>
       <c r="B592">
-        <v>146.4392207254933</v>
+        <v>145.1595571759092</v>
       </c>
       <c r="C592">
         <v>11772.56</v>
@@ -5603,7 +5603,7 @@
         <v>39845</v>
       </c>
       <c r="B593">
-        <v>144.3146908439211</v>
+        <v>143.5728099996693</v>
       </c>
       <c r="C593">
         <v>15087.54</v>
@@ -5617,7 +5617,7 @@
         <v>39873</v>
       </c>
       <c r="B594">
-        <v>136.3779948874119</v>
+        <v>135.5392915874432</v>
       </c>
       <c r="C594">
         <v>20401.91</v>
@@ -5631,7 +5631,7 @@
         <v>39904</v>
       </c>
       <c r="B595">
-        <v>104.745746029674</v>
+        <v>104.0756724751827</v>
       </c>
       <c r="C595">
         <v>16736.19</v>
@@ -5645,7 +5645,7 @@
         <v>39934</v>
       </c>
       <c r="B596">
-        <v>100.5218985281527</v>
+        <v>100.3255047445722</v>
       </c>
       <c r="C596">
         <v>16066.15</v>
@@ -5659,7 +5659,7 @@
         <v>39965</v>
       </c>
       <c r="B597">
-        <v>130.580307638156</v>
+        <v>128.8551785432665</v>
       </c>
       <c r="C597">
         <v>17881.58</v>
@@ -5673,7 +5673,7 @@
         <v>39995</v>
       </c>
       <c r="B598">
-        <v>117.7992038866299</v>
+        <v>116.6272559565857</v>
       </c>
       <c r="C598">
         <v>12265.1</v>
@@ -5687,7 +5687,7 @@
         <v>40026</v>
       </c>
       <c r="B599">
-        <v>109.2755924845191</v>
+        <v>108.3243792150083</v>
       </c>
       <c r="C599">
         <v>14420.23</v>
@@ -5701,7 +5701,7 @@
         <v>40057</v>
       </c>
       <c r="B600">
-        <v>119.5786353129479</v>
+        <v>118.0273220041321</v>
       </c>
       <c r="C600">
         <v>13766.26</v>
@@ -5715,7 +5715,7 @@
         <v>40087</v>
       </c>
       <c r="B601">
-        <v>98.05284284168079</v>
+        <v>97.24105850355646</v>
       </c>
       <c r="C601">
         <v>19294.3</v>
@@ -5729,7 +5729,7 @@
         <v>40118</v>
       </c>
       <c r="B602">
-        <v>109.3460052265073</v>
+        <v>108.0853682974562</v>
       </c>
       <c r="C602">
         <v>20780.36</v>
@@ -5743,7 +5743,7 @@
         <v>40148</v>
       </c>
       <c r="B603">
-        <v>105.6822037323678</v>
+        <v>104.698343737892</v>
       </c>
       <c r="C603">
         <v>19363.22</v>
@@ -5757,7 +5757,7 @@
         <v>40179</v>
       </c>
       <c r="B604">
-        <v>120.6541925646326</v>
+        <v>119.555216759501</v>
       </c>
       <c r="C604">
         <v>23146.06</v>
@@ -5771,7 +5771,7 @@
         <v>40210</v>
       </c>
       <c r="B605">
-        <v>120.4738756830882</v>
+        <v>119.2280136417946</v>
       </c>
       <c r="C605">
         <v>29661.91</v>
@@ -5785,7 +5785,7 @@
         <v>40238</v>
       </c>
       <c r="B606">
-        <v>121.4486499167599</v>
+        <v>119.8838706859767</v>
       </c>
       <c r="C606">
         <v>19562.9</v>
@@ -5799,7 +5799,7 @@
         <v>40269</v>
       </c>
       <c r="B607">
-        <v>109.2899844711115</v>
+        <v>108.2369043268468</v>
       </c>
       <c r="C607">
         <v>23612.76</v>
@@ -5813,7 +5813,7 @@
         <v>40299</v>
       </c>
       <c r="B608">
-        <v>143.2495778135694</v>
+        <v>142.3253228357702</v>
       </c>
       <c r="C608">
         <v>22580.16</v>
@@ -5827,7 +5827,7 @@
         <v>40330</v>
       </c>
       <c r="B609">
-        <v>142.0473363347887</v>
+        <v>140.6630037503433</v>
       </c>
       <c r="C609">
         <v>23196.64</v>
@@ -5841,7 +5841,7 @@
         <v>40360</v>
       </c>
       <c r="B610">
-        <v>146.8894558961345</v>
+        <v>145.6500535067759</v>
       </c>
       <c r="C610">
         <v>20535.61</v>
@@ -5855,7 +5855,7 @@
         <v>40391</v>
       </c>
       <c r="B611">
-        <v>121.8905923644854</v>
+        <v>121.0362669980848</v>
       </c>
       <c r="C611">
         <v>32177.13</v>
@@ -5869,7 +5869,7 @@
         <v>40422</v>
       </c>
       <c r="B612">
-        <v>127.3968295946675</v>
+        <v>126.9325302656393</v>
       </c>
       <c r="C612">
         <v>20655.87</v>
@@ -5883,7 +5883,7 @@
         <v>40452</v>
       </c>
       <c r="B613">
-        <v>123.387131219425</v>
+        <v>122.4835852769034</v>
       </c>
       <c r="C613">
         <v>27171.7</v>
@@ -5897,7 +5897,7 @@
         <v>40483</v>
       </c>
       <c r="B614">
-        <v>127.6874940383572</v>
+        <v>127.3967412444531</v>
       </c>
       <c r="C614">
         <v>13966.62</v>
@@ -5911,7 +5911,7 @@
         <v>40513</v>
       </c>
       <c r="B615">
-        <v>139.8541643252609</v>
+        <v>138.7053420130619</v>
       </c>
       <c r="C615">
         <v>14303.45</v>
@@ -5925,7 +5925,7 @@
         <v>40544</v>
       </c>
       <c r="B616">
-        <v>124.4218623012391</v>
+        <v>122.8220914550955</v>
       </c>
       <c r="C616">
         <v>15449.49</v>
@@ -5939,7 +5939,7 @@
         <v>40575</v>
       </c>
       <c r="B617">
-        <v>97.59380192664925</v>
+        <v>97.03994203349446</v>
       </c>
       <c r="C617">
         <v>14260.61</v>
@@ -5953,7 +5953,7 @@
         <v>40603</v>
       </c>
       <c r="B618">
-        <v>132.0426524142706</v>
+        <v>130.7574818953301</v>
       </c>
       <c r="C618">
         <v>12549.44</v>
@@ -5967,7 +5967,7 @@
         <v>40634</v>
       </c>
       <c r="B619">
-        <v>124.2883772537001</v>
+        <v>122.7145545799942</v>
       </c>
       <c r="C619">
         <v>10858.82</v>
@@ -5981,7 +5981,7 @@
         <v>40664</v>
       </c>
       <c r="B620">
-        <v>94.70958434682804</v>
+        <v>93.73179639503762</v>
       </c>
       <c r="C620">
         <v>14147.12</v>
@@ -5995,7 +5995,7 @@
         <v>40695</v>
       </c>
       <c r="B621">
-        <v>124.3094285103497</v>
+        <v>123.4075019395278</v>
       </c>
       <c r="C621">
         <v>12621</v>
@@ -6009,7 +6009,7 @@
         <v>40725</v>
       </c>
       <c r="B622">
-        <v>151.2452272338302</v>
+        <v>150.4897085334831</v>
       </c>
       <c r="C622">
         <v>16853.56</v>
@@ -6023,7 +6023,7 @@
         <v>40756</v>
       </c>
       <c r="B623">
-        <v>215.6544495486055</v>
+        <v>214.329232667804</v>
       </c>
       <c r="C623">
         <v>15732.06</v>
@@ -6037,7 +6037,7 @@
         <v>40787</v>
       </c>
       <c r="B624">
-        <v>194.6587815391837</v>
+        <v>193.5056137891833</v>
       </c>
       <c r="C624">
         <v>18687.09</v>
@@ -6051,7 +6051,7 @@
         <v>40817</v>
       </c>
       <c r="B625">
-        <v>173.323636431364</v>
+        <v>171.6096588888011</v>
       </c>
       <c r="C625">
         <v>22334.08</v>
@@ -6065,7 +6065,7 @@
         <v>40848</v>
       </c>
       <c r="B626">
-        <v>195.3191983945288</v>
+        <v>194.1200886959885</v>
       </c>
       <c r="C626">
         <v>18310.76</v>
@@ -6079,7 +6079,7 @@
         <v>40878</v>
       </c>
       <c r="B627">
-        <v>186.3661586629061</v>
+        <v>184.8633223677085</v>
       </c>
       <c r="C627">
         <v>17926.63</v>
@@ -6093,7 +6093,7 @@
         <v>40909</v>
       </c>
       <c r="B628">
-        <v>158.4827450981174</v>
+        <v>157.4103645155096</v>
       </c>
       <c r="C628">
         <v>18402.08</v>
@@ -6107,7 +6107,7 @@
         <v>40940</v>
       </c>
       <c r="B629">
-        <v>148.336169817166</v>
+        <v>146.9292622417652</v>
       </c>
       <c r="C629">
         <v>18511.58</v>
@@ -6121,7 +6121,7 @@
         <v>40969</v>
       </c>
       <c r="B630">
-        <v>146.8662941329987</v>
+        <v>145.4045332961312</v>
       </c>
       <c r="C630">
         <v>18355.28</v>
@@ -6135,7 +6135,7 @@
         <v>41000</v>
       </c>
       <c r="B631">
-        <v>136.5026773660001</v>
+        <v>135.0679968782495</v>
       </c>
       <c r="C631">
         <v>15813.25</v>
@@ -6149,7 +6149,7 @@
         <v>41030</v>
       </c>
       <c r="B632">
-        <v>165.5725107898236</v>
+        <v>164.316348189289</v>
       </c>
       <c r="C632">
         <v>14609.73</v>
@@ -6163,7 +6163,7 @@
         <v>41061</v>
       </c>
       <c r="B633">
-        <v>188.3104954970489</v>
+        <v>186.9947549931406</v>
       </c>
       <c r="C633">
         <v>36236.57</v>
@@ -6177,7 +6177,7 @@
         <v>41091</v>
       </c>
       <c r="B634">
-        <v>152.9925643094402</v>
+        <v>151.4488245605221</v>
       </c>
       <c r="C634">
         <v>33079.34</v>
@@ -6191,7 +6191,7 @@
         <v>41122</v>
       </c>
       <c r="B635">
-        <v>118.6340184514001</v>
+        <v>117.9418224588084</v>
       </c>
       <c r="C635">
         <v>35269.25</v>
@@ -6205,7 +6205,7 @@
         <v>41153</v>
       </c>
       <c r="B636">
-        <v>156.1049057969113</v>
+        <v>154.8690042634695</v>
       </c>
       <c r="C636">
         <v>24828.08</v>
@@ -6219,7 +6219,7 @@
         <v>41183</v>
       </c>
       <c r="B637">
-        <v>151.6563442957393</v>
+        <v>150.4968791121075</v>
       </c>
       <c r="C637">
         <v>20310.6</v>
@@ -6233,7 +6233,7 @@
         <v>41214</v>
       </c>
       <c r="B638">
-        <v>161.037000110006</v>
+        <v>159.677797116342</v>
       </c>
       <c r="C638">
         <v>30968.85</v>
@@ -6247,7 +6247,7 @@
         <v>41244</v>
       </c>
       <c r="B639">
-        <v>170.0445051229279</v>
+        <v>168.5665353236465</v>
       </c>
       <c r="C639">
         <v>39555.1</v>
@@ -6261,7 +6261,7 @@
         <v>41275</v>
       </c>
       <c r="B640">
-        <v>165.9602131185743</v>
+        <v>164.4800151705872</v>
       </c>
       <c r="C640">
         <v>30948.78</v>
@@ -6275,7 +6275,7 @@
         <v>41306</v>
       </c>
       <c r="B641">
-        <v>123.416359685074</v>
+        <v>122.2500860633757</v>
       </c>
       <c r="C641">
         <v>20086.67</v>
@@ -6289,7 +6289,7 @@
         <v>41334</v>
       </c>
       <c r="B642">
-        <v>145.2660393616929</v>
+        <v>144.3381785908585</v>
       </c>
       <c r="C642">
         <v>31259.48</v>
@@ -6303,7 +6303,7 @@
         <v>41365</v>
       </c>
       <c r="B643">
-        <v>139.8121878879431</v>
+        <v>138.5681752243291</v>
       </c>
       <c r="C643">
         <v>20386.52</v>
@@ -6317,7 +6317,7 @@
         <v>41395</v>
       </c>
       <c r="B644">
-        <v>108.4549273193699</v>
+        <v>107.3736009971986</v>
       </c>
       <c r="C644">
         <v>14386.56</v>
@@ -6331,7 +6331,7 @@
         <v>41426</v>
       </c>
       <c r="B645">
-        <v>130.3340246119637</v>
+        <v>128.9385971166541</v>
       </c>
       <c r="C645">
         <v>13789.65</v>
@@ -6345,7 +6345,7 @@
         <v>41456</v>
       </c>
       <c r="B646">
-        <v>108.6116566460297</v>
+        <v>107.4570464892616</v>
       </c>
       <c r="C646">
         <v>15417.21</v>
@@ -6359,7 +6359,7 @@
         <v>41487</v>
       </c>
       <c r="B647">
-        <v>127.5034977499067</v>
+        <v>126.2155870727981</v>
       </c>
       <c r="C647">
         <v>14158.71</v>
@@ -6373,7 +6373,7 @@
         <v>41518</v>
       </c>
       <c r="B648">
-        <v>141.4751687497372</v>
+        <v>140.2353852234925</v>
       </c>
       <c r="C648">
         <v>15448.87</v>
@@ -6387,7 +6387,7 @@
         <v>41548</v>
       </c>
       <c r="B649">
-        <v>167.4150691586816</v>
+        <v>165.600125093339</v>
       </c>
       <c r="C649">
         <v>21717.67</v>
@@ -6401,7 +6401,7 @@
         <v>41579</v>
       </c>
       <c r="B650">
-        <v>108.1183175636579</v>
+        <v>106.7454152044698</v>
       </c>
       <c r="C650">
         <v>12641.28</v>
@@ -6415,7 +6415,7 @@
         <v>41609</v>
       </c>
       <c r="B651">
-        <v>128.2759877710655</v>
+        <v>126.5166022351656</v>
       </c>
       <c r="C651">
         <v>17539.43</v>
@@ -6429,7 +6429,7 @@
         <v>41640</v>
       </c>
       <c r="B652">
-        <v>119.7245269233516</v>
+        <v>118.5646765624796</v>
       </c>
       <c r="C652">
         <v>21842.74</v>
@@ -6443,7 +6443,7 @@
         <v>41671</v>
       </c>
       <c r="B653">
-        <v>100.9257881140897</v>
+        <v>99.95335340706762</v>
       </c>
       <c r="C653">
         <v>21788.17</v>
@@ -6457,7 +6457,7 @@
         <v>41699</v>
       </c>
       <c r="B654">
-        <v>114.6227417235872</v>
+        <v>113.2747869513521</v>
       </c>
       <c r="C654">
         <v>19225.85</v>
@@ -6471,7 +6471,7 @@
         <v>41730</v>
       </c>
       <c r="B655">
-        <v>118.4856502358804</v>
+        <v>116.985740328861</v>
       </c>
       <c r="C655">
         <v>13590.26</v>
@@ -6485,7 +6485,7 @@
         <v>41760</v>
       </c>
       <c r="B656">
-        <v>111.0433455756112</v>
+        <v>110.0210071068496</v>
       </c>
       <c r="C656">
         <v>17282.29</v>
@@ -6499,7 +6499,7 @@
         <v>41791</v>
       </c>
       <c r="B657">
-        <v>96.48710743626016</v>
+        <v>95.23222135493667</v>
       </c>
       <c r="C657">
         <v>19739.77</v>
@@ -6513,7 +6513,7 @@
         <v>41821</v>
       </c>
       <c r="B658">
-        <v>99.91989950272327</v>
+        <v>98.63376284558369</v>
       </c>
       <c r="C658">
         <v>20342.31</v>
@@ -6527,7 +6527,7 @@
         <v>41852</v>
       </c>
       <c r="B659">
-        <v>105.1212350096452</v>
+        <v>104.0928313313606</v>
       </c>
       <c r="C659">
         <v>13934.56</v>
@@ -6541,7 +6541,7 @@
         <v>41883</v>
       </c>
       <c r="B660">
-        <v>128.619448259001</v>
+        <v>127.2664035417716</v>
       </c>
       <c r="C660">
         <v>14067.97</v>
@@ -6555,7 +6555,7 @@
         <v>41913</v>
       </c>
       <c r="B661">
-        <v>114.7173344999121</v>
+        <v>113.6784470930189</v>
       </c>
       <c r="C661">
         <v>14332.98</v>
@@ -6569,7 +6569,7 @@
         <v>41944</v>
       </c>
       <c r="B662">
-        <v>128.5742069786289</v>
+        <v>127.1133237248658</v>
       </c>
       <c r="C662">
         <v>25064.32</v>
@@ -6583,7 +6583,7 @@
         <v>41974</v>
       </c>
       <c r="B663">
-        <v>113.9207567224148</v>
+        <v>113.3508406716302</v>
       </c>
       <c r="C663">
         <v>17021.78</v>
@@ -6597,7 +6597,7 @@
         <v>42005</v>
       </c>
       <c r="B664">
-        <v>135.149157854376</v>
+        <v>133.9386088487255</v>
       </c>
       <c r="C664">
         <v>25443.97</v>
@@ -6611,7 +6611,7 @@
         <v>42036</v>
       </c>
       <c r="B665">
-        <v>122.7105160759219</v>
+        <v>121.8015892684479</v>
       </c>
       <c r="C665">
         <v>29456.69</v>
@@ -6625,7 +6625,7 @@
         <v>42064</v>
       </c>
       <c r="B666">
-        <v>117.8843039202131</v>
+        <v>115.9300541223834</v>
       </c>
       <c r="C666">
         <v>29700.53</v>
@@ -6639,7 +6639,7 @@
         <v>42095</v>
       </c>
       <c r="B667">
-        <v>100.8251195492363</v>
+        <v>99.67836720920404</v>
       </c>
       <c r="C667">
         <v>22530.23</v>
@@ -6653,7 +6653,7 @@
         <v>42125</v>
       </c>
       <c r="B668">
-        <v>101.5000153384344</v>
+        <v>100.7768578536792</v>
       </c>
       <c r="C668">
         <v>21803.69</v>
@@ -6667,7 +6667,7 @@
         <v>42156</v>
       </c>
       <c r="B669">
-        <v>118.7254655937451</v>
+        <v>117.5977528966915</v>
       </c>
       <c r="C669">
         <v>25042.18</v>
@@ -6681,7 +6681,7 @@
         <v>42186</v>
       </c>
       <c r="B670">
-        <v>122.9482155335303</v>
+        <v>121.4457753078265</v>
       </c>
       <c r="C670">
         <v>26689.86</v>
@@ -6695,7 +6695,7 @@
         <v>42217</v>
       </c>
       <c r="B671">
-        <v>117.1897306919892</v>
+        <v>116.480904188619</v>
       </c>
       <c r="C671">
         <v>22015.01</v>
@@ -6709,7 +6709,7 @@
         <v>42248</v>
       </c>
       <c r="B672">
-        <v>153.8398599199942</v>
+        <v>152.9517237083356</v>
       </c>
       <c r="C672">
         <v>20895.17</v>
@@ -6723,7 +6723,7 @@
         <v>42278</v>
       </c>
       <c r="B673">
-        <v>115.3986716072227</v>
+        <v>114.6020950105016</v>
       </c>
       <c r="C673">
         <v>25572.94</v>
@@ -6737,7 +6737,7 @@
         <v>42309</v>
       </c>
       <c r="B674">
-        <v>106.0600801796203</v>
+        <v>104.8612585660686</v>
       </c>
       <c r="C674">
         <v>21316.99</v>
@@ -6751,7 +6751,7 @@
         <v>42339</v>
       </c>
       <c r="B675">
-        <v>116.9237490628539</v>
+        <v>115.9357075215106</v>
       </c>
       <c r="C675">
         <v>16845.93</v>
@@ -6765,7 +6765,7 @@
         <v>42370</v>
       </c>
       <c r="B676">
-        <v>140.9802811438042</v>
+        <v>139.9642540371341</v>
       </c>
       <c r="C676">
         <v>18498.77</v>
@@ -6779,7 +6779,7 @@
         <v>42401</v>
       </c>
       <c r="B677">
-        <v>145.7767468580293</v>
+        <v>144.826617455293</v>
       </c>
       <c r="C677">
         <v>20446.37</v>
@@ -6793,7 +6793,7 @@
         <v>42430</v>
       </c>
       <c r="B678">
-        <v>162.3461336415121</v>
+        <v>160.7291506237977</v>
       </c>
       <c r="C678">
         <v>22191.53</v>
@@ -6807,7 +6807,7 @@
         <v>42461</v>
       </c>
       <c r="B679">
-        <v>146.3993800613457</v>
+        <v>144.8379381031954</v>
       </c>
       <c r="C679">
         <v>15032.11</v>
@@ -6821,7 +6821,7 @@
         <v>42491</v>
       </c>
       <c r="B680">
-        <v>123.777640218217</v>
+        <v>122.2084108208894</v>
       </c>
       <c r="C680">
         <v>21466.45</v>
@@ -6835,7 +6835,7 @@
         <v>42522</v>
       </c>
       <c r="B681">
-        <v>220.8623331558001</v>
+        <v>220.1147415136731</v>
       </c>
       <c r="C681">
         <v>17423.54</v>
@@ -6849,7 +6849,7 @@
         <v>42552</v>
       </c>
       <c r="B682">
-        <v>189.0333227967832</v>
+        <v>188.7607739232181</v>
       </c>
       <c r="C682">
         <v>45973.39</v>
@@ -6863,7 +6863,7 @@
         <v>42583</v>
       </c>
       <c r="B683">
-        <v>136.5229370638752</v>
+        <v>135.3258803627412</v>
       </c>
       <c r="C683">
         <v>44083.75</v>
@@ -6877,7 +6877,7 @@
         <v>42614</v>
       </c>
       <c r="B684">
-        <v>139.162318128015</v>
+        <v>137.5261376255996</v>
       </c>
       <c r="C684">
         <v>28374.06</v>
@@ -6891,7 +6891,7 @@
         <v>42644</v>
       </c>
       <c r="B685">
-        <v>122.411453039911</v>
+        <v>121.611165183971</v>
       </c>
       <c r="C685">
         <v>18582.51</v>
@@ -6905,7 +6905,7 @@
         <v>42675</v>
       </c>
       <c r="B686">
-        <v>215.2003134715575</v>
+        <v>213.8180989889198</v>
       </c>
       <c r="C686">
         <v>26743.54</v>
@@ -6919,7 +6919,7 @@
         <v>42705</v>
       </c>
       <c r="B687">
-        <v>186.7729169531476</v>
+        <v>185.3912372721263</v>
       </c>
       <c r="C687">
         <v>30556.11</v>
@@ -6933,7 +6933,7 @@
         <v>42736</v>
       </c>
       <c r="B688">
-        <v>255.4222639433124</v>
+        <v>252.5567930262066</v>
       </c>
       <c r="C688">
         <v>38065.04</v>
@@ -6947,7 +6947,7 @@
         <v>42767</v>
       </c>
       <c r="B689">
-        <v>189.7555808488887</v>
+        <v>188.4748211580352</v>
       </c>
       <c r="C689">
         <v>34721.72</v>
@@ -6961,7 +6961,7 @@
         <v>42795</v>
       </c>
       <c r="B690">
-        <v>250.2431285926663</v>
+        <v>246.4132433169806</v>
       </c>
       <c r="C690">
         <v>28585.07</v>
@@ -6975,7 +6975,7 @@
         <v>42826</v>
       </c>
       <c r="B691">
-        <v>177.869298691183</v>
+        <v>175.7483549203579</v>
       </c>
       <c r="C691">
         <v>22038.28</v>
@@ -6989,7 +6989,7 @@
         <v>42856</v>
       </c>
       <c r="B692">
-        <v>142.7336804079073</v>
+        <v>141.1083830098967</v>
       </c>
       <c r="C692">
         <v>20300.89</v>
@@ -7003,7 +7003,7 @@
         <v>42887</v>
       </c>
       <c r="B693">
-        <v>175.6060180706379</v>
+        <v>173.1601118851287</v>
       </c>
       <c r="C693">
         <v>15384.21</v>
@@ -7017,7 +7017,7 @@
         <v>42917</v>
       </c>
       <c r="B694">
-        <v>172.379027228027</v>
+        <v>169.3940974540218</v>
       </c>
       <c r="C694">
         <v>16915.2</v>
@@ -7031,7 +7031,7 @@
         <v>42948</v>
       </c>
       <c r="B695">
-        <v>141.8386167108098</v>
+        <v>140.4061625163181</v>
       </c>
       <c r="C695">
         <v>21567.95</v>
@@ -7045,7 +7045,7 @@
         <v>42979</v>
       </c>
       <c r="B696">
-        <v>163.5386274069365</v>
+        <v>161.1373268218316</v>
       </c>
       <c r="C696">
         <v>15468.96</v>
@@ -7059,7 +7059,7 @@
         <v>43009</v>
       </c>
       <c r="B697">
-        <v>149.8742658588074</v>
+        <v>148.4371288213831</v>
       </c>
       <c r="C697">
         <v>20376.24</v>
@@ -7073,7 +7073,7 @@
         <v>43040</v>
       </c>
       <c r="B698">
-        <v>168.1000626230824</v>
+        <v>165.6133808546744</v>
       </c>
       <c r="C698">
         <v>20821.27</v>
@@ -7087,7 +7087,7 @@
         <v>43070</v>
       </c>
       <c r="B699">
-        <v>155.6193982051384</v>
+        <v>153.4196525390174</v>
       </c>
       <c r="C699">
         <v>27945.3</v>
@@ -7101,7 +7101,7 @@
         <v>43101</v>
       </c>
       <c r="B700">
-        <v>180.2059169545451</v>
+        <v>177.0375604399123</v>
       </c>
       <c r="C700">
         <v>21420.12</v>
@@ -7115,7 +7115,7 @@
         <v>43132</v>
       </c>
       <c r="B701">
-        <v>130.8336031571206</v>
+        <v>128.6703239074004</v>
       </c>
       <c r="C701">
         <v>17493.08</v>
@@ -7129,7 +7129,7 @@
         <v>43160</v>
       </c>
       <c r="B702">
-        <v>181.5623216587443</v>
+        <v>178.4530034912016</v>
       </c>
       <c r="C702">
         <v>12197.86</v>
@@ -7143,7 +7143,7 @@
         <v>43191</v>
       </c>
       <c r="B703">
-        <v>173.5819054444155</v>
+        <v>170.6900898970385</v>
       </c>
       <c r="C703">
         <v>12920.08</v>
@@ -7157,7 +7157,7 @@
         <v>43221</v>
       </c>
       <c r="B704">
-        <v>172.6211881258129</v>
+        <v>170.2781483345167</v>
       </c>
       <c r="C704">
         <v>19883.07</v>
@@ -7171,7 +7171,7 @@
         <v>43252</v>
       </c>
       <c r="B705">
-        <v>163.585354280652</v>
+        <v>161.661239991144</v>
       </c>
       <c r="C705">
         <v>25859.36</v>
@@ -7185,7 +7185,7 @@
         <v>43282</v>
       </c>
       <c r="B706">
-        <v>238.6202618329807</v>
+        <v>233.4648588592692</v>
       </c>
       <c r="C706">
         <v>22117.7</v>
@@ -7199,7 +7199,7 @@
         <v>43313</v>
       </c>
       <c r="B707">
-        <v>182.2319292355351</v>
+        <v>179.2019741805026</v>
       </c>
       <c r="C707">
         <v>30926.84</v>
@@ -7213,7 +7213,7 @@
         <v>43344</v>
       </c>
       <c r="B708">
-        <v>205.8479735884054</v>
+        <v>202.4367793749528</v>
       </c>
       <c r="C708">
         <v>27915.26</v>
@@ -7227,7 +7227,7 @@
         <v>43374</v>
       </c>
       <c r="B709">
-        <v>225.9593538889647</v>
+        <v>222.1465397952716</v>
       </c>
       <c r="C709">
         <v>22779.45</v>
@@ -7241,7 +7241,7 @@
         <v>43405</v>
       </c>
       <c r="B710">
-        <v>265.3688590079915</v>
+        <v>260.26032300337</v>
       </c>
       <c r="C710">
         <v>18793.39</v>
@@ -7255,7 +7255,7 @@
         <v>43435</v>
       </c>
       <c r="B711">
-        <v>218.3552899090525</v>
+        <v>215.5648434194108</v>
       </c>
       <c r="C711">
         <v>26231.1</v>
@@ -7269,7 +7269,7 @@
         <v>43466</v>
       </c>
       <c r="B712">
-        <v>243.7158717420112</v>
+        <v>240.5242538829954</v>
       </c>
       <c r="C712">
         <v>36382.28</v>
@@ -7283,7 +7283,7 @@
         <v>43497</v>
       </c>
       <c r="B713">
-        <v>177.8681478999297</v>
+        <v>175.6227191045105</v>
       </c>
       <c r="C713">
         <v>51178.63</v>
@@ -7297,7 +7297,7 @@
         <v>43525</v>
       </c>
       <c r="B714">
-        <v>251.8588298763838</v>
+        <v>247.7255139672963</v>
       </c>
       <c r="C714">
         <v>35809.01</v>
@@ -7311,7 +7311,7 @@
         <v>43556</v>
       </c>
       <c r="B715">
-        <v>204.9201688447855</v>
+        <v>201.6295838116967</v>
       </c>
       <c r="C715">
         <v>27627.57</v>
@@ -7325,7 +7325,7 @@
         <v>43586</v>
       </c>
       <c r="B716">
-        <v>238.2745103394634</v>
+        <v>234.3078071592159</v>
       </c>
       <c r="C716">
         <v>57517.98</v>
@@ -7339,7 +7339,7 @@
         <v>43617</v>
       </c>
       <c r="B717">
-        <v>350.0304589158609</v>
+        <v>342.2914178463964</v>
       </c>
       <c r="C717">
         <v>41085.63</v>
@@ -7353,7 +7353,7 @@
         <v>43647</v>
       </c>
       <c r="B718">
-        <v>259.8561942074757</v>
+        <v>255.8494199320641</v>
       </c>
       <c r="C718">
         <v>22822.22</v>
@@ -7367,7 +7367,7 @@
         <v>43678</v>
       </c>
       <c r="B719">
-        <v>293.1981802654853</v>
+        <v>288.7119942269406</v>
       </c>
       <c r="C719">
         <v>33126.3</v>
@@ -7381,7 +7381,7 @@
         <v>43709</v>
       </c>
       <c r="B720">
-        <v>250.5044558967545</v>
+        <v>246.9136997403976</v>
       </c>
       <c r="C720">
         <v>32220.86</v>
@@ -7395,7 +7395,7 @@
         <v>43739</v>
       </c>
       <c r="B721">
-        <v>208.9544648685717</v>
+        <v>206.7412144605118</v>
       </c>
       <c r="C721">
         <v>39475.35</v>
@@ -7409,7 +7409,7 @@
         <v>43770</v>
       </c>
       <c r="B722">
-        <v>259.36974506763</v>
+        <v>254.5405484980237</v>
       </c>
       <c r="C722">
         <v>39040.36</v>
@@ -7423,7 +7423,7 @@
         <v>43800</v>
       </c>
       <c r="B723">
-        <v>244.621386533282</v>
+        <v>241.2865805218555</v>
       </c>
       <c r="C723">
         <v>52683.16</v>
@@ -7437,7 +7437,7 @@
         <v>43831</v>
       </c>
       <c r="B724">
-        <v>199.4266364361742</v>
+        <v>196.3321175298275</v>
       </c>
       <c r="C724">
         <v>42258.74</v>
@@ -7451,7 +7451,7 @@
         <v>43862</v>
       </c>
       <c r="B725">
-        <v>198.0965730411711</v>
+        <v>195.5943393684268</v>
       </c>
       <c r="C725">
         <v>39762.47</v>
@@ -7465,7 +7465,7 @@
         <v>43891</v>
       </c>
       <c r="B726">
-        <v>311.567901301411</v>
+        <v>309.2800270112081</v>
       </c>
       <c r="C726">
         <v>56223.62</v>
@@ -7479,7 +7479,7 @@
         <v>43922</v>
       </c>
       <c r="B727">
-        <v>334.9766594393689</v>
+        <v>330.9455147178349</v>
       </c>
       <c r="C727">
         <v>21438.99</v>
@@ -7493,7 +7493,7 @@
         <v>43952</v>
       </c>
       <c r="B728">
-        <v>424.1125449663939</v>
+        <v>418.1484090379876</v>
       </c>
       <c r="C728">
         <v>26490.73</v>
@@ -7507,7 +7507,7 @@
         <v>43983</v>
       </c>
       <c r="B729">
-        <v>325.133513407121</v>
+        <v>319.7302475651302</v>
       </c>
       <c r="C729">
         <v>28737.92</v>
@@ -7521,7 +7521,7 @@
         <v>44013</v>
       </c>
       <c r="B730">
-        <v>308.7049646398453</v>
+        <v>304.3794526427777</v>
       </c>
       <c r="C730">
         <v>26888.29</v>
@@ -7535,7 +7535,7 @@
         <v>44044</v>
       </c>
       <c r="B731">
-        <v>304.4329421174711</v>
+        <v>298.7593161205136</v>
       </c>
       <c r="C731">
         <v>20430.03</v>
@@ -7549,7 +7549,7 @@
         <v>44075</v>
       </c>
       <c r="B732">
-        <v>328.0033306297782</v>
+        <v>321.6726174788043</v>
       </c>
       <c r="C732">
         <v>26409.8</v>
@@ -7563,7 +7563,7 @@
         <v>44105</v>
       </c>
       <c r="B733">
-        <v>313.184656510125</v>
+        <v>308.8275278640793</v>
       </c>
       <c r="C733">
         <v>28194.52</v>
@@ -7577,7 +7577,7 @@
         <v>44136</v>
       </c>
       <c r="B734">
-        <v>421.6440340990687</v>
+        <v>413.0268277626341</v>
       </c>
       <c r="C734">
         <v>25062.17</v>
@@ -7591,7 +7591,7 @@
         <v>44166</v>
       </c>
       <c r="B735">
-        <v>315.1138397972732</v>
+        <v>309.4721506268532</v>
       </c>
       <c r="C735">
         <v>14886.35</v>
@@ -7605,7 +7605,7 @@
         <v>44197</v>
       </c>
       <c r="B736">
-        <v>283.3187814552742</v>
+        <v>278.1276531576149</v>
       </c>
       <c r="C736">
         <v>11956.53</v>
@@ -7619,7 +7619,7 @@
         <v>44228</v>
       </c>
       <c r="B737">
-        <v>200.1679891856918</v>
+        <v>197.4421938797589</v>
       </c>
       <c r="C737">
         <v>9050.271000000001</v>
@@ -7633,7 +7633,7 @@
         <v>44256</v>
       </c>
       <c r="B738">
-        <v>221.5326150185953</v>
+        <v>217.3432453229355</v>
       </c>
       <c r="C738">
         <v>13602.12</v>
@@ -7647,7 +7647,7 @@
         <v>44287</v>
       </c>
       <c r="B739">
-        <v>206.4836958067224</v>
+        <v>201.9273109746566</v>
       </c>
       <c r="C739">
         <v>14889.97</v>
@@ -7661,7 +7661,7 @@
         <v>44317</v>
       </c>
       <c r="B740">
-        <v>179.8988429019772</v>
+        <v>176.6224532944461</v>
       </c>
       <c r="C740">
         <v>15392.93</v>
@@ -7675,7 +7675,7 @@
         <v>44348</v>
       </c>
       <c r="B741">
-        <v>181.2342842132373</v>
+        <v>178.2599901070918</v>
       </c>
       <c r="C741">
         <v>21543.41</v>
@@ -7689,7 +7689,7 @@
         <v>44378</v>
       </c>
       <c r="B742">
-        <v>190.6583625160694</v>
+        <v>187.3705402994354</v>
       </c>
       <c r="C742">
         <v>19371.39</v>
@@ -7703,7 +7703,7 @@
         <v>44409</v>
       </c>
       <c r="B743">
-        <v>210.2341172280997</v>
+        <v>205.7920383952943</v>
       </c>
       <c r="C743">
         <v>17169.7</v>
@@ -7717,7 +7717,7 @@
         <v>44440</v>
       </c>
       <c r="B744">
-        <v>220.0526691068803</v>
+        <v>216.0359169310264</v>
       </c>
       <c r="C744">
         <v>23904</v>
@@ -7731,7 +7731,7 @@
         <v>44470</v>
       </c>
       <c r="B745">
-        <v>195.5307381228812</v>
+        <v>191.671836435197</v>
       </c>
       <c r="C745">
         <v>10477.78</v>
@@ -7745,7 +7745,7 @@
         <v>44501</v>
       </c>
       <c r="B746">
-        <v>234.9165445577295</v>
+        <v>230.3837822958489</v>
       </c>
       <c r="C746">
         <v>14556.52</v>
@@ -7759,7 +7759,7 @@
         <v>44531</v>
       </c>
       <c r="B747">
-        <v>267.8143930604346</v>
+        <v>262.1064307240119</v>
       </c>
       <c r="C747">
         <v>28225.75</v>
@@ -7773,7 +7773,7 @@
         <v>44562</v>
       </c>
       <c r="B748">
-        <v>233.8661103275871</v>
+        <v>228.7356125041467</v>
       </c>
       <c r="C748">
         <v>25576.78</v>
@@ -7787,7 +7787,7 @@
         <v>44593</v>
       </c>
       <c r="B749">
-        <v>186.5148530451768</v>
+        <v>183.6057727439216</v>
       </c>
       <c r="C749">
         <v>25212.72</v>
@@ -7801,7 +7801,7 @@
         <v>44621</v>
       </c>
       <c r="B750">
-        <v>305.9287663785963</v>
+        <v>301.131488026495</v>
       </c>
       <c r="C750">
         <v>27256.75</v>
@@ -7815,7 +7815,7 @@
         <v>44652</v>
       </c>
       <c r="B751">
-        <v>288.3391639672753</v>
+        <v>283.8781363515557</v>
       </c>
       <c r="C751">
         <v>41669.1</v>
@@ -7829,7 +7829,7 @@
         <v>44682</v>
       </c>
       <c r="B752">
-        <v>290.8332859373045</v>
+        <v>285.0584566904991</v>
       </c>
       <c r="C752">
         <v>25064.35</v>
@@ -7843,7 +7843,7 @@
         <v>44713</v>
       </c>
       <c r="B753">
-        <v>265.6497128228669</v>
+        <v>260.4604867643259</v>
       </c>
       <c r="C753">
         <v>23022.65</v>
@@ -7857,7 +7857,7 @@
         <v>44743</v>
       </c>
       <c r="B754">
-        <v>305.8102585798032</v>
+        <v>299.8935277200466</v>
       </c>
       <c r="C754">
         <v>19588.13</v>
@@ -7871,7 +7871,7 @@
         <v>44774</v>
       </c>
       <c r="B755">
-        <v>242.0802472826197</v>
+        <v>237.9736347313059</v>
       </c>
       <c r="C755">
         <v>31577.91</v>
@@ -7885,7 +7885,7 @@
         <v>44805</v>
       </c>
       <c r="B756">
-        <v>254.3224621816378</v>
+        <v>250.2901686848818</v>
       </c>
       <c r="C756">
         <v>22559.72</v>
@@ -7899,7 +7899,7 @@
         <v>44835</v>
       </c>
       <c r="B757">
-        <v>269.3816730800331</v>
+        <v>265.1142171465856</v>
       </c>
       <c r="C757">
         <v>28962.72</v>
@@ -7913,7 +7913,7 @@
         <v>44866</v>
       </c>
       <c r="B758">
-        <v>327.4263194628471</v>
+        <v>321.1608838289191</v>
       </c>
       <c r="C758">
         <v>34628.48</v>
@@ -7927,7 +7927,7 @@
         <v>44896</v>
       </c>
       <c r="B759">
-        <v>256.1258688829618</v>
+        <v>251.2434825867213</v>
       </c>
       <c r="C759">
         <v>17405.95</v>
@@ -7941,7 +7941,7 @@
         <v>44927</v>
       </c>
       <c r="B760">
-        <v>229.4347090707321</v>
+        <v>225.2665652637865</v>
       </c>
       <c r="C760">
         <v>29339.84</v>
@@ -7955,7 +7955,7 @@
         <v>44958</v>
       </c>
       <c r="B761">
-        <v>263.5794920922101</v>
+        <v>258.7959960011182</v>
       </c>
       <c r="C761">
         <v>32027.81</v>
@@ -7969,7 +7969,7 @@
         <v>44986</v>
       </c>
       <c r="B762">
-        <v>339.9825171873146</v>
+        <v>332.4381520705156</v>
       </c>
       <c r="C762">
         <v>17736.47</v>
@@ -7983,7 +7983,7 @@
         <v>45017</v>
       </c>
       <c r="B763">
-        <v>284.4818161033235</v>
+        <v>279.146716520926</v>
       </c>
       <c r="C763">
         <v>37638.8</v>
@@ -7997,7 +7997,7 @@
         <v>45047</v>
       </c>
       <c r="B764">
-        <v>214.0624366053083</v>
+        <v>210.2686299593984</v>
       </c>
       <c r="C764">
         <v>37309.42</v>
@@ -8011,7 +8011,7 @@
         <v>45078</v>
       </c>
       <c r="B765">
-        <v>238.4918358182614</v>
+        <v>233.8880561046794</v>
       </c>
       <c r="C765">
         <v>17679.01</v>
@@ -8025,7 +8025,7 @@
         <v>45108</v>
       </c>
       <c r="B766">
-        <v>203.2750010433726</v>
+        <v>199.4297538280572</v>
       </c>
       <c r="C766">
         <v>15649.48</v>
@@ -8039,7 +8039,7 @@
         <v>45139</v>
       </c>
       <c r="B767">
-        <v>188.6206020614568</v>
+        <v>185.1914308783575</v>
       </c>
       <c r="C767">
         <v>22258</v>
@@ -8053,7 +8053,7 @@
         <v>45170</v>
       </c>
       <c r="B768">
-        <v>213.4214422189196</v>
+        <v>209.203135049783</v>
       </c>
       <c r="C768">
         <v>16389.48</v>
@@ -8067,7 +8067,7 @@
         <v>45200</v>
       </c>
       <c r="B769">
-        <v>199.4589966404571</v>
+        <v>196.6001893058505</v>
       </c>
       <c r="C769">
         <v>15354.48</v>
@@ -8081,7 +8081,7 @@
         <v>45231</v>
       </c>
       <c r="B770">
-        <v>221.2394737275754</v>
+        <v>217.6053796407122</v>
       </c>
       <c r="C770">
         <v>17278.77</v>
@@ -8095,7 +8095,7 @@
         <v>45261</v>
       </c>
       <c r="B771">
-        <v>250.0928694319573</v>
+        <v>245.1914869375509</v>
       </c>
       <c r="C771">
         <v>17108.95</v>
@@ -8109,7 +8109,7 @@
         <v>45292</v>
       </c>
       <c r="B772">
-        <v>263.2454120216013</v>
+        <v>257.7093070425981</v>
       </c>
       <c r="C772">
         <v>17865.73</v>
@@ -8123,7 +8123,7 @@
         <v>45323</v>
       </c>
       <c r="B773">
-        <v>182.0078607190419</v>
+        <v>179.2567291827761</v>
       </c>
       <c r="C773">
         <v>16358.07</v>
@@ -8137,7 +8137,7 @@
         <v>45352</v>
       </c>
       <c r="B774">
-        <v>189.8975372153553</v>
+        <v>186.4398425231949</v>
       </c>
       <c r="C774">
         <v>17273.86</v>
@@ -8151,7 +8151,7 @@
         <v>45383</v>
       </c>
       <c r="B775">
-        <v>178.1456803307008</v>
+        <v>175.2480331890256</v>
       </c>
       <c r="C775">
         <v>16746.02</v>
@@ -8165,7 +8165,7 @@
         <v>45413</v>
       </c>
       <c r="B776">
-        <v>191.4040114292682</v>
+        <v>187.8818622780019</v>
       </c>
       <c r="C776">
         <v>15083.26</v>
@@ -8179,7 +8179,7 @@
         <v>45444</v>
       </c>
       <c r="B777">
-        <v>175.6118807949544</v>
+        <v>173.3483185053474</v>
       </c>
       <c r="C777">
         <v>14606.01</v>
@@ -8193,7 +8193,7 @@
         <v>45474</v>
       </c>
       <c r="B778">
-        <v>244.8646092924179</v>
+        <v>240.1429876117324</v>
       </c>
       <c r="C778">
         <v>15929.92</v>
@@ -8207,7 +8207,7 @@
         <v>45505</v>
       </c>
       <c r="B779">
-        <v>202.1984665853855</v>
+        <v>198.4387514274488</v>
       </c>
       <c r="C779">
         <v>21425.35</v>
@@ -8221,7 +8221,7 @@
         <v>45536</v>
       </c>
       <c r="B780">
-        <v>211.6260664172923</v>
+        <v>207.6940195296586</v>
       </c>
       <c r="C780">
         <v>20372.42</v>
@@ -8235,7 +8235,7 @@
         <v>45566</v>
       </c>
       <c r="B781">
-        <v>215.3047781947442</v>
+        <v>211.2685233870294</v>
       </c>
       <c r="C781">
         <v>21669.22</v>
@@ -8249,7 +8249,7 @@
         <v>45597</v>
       </c>
       <c r="B782">
-        <v>281.9809491690933</v>
+        <v>278.0729457167616</v>
       </c>
       <c r="C782">
         <v>24333.03</v>
@@ -8263,7 +8263,7 @@
         <v>45627</v>
       </c>
       <c r="B783">
-        <v>336.7250888039603</v>
+        <v>331.6220487542951</v>
       </c>
       <c r="C783">
         <v>30375.61</v>
@@ -8277,7 +8277,7 @@
         <v>45658</v>
       </c>
       <c r="B784">
-        <v>309.6800077582786</v>
+        <v>305.4691909196304</v>
       </c>
       <c r="C784">
         <v>41383.23</v>
@@ -8291,7 +8291,7 @@
         <v>45689</v>
       </c>
       <c r="B785">
-        <v>319.9595703778059</v>
+        <v>316.4400431868589</v>
       </c>
       <c r="C785">
         <v>48816.02</v>
@@ -8305,7 +8305,7 @@
         <v>45717</v>
       </c>
       <c r="B786">
-        <v>459.3789618456659</v>
+        <v>453.5588276474364</v>
       </c>
       <c r="C786">
         <v>53189.5</v>
@@ -8319,7 +8319,7 @@
         <v>45748</v>
       </c>
       <c r="B787">
-        <v>584.6521275425574</v>
+        <v>578.5987937727353</v>
       </c>
       <c r="C787">
         <v>72733.48</v>
@@ -8333,7 +8333,7 @@
         <v>45778</v>
       </c>
       <c r="B788">
-        <v>484.7157843271671</v>
+        <v>478.0368720970759</v>
       </c>
       <c r="C788">
         <v>77997.67999999999</v>
@@ -8347,7 +8347,7 @@
         <v>45809</v>
       </c>
       <c r="B789">
-        <v>358.5588823693955</v>
+        <v>354.568116960097</v>
       </c>
       <c r="C789">
         <v>84305.33</v>
@@ -8361,7 +8361,7 @@
         <v>45839</v>
       </c>
       <c r="B790">
-        <v>395.3445338948545</v>
+        <v>388.6548275568686</v>
       </c>
       <c r="C790">
         <v>95509.25999999999</v>
@@ -8375,7 +8375,7 @@
         <v>45870</v>
       </c>
       <c r="B791">
-        <v>332.0747970501799</v>
+        <v>325.9119299744629</v>
       </c>
       <c r="C791">
         <v>105558.3</v>
@@ -8389,7 +8389,7 @@
         <v>45901</v>
       </c>
       <c r="B792">
-        <v>297.6189053615164</v>
+        <v>294.0360347790922</v>
       </c>
       <c r="C792">
         <v>122422.5</v>
@@ -8403,7 +8403,7 @@
         <v>45931</v>
       </c>
       <c r="B793">
-        <v>404.5629347054088</v>
+        <v>413.5165987986647</v>
       </c>
       <c r="C793">
         <v>110331.9</v>
@@ -8416,6 +8416,9 @@
       <c r="A794" s="2">
         <v>45962</v>
       </c>
+      <c r="B794">
+        <v>373.2841601001309</v>
+      </c>
       <c r="C794">
         <v>91874.55</v>
       </c>
@@ -8432,6 +8435,28 @@
       </c>
       <c r="D795">
         <v>308.280990542199</v>
+      </c>
+    </row>
+    <row r="796" spans="1:4">
+      <c r="A796" s="2">
+        <v>46023</v>
+      </c>
+      <c r="C796">
+        <v>79904.34</v>
+      </c>
+      <c r="D796">
+        <v>410.757946210268</v>
+      </c>
+    </row>
+    <row r="797" spans="1:4">
+      <c r="A797" s="2">
+        <v>46054</v>
+      </c>
+      <c r="C797">
+        <v>83844.86</v>
+      </c>
+      <c r="D797">
+        <v>383.968181122839</v>
       </c>
     </row>
   </sheetData>
